--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -2999,7 +2999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3014,14 +3014,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DAIC runtime participant-packed30: v1 vs joint-K4 (official 47-subject test, seed 1337, strict teacher-forced)</t>
+          <t>DAIC runtime participant-packed30: canonical vs v1 vs joint-K4 (official 47-subject test, seed 1337, strict teacher-forced)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Qwen verdict = mean teacher-forced score margin per subject (INVALID counts as wrong; INVALID=0). Heads = logreg_raw / xgb_raw on hidden features, mean depressed probability &gt;= 0.5 per subject. Selected epochs: joint-K4 audio-only 5, audio+text 3; v1 audio-only 3, audio+text 2.</t>
+          <t>Qwen verdict = mean teacher-forced score margin per subject (INVALID counts as wrong; INVALID=0). Heads = logreg_raw / xgb_raw on hidden features, mean depressed probability &gt;= 0.5 per subject. Canonical joint-K4 has no head caches under this recipe (not run). Selected epochs: joint-K4 audio-only 5, audio+text 3; v1 audio-only 3, audio+text 2.</t>
         </is>
       </c>
     </row>
@@ -3053,10 +3053,15 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>Canonical joint-K4 (pos / macro)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Source run</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Local artifact</t>
         </is>
@@ -3082,10 +3087,15 @@
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="inlineStr">
         <is>
+          <t>0.800 / 0.841</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_audio_text_s1337_05b52c6b (commit 3caa208)</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30/audio_text/&lt;run&gt;/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json (recomputed from predictions)</t>
         </is>
@@ -3113,10 +3123,15 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_audio_text_s1337_05b52c6b (commit 3caa208)</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30/audio_text/&lt;run&gt;/fold_0/best_model/logreg_raw/metrics.json (recomputed from predictions)</t>
         </is>
@@ -3144,10 +3159,15 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_audio_text_s1337_05b52c6b (commit 3caa208)</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30/audio_text/&lt;run&gt;/fold_0/best_model/xgb_raw/metrics.json (recomputed from predictions)</t>
         </is>
@@ -3173,10 +3193,15 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="inlineStr">
         <is>
+          <t>0.522 / 0.683</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_audio_only_s1337_05b52c6b (commit 3caa208)</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30/audio_only/&lt;run&gt;/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json (recomputed from predictions)</t>
         </is>
@@ -3204,10 +3229,15 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_audio_only_s1337_05b52c6b (commit 3caa208)</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30/audio_only/&lt;run&gt;/fold_0/best_model/logreg_raw/metrics.json (recomputed from predictions)</t>
         </is>
@@ -3235,10 +3265,15 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_audio_only_s1337_05b52c6b (commit 3caa208)</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30/audio_only/&lt;run&gt;/fold_0/best_model/xgb_raw/metrics.json (recomputed from predictions)</t>
         </is>
@@ -3264,10 +3299,15 @@
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="inlineStr">
         <is>
+          <t>0.800 / 0.841</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_jointk4_audio_text_s1337_e3b0f1c3 (commit e3b0f1c)</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30_jointk4/audio_text/&lt;run&gt;/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json (recomputed from predictions)</t>
         </is>
@@ -3295,10 +3335,15 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_jointk4_audio_text_s1337_e3b0f1c3 (commit e3b0f1c)</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30_jointk4/audio_text/&lt;run&gt;/fold_0/best_model/logreg_raw/metrics.json (recomputed from predictions)</t>
         </is>
@@ -3326,10 +3371,15 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_jointk4_audio_text_s1337_e3b0f1c3 (commit e3b0f1c)</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30_jointk4/audio_text/&lt;run&gt;/fold_0/best_model/xgb_raw/metrics.json (recomputed from predictions)</t>
         </is>
@@ -3355,10 +3405,15 @@
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="inlineStr">
         <is>
+          <t>0.522 / 0.683</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_jointk4_audio_only_s1337_e3b0f1c3 (commit e3b0f1c)</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30_jointk4/audio_only/&lt;run&gt;/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json (recomputed from predictions)</t>
         </is>
@@ -3386,10 +3441,15 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_jointk4_audio_only_s1337_e3b0f1c3 (commit e3b0f1c)</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30_jointk4/audio_only/&lt;run&gt;/fold_0/best_model/logreg_raw/metrics.json (recomputed from predictions)</t>
         </is>
@@ -3417,10 +3477,15 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
           <t>daic_participant_p30_jointk4_audio_only_s1337_e3b0f1c3 (commit e3b0f1c)</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>output_model/experiments/daic_participant_packed30_jointk4/audio_only/&lt;run&gt;/fold_0/best_model/xgb_raw/metrics.json (recomputed from predictions)</t>
         </is>
@@ -3429,7 +3494,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Provenance sheet holds the full mapping (commit, job IDs incl. resubmits, eval view, aggregation, audits 44369722/44369723 GPFS PASSED + local evidence audit PASSED).</t>
+          <t>Canonical = preprocessed joint-K4 (2026-08-05 coverage validation; no head caches under this recipe). Provenance sheet holds the full mapping (commit, job IDs incl. resubmits, eval view, aggregation, audits 44369722/44369723 GPFS PASSED + local evidence audit PASSED).</t>
         </is>
       </c>
     </row>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -3021,7 +3021,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Qwen verdict = mean teacher-forced score margin per subject (INVALID counts as wrong; INVALID=0). Heads = logreg_raw / xgb_raw on hidden features, mean depressed probability &gt;= 0.5 per subject. Canonical joint-K4 has no head caches under this recipe (not run). Selected epochs: joint-K4 audio-only 5, audio+text 3; v1 audio-only 3, audio+text 2.</t>
+          <t>Qwen verdict = mean teacher-forced score margin per subject (INVALID counts as wrong; INVALID=0). Heads = logreg_raw / xgb_raw on hidden features, mean depressed probability &gt;= 0.5 per subject. Canonical heads = daic_coverage_heads_20260805_04f2e19 complete-coverage (c2_balanced) view. Selected epochs: joint-K4 audio-only 5, audio+text 3; v1 audio-only 3, audio+text 2.</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Canonical joint-K4 (pos / macro)</t>
+          <t>Canonical joint-K4 (pos / macro / AUROC)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>0.800 / 0.841</t>
+          <t>0.800 / 0.841 / n/a</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>0.765 / 0.816 / 0.918</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>0.643 / 0.746 / 0.883</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -3193,7 +3193,7 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>0.522 / 0.683</t>
+          <t>0.522 / 0.683 / n/a</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>0.571 / 0.659 / 0.823</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>0.364 / 0.585 / 0.781</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -3299,7 +3299,7 @@
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>0.800 / 0.841</t>
+          <t>0.800 / 0.841 / n/a</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>0.765 / 0.816 / 0.918</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>0.643 / 0.746 / 0.883</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -3405,7 +3405,7 @@
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>0.522 / 0.683</t>
+          <t>0.522 / 0.683 / n/a</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>0.571 / 0.659 / 0.823</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>not run</t>
+          <t>0.364 / 0.585 / 0.781</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Canonical = preprocessed joint-K4 (2026-08-05 coverage validation; no head caches under this recipe). Provenance sheet holds the full mapping (commit, job IDs incl. resubmits, eval view, aggregation, audits 44369722/44369723 GPFS PASSED + local evidence audit PASSED).</t>
+          <t>Canonical = preprocessed joint-K4 (Qwen: 2026-08-05 coverage validation; heads: daic_coverage_heads_20260805_04f2e19 c2_balanced, verified locally by recomputation). Provenance sheet holds the full mapping (commit, job IDs incl. resubmits, eval view, aggregation, audits 44369722/44369723 GPFS PASSED + local evidence audit PASSED).</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I186"/>
+  <dimension ref="A1:I190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="C183" s="14" t="inlineStr">
         <is>
-          <t>Joint-K4 Audio + Text</t>
+          <t>Canonical Audio + Text</t>
         </is>
       </c>
       <c r="D183" s="14" t="inlineStr">
@@ -11704,26 +11704,26 @@
         </is>
       </c>
       <c r="E183" s="15" t="n">
-        <v>0.7333</v>
+        <v>0.7647</v>
       </c>
       <c r="F183" s="16" t="inlineStr">
         <is>
-          <t>daic_participant_p30_jointk4_&lt;mod&gt;_s1337_e3b0f1c3 selected-epoch head fit (107 vectors, weights 1.0)</t>
+          <t>daic_coverage_heads_20260805_04f2e19 canonical checkpoints (audio_text=daic_main_k4_control_20260804_f26dd45, audio_only=daic_replicates_20ep_s1337_daic_audio_only_selposf1_tf)</t>
         </is>
       </c>
       <c r="G183" s="16" t="inlineStr">
         <is>
-          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, 617 bundles</t>
+          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, complete-coverage (c2_balanced) view</t>
         </is>
       </c>
       <c r="H183" s="16" t="inlineStr">
         <is>
-          <t>output_model/experiments/daic_participant_packed30_jointk4/&lt;modality&gt;/&lt;run&gt;/hidden_classifiers/audio_text/logreg_raw/</t>
+          <t>outputs/daic_coverage_heads/daic_coverage_heads_20260805_04f2e19/audio_text/classical/c2/logreg_raw/</t>
         </is>
       </c>
       <c r="I183" s="16" t="inlineStr">
         <is>
-          <t>matched to audited hidden-classifier outputs</t>
+          <t>recomputed from predictions_subject_level.jsonl (metrics match)</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="C184" s="14" t="inlineStr">
         <is>
-          <t>Joint-K4 Audio + Text</t>
+          <t>Canonical Audio + Text</t>
         </is>
       </c>
       <c r="D184" s="14" t="inlineStr">
@@ -11749,26 +11749,26 @@
         </is>
       </c>
       <c r="E184" s="15" t="n">
-        <v>0.7692</v>
+        <v>0.6429</v>
       </c>
       <c r="F184" s="16" t="inlineStr">
         <is>
-          <t>daic_participant_p30_jointk4_&lt;mod&gt;_s1337_e3b0f1c3 selected-epoch head fit (107 vectors, weights 1.0)</t>
+          <t>daic_coverage_heads_20260805_04f2e19 canonical checkpoints (audio_text=daic_main_k4_control_20260804_f26dd45, audio_only=daic_replicates_20ep_s1337_daic_audio_only_selposf1_tf)</t>
         </is>
       </c>
       <c r="G184" s="16" t="inlineStr">
         <is>
-          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, 617 bundles</t>
+          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, complete-coverage (c2_balanced) view</t>
         </is>
       </c>
       <c r="H184" s="16" t="inlineStr">
         <is>
-          <t>output_model/experiments/daic_participant_packed30_jointk4/&lt;modality&gt;/&lt;run&gt;/hidden_classifiers/audio_text/xgb_raw/</t>
+          <t>outputs/daic_coverage_heads/daic_coverage_heads_20260805_04f2e19/audio_text/classical/c2/xgb_raw/</t>
         </is>
       </c>
       <c r="I184" s="16" t="inlineStr">
         <is>
-          <t>matched to audited hidden-classifier outputs</t>
+          <t>recomputed from predictions_subject_level.jsonl (metrics match)</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C185" s="14" t="inlineStr">
         <is>
-          <t>Joint-K4 Audio only</t>
+          <t>Canonical Audio only</t>
         </is>
       </c>
       <c r="D185" s="14" t="inlineStr">
@@ -11794,26 +11794,26 @@
         </is>
       </c>
       <c r="E185" s="15" t="n">
-        <v>0.6471</v>
+        <v>0.5714</v>
       </c>
       <c r="F185" s="16" t="inlineStr">
         <is>
-          <t>daic_participant_p30_jointk4_&lt;mod&gt;_s1337_e3b0f1c3 selected-epoch head fit (107 vectors, weights 1.0)</t>
+          <t>daic_coverage_heads_20260805_04f2e19 canonical checkpoints (audio_text=daic_main_k4_control_20260804_f26dd45, audio_only=daic_replicates_20ep_s1337_daic_audio_only_selposf1_tf)</t>
         </is>
       </c>
       <c r="G185" s="16" t="inlineStr">
         <is>
-          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, 617 bundles</t>
+          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, complete-coverage (c2_balanced) view</t>
         </is>
       </c>
       <c r="H185" s="16" t="inlineStr">
         <is>
-          <t>output_model/experiments/daic_participant_packed30_jointk4/&lt;modality&gt;/&lt;run&gt;/hidden_classifiers/audio_only/logreg_raw/</t>
+          <t>outputs/daic_coverage_heads/daic_coverage_heads_20260805_04f2e19/audio_only/classical/c2/logreg_raw/</t>
         </is>
       </c>
       <c r="I185" s="16" t="inlineStr">
         <is>
-          <t>matched to audited hidden-classifier outputs</t>
+          <t>recomputed from predictions_subject_level.jsonl (metrics match)</t>
         </is>
       </c>
     </row>
@@ -11830,35 +11830,215 @@
       </c>
       <c r="C186" s="14" t="inlineStr">
         <is>
+          <t>Canonical Audio only</t>
+        </is>
+      </c>
+      <c r="D186" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost raw</t>
+        </is>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="F186" s="16" t="inlineStr">
+        <is>
+          <t>daic_coverage_heads_20260805_04f2e19 canonical checkpoints (audio_text=daic_main_k4_control_20260804_f26dd45, audio_only=daic_replicates_20ep_s1337_daic_audio_only_selposf1_tf)</t>
+        </is>
+      </c>
+      <c r="G186" s="16" t="inlineStr">
+        <is>
+          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, complete-coverage (c2_balanced) view</t>
+        </is>
+      </c>
+      <c r="H186" s="16" t="inlineStr">
+        <is>
+          <t>outputs/daic_coverage_heads/daic_coverage_heads_20260805_04f2e19/audio_only/classical/c2/xgb_raw/</t>
+        </is>
+      </c>
+      <c r="I186" s="16" t="inlineStr">
+        <is>
+          <t>recomputed from predictions_subject_level.jsonl (metrics match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="14" t="inlineStr">
+        <is>
+          <t>DAIC packed30 family</t>
+        </is>
+      </c>
+      <c r="B187" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C187" s="14" t="inlineStr">
+        <is>
+          <t>Joint-K4 Audio + Text</t>
+        </is>
+      </c>
+      <c r="D187" s="14" t="inlineStr">
+        <is>
+          <t>LogReg raw</t>
+        </is>
+      </c>
+      <c r="E187" s="15" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="F187" s="16" t="inlineStr">
+        <is>
+          <t>daic_participant_p30_jointk4_&lt;mod&gt;_s1337_e3b0f1c3 selected-epoch head fit (107 vectors, weights 1.0)</t>
+        </is>
+      </c>
+      <c r="G187" s="16" t="inlineStr">
+        <is>
+          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, 617 bundles</t>
+        </is>
+      </c>
+      <c r="H187" s="16" t="inlineStr">
+        <is>
+          <t>hidden_classifiers/audio_text/logreg_raw/</t>
+        </is>
+      </c>
+      <c r="I187" s="16" t="inlineStr">
+        <is>
+          <t>recomputed from predictions_subject_level.jsonl (metrics match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="14" t="inlineStr">
+        <is>
+          <t>DAIC packed30 family</t>
+        </is>
+      </c>
+      <c r="B188" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C188" s="14" t="inlineStr">
+        <is>
+          <t>Joint-K4 Audio + Text</t>
+        </is>
+      </c>
+      <c r="D188" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost raw</t>
+        </is>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.7692</v>
+      </c>
+      <c r="F188" s="16" t="inlineStr">
+        <is>
+          <t>daic_participant_p30_jointk4_&lt;mod&gt;_s1337_e3b0f1c3 selected-epoch head fit (107 vectors, weights 1.0)</t>
+        </is>
+      </c>
+      <c r="G188" s="16" t="inlineStr">
+        <is>
+          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, 617 bundles</t>
+        </is>
+      </c>
+      <c r="H188" s="16" t="inlineStr">
+        <is>
+          <t>hidden_classifiers/audio_text/xgb_raw/</t>
+        </is>
+      </c>
+      <c r="I188" s="16" t="inlineStr">
+        <is>
+          <t>recomputed from predictions_subject_level.jsonl (metrics match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="14" t="inlineStr">
+        <is>
+          <t>DAIC packed30 family</t>
+        </is>
+      </c>
+      <c r="B189" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C189" s="14" t="inlineStr">
+        <is>
           <t>Joint-K4 Audio only</t>
         </is>
       </c>
-      <c r="D186" s="14" t="inlineStr">
+      <c r="D189" s="14" t="inlineStr">
+        <is>
+          <t>LogReg raw</t>
+        </is>
+      </c>
+      <c r="E189" s="15" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="F189" s="16" t="inlineStr">
+        <is>
+          <t>daic_participant_p30_jointk4_&lt;mod&gt;_s1337_e3b0f1c3 selected-epoch head fit (107 vectors, weights 1.0)</t>
+        </is>
+      </c>
+      <c r="G189" s="16" t="inlineStr">
+        <is>
+          <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, 617 bundles</t>
+        </is>
+      </c>
+      <c r="H189" s="16" t="inlineStr">
+        <is>
+          <t>hidden_classifiers/audio_only/logreg_raw/</t>
+        </is>
+      </c>
+      <c r="I189" s="16" t="inlineStr">
+        <is>
+          <t>recomputed from predictions_subject_level.jsonl (metrics match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="14" t="inlineStr">
+        <is>
+          <t>DAIC packed30 family</t>
+        </is>
+      </c>
+      <c r="B190" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C190" s="14" t="inlineStr">
+        <is>
+          <t>Joint-K4 Audio only</t>
+        </is>
+      </c>
+      <c r="D190" s="14" t="inlineStr">
         <is>
           <t>XGBoost raw</t>
         </is>
       </c>
-      <c r="E186" s="15" t="n">
+      <c r="E190" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="F186" s="16" t="inlineStr">
+      <c r="F190" s="16" t="inlineStr">
         <is>
           <t>daic_participant_p30_jointk4_&lt;mod&gt;_s1337_e3b0f1c3 selected-epoch head fit (107 vectors, weights 1.0)</t>
         </is>
       </c>
-      <c r="G186" s="16" t="inlineStr">
+      <c r="G190" s="16" t="inlineStr">
         <is>
           <t>mean depressed probability &gt;= 0.5 per subject, 47 test subjects, 617 bundles</t>
         </is>
       </c>
-      <c r="H186" s="16" t="inlineStr">
-        <is>
-          <t>output_model/experiments/daic_participant_packed30_jointk4/&lt;modality&gt;/&lt;run&gt;/hidden_classifiers/audio_only/xgb_raw/</t>
-        </is>
-      </c>
-      <c r="I186" s="16" t="inlineStr">
-        <is>
-          <t>matched to audited hidden-classifier outputs</t>
+      <c r="H190" s="16" t="inlineStr">
+        <is>
+          <t>hidden_classifiers/audio_only/xgb_raw/</t>
+        </is>
+      </c>
+      <c r="I190" s="16" t="inlineStr">
+        <is>
+          <t>recomputed from predictions_subject_level.jsonl (metrics match)</t>
         </is>
       </c>
     </row>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -12,7 +12,8 @@
     <sheet name="EN Translation MacroF1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Merged vs Standalone MacroF1" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="DAIC Packed30 Family" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Provenance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Harmonized Campaign" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Provenance" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3514,7 +3515,686 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Harmonized Campaign (recipe harmonized_full_transcript_single30_allwindows_selmacrof1_tf_v1) — Macro-F1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Campaign harmonized_v1_prod_20260809T171705Z_d1e8130b (Issue #12 / PR #10); teacher-forced, binary-strict, best_model, seed 1337; 20-epoch cap, patience 3, macro-F1 selection; audio encoder frozen; no Optuna. Standalone aggregations: D3TEC/Androids pooled subject-level 5-fold; Turkish/CMDC 5-fold mean; DAIC fixed official test (47 subjects). First wave had two documented failure classes (NCCL watchdog on long final evals; standalone-eval KeyError), fixed in PRs #14/#16 and rerun under _r1 attempt names; retry registry retry_r1_jobs.tsv (148 jobs, all COMPLETED). Merged: five-dataset CV (holdout per fold, 5-fold mean) and final training on the DAIC protected official test only (daic_official_test_only), final epochs 2/4/5 (rounded median of CV-selected epochs). Optuna/Subject-OS not run -&gt; blank. All values recomputed 2026-08-10 from local artifacts; per-cell provenance on the Provenance sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Evaluation / Modality</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Standalone — Qwen (headline macro-F1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Evaluation / Modality</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>DAIC — Audio + Text</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.7432</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>DAIC — Audio only</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.519</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>DAIC — Text only</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7457</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CMDC — Audio + Text</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9614</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CMDC — Audio only</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0.9516</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.9225</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CMDC — Text only</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9683</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Turkish — Audio + Text</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6289</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6325</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Turkish — Audio only</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5209</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4271</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Turkish — Text only</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5234</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC — Audio + Text</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5585</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC — Audio only</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0.6649</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5404</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC — Text only</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5911</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview — Audio + Text</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.8656</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview — Audio only</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.8235</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview — Text only</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0.7317</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.8241000000000001</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Merged final — DAIC protected official test (n=47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Evaluation / Modality</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Merged Audio + Text (final, 2 epochs)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0.7631</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.7432</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.7432</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Merged Audio only (final, 4 epochs)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0.5554</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Merged Text only (final, 5 epochs)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0.7756</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.7157</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0.7552</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Merged five-dataset CV — mean of per-fold holdout macro-F1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Evaluation / Modality</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>DAIC — Audio + Text (merged CV)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.6634</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0.6835</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CMDC — Audio + Text (merged CV)</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0.9262</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0.9421</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0.9577</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Turkish — Audio + Text (merged CV)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0.494</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC — Audio + Text (merged CV)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0.5737</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview — Audio + Text (merged CV)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0.7842</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>DAIC — Audio only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0.5631</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>CMDC — Audio only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0.9366</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Turkish — Audio only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>0.4484</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC — Audio only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0.5925</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.5387</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview — Audio only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0.8564000000000001</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.8441</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>0.8531</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>DAIC — Text only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.7219</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.7168</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0.7093</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>CMDC — Text only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.9698</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>0.9405</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Turkish — Text only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.6684</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0.6288</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC — Text only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0.6528</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.5733</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0.5622</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview — Text only (merged CV)</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.7714</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0.8079</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12042,6 +12722,4461 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B191" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C191" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D191" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E191" s="15" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="F191" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_audio_text (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G191" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; fixed official test (47 subjects)</t>
+        </is>
+      </c>
+      <c r="H191" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B192" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C192" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D192" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0.7432</v>
+      </c>
+      <c r="F192" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G192" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H192" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I192" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B193" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C193" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D193" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E193" s="15" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="F193" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G193" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H193" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I193" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B194" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C194" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D194" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E194" s="15" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="F194" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_audio_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G194" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; fixed official test (47 subjects)</t>
+        </is>
+      </c>
+      <c r="H194" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I194" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B195" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C195" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D195" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E195" s="15" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G195" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H195" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I195" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B196" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C196" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D196" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E196" s="15" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="F196" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G196" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H196" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I196" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B197" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C197" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D197" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E197" s="15" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="F197" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_text_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G197" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; fixed official test (47 subjects)</t>
+        </is>
+      </c>
+      <c r="H197" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I197" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B198" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C198" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D198" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="F198" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G198" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H198" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I198" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B199" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C199" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D199" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E199" s="15" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="F199" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G199" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H199" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B200" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C200" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D200" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E200" s="15" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F200" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_audio_text (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G200" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; 5-fold mean</t>
+        </is>
+      </c>
+      <c r="H200" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I200" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B201" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C201" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D201" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E201" s="15" t="n">
+        <v>0.9614</v>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G201" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H201" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I201" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B202" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C202" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D202" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E202" s="15" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F202" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G202" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H202" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I202" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B203" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C203" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D203" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E203" s="15" t="n">
+        <v>0.9516</v>
+      </c>
+      <c r="F203" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_audio_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G203" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; 5-fold mean</t>
+        </is>
+      </c>
+      <c r="H203" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I203" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B204" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C204" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D204" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E204" s="15" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G204" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H204" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I204" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B205" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C205" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D205" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E205" s="15" t="n">
+        <v>0.9225</v>
+      </c>
+      <c r="F205" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G205" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H205" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I205" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B206" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C206" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D206" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E206" s="15" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="F206" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_text_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G206" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; 5-fold mean</t>
+        </is>
+      </c>
+      <c r="H206" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I206" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B207" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C207" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D207" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E207" s="15" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G207" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H207" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I207" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B208" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C208" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D208" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E208" s="15" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="F208" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G208" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H208" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I208" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B209" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C209" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D209" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E209" s="15" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_audio_text (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G209" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; 5-fold mean</t>
+        </is>
+      </c>
+      <c r="H209" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I209" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B210" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C210" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D210" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E210" s="15" t="n">
+        <v>0.6289</v>
+      </c>
+      <c r="F210" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G210" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H210" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I210" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B211" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C211" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D211" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E211" s="15" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="F211" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G211" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H211" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I211" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B212" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C212" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D212" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E212" s="15" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_audio_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G212" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; 5-fold mean</t>
+        </is>
+      </c>
+      <c r="H212" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I212" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B213" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C213" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D213" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E213" s="15" t="n">
+        <v>0.5209</v>
+      </c>
+      <c r="F213" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G213" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H213" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I213" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B214" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C214" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D214" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E214" s="15" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="F214" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G214" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H214" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I214" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B215" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C215" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D215" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E215" s="15" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="F215" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_text_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G215" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; 5-fold mean</t>
+        </is>
+      </c>
+      <c r="H215" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I215" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B216" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C216" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D216" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E216" s="15" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="F216" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G216" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H216" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I216" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B217" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C217" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D217" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E217" s="15" t="n">
+        <v>0.5234</v>
+      </c>
+      <c r="F217" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G217" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H217" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I217" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B218" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C218" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D218" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E218" s="15" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="F218" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_audio_text (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G218" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; pooled subject-level 5-fold</t>
+        </is>
+      </c>
+      <c r="H218" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I218" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B219" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C219" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D219" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E219" s="15" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="F219" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G219" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H219" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I219" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B220" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D220" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E220" s="15" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="F220" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G220" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H220" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I220" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B221" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C221" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D221" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E221" s="15" t="n">
+        <v>0.6649</v>
+      </c>
+      <c r="F221" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_audio_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G221" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; pooled subject-level 5-fold</t>
+        </is>
+      </c>
+      <c r="H221" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I221" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B222" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C222" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D222" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E222" s="15" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="F222" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G222" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H222" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I222" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B223" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C223" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D223" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E223" s="15" t="n">
+        <v>0.5404</v>
+      </c>
+      <c r="F223" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G223" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H223" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I223" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B224" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C224" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D224" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E224" s="15" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="F224" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_text_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G224" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; pooled subject-level 5-fold</t>
+        </is>
+      </c>
+      <c r="H224" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I224" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B225" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C225" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D225" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E225" s="15" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="F225" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G225" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H225" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I225" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B226" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C226" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D226" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E226" s="15" t="n">
+        <v>0.5911</v>
+      </c>
+      <c r="F226" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G226" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H226" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I226" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B227" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C227" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D227" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E227" s="15" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="F227" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_audio_text (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G227" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; pooled subject-level 5-fold</t>
+        </is>
+      </c>
+      <c r="H227" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I227" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B228" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C228" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D228" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E228" s="15" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="F228" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G228" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H228" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I228" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B229" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C229" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D229" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E229" s="15" t="n">
+        <v>0.8656</v>
+      </c>
+      <c r="F229" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G229" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H229" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I229" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B230" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C230" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D230" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E230" s="15" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="F230" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_audio_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G230" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; pooled subject-level 5-fold</t>
+        </is>
+      </c>
+      <c r="H230" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I230" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B231" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C231" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D231" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E231" s="15" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="F231" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G231" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H231" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I231" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B232" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C232" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D232" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E232" s="15" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="F232" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G232" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H232" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I232" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized standalone</t>
+        </is>
+      </c>
+      <c r="B233" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C233" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D233" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E233" s="15" t="n">
+        <v>0.7317</v>
+      </c>
+      <c r="F233" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_text_only (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; first-wave failures replaced by _r1 retries, retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="G233" s="16" t="inlineStr">
+        <is>
+          <t>original_teacher_forced, headline/binary_strict, best_model; pooled subject-level 5-fold</t>
+        </is>
+      </c>
+      <c r="H233" s="16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/&lt;modality&gt;/&lt;dataset&gt;/&lt;run&gt;[_r1]/fold_&lt;n&gt;/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I233" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local predictions/metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B234" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C234" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D234" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E234" s="15" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="F234" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G234" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, logreg_raw</t>
+        </is>
+      </c>
+      <c r="H234" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I234" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized heads</t>
+        </is>
+      </c>
+      <c r="B235" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C235" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D235" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E235" s="15" t="n">
+        <v>0.8241000000000001</v>
+      </c>
+      <c r="F235" s="16" t="inlineStr">
+        <is>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+        </is>
+      </c>
+      <c r="G235" s="16" t="inlineStr">
+        <is>
+          <t>5-fold mean subject-level, xgb_raw</t>
+        </is>
+      </c>
+      <c r="H235" s="16" t="inlineStr">
+        <is>
+          <t>outputs/hidden_classifiers/harmonized_v1/&lt;dataset&gt;/&lt;run&gt;_r1/fold_&lt;n&gt;/{logreg_raw,xgb_raw}/metrics.json</t>
+        </is>
+      </c>
+      <c r="I235" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B236" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C236" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D236" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E236" s="15" t="n">
+        <v>0.7631</v>
+      </c>
+      <c r="F236" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text, final stage 2 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G236" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H236" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I236" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B237" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C237" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D237" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E237" s="15" t="n">
+        <v>0.7432</v>
+      </c>
+      <c r="F237" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text, final stage 2 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G237" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H237" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I237" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B238" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C238" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D238" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E238" s="15" t="n">
+        <v>0.7432</v>
+      </c>
+      <c r="F238" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text, final stage 2 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G238" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H238" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I238" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B239" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C239" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D239" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E239" s="15" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="F239" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G239" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H239" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I239" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B240" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C240" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D240" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E240" s="15" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="F240" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G240" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H240" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I240" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B241" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C241" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D241" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E241" s="15" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="F241" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G241" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H241" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I241" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B242" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C242" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D242" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E242" s="15" t="n">
+        <v>0.9421</v>
+      </c>
+      <c r="F242" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G242" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H242" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I242" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B243" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C243" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D243" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E243" s="15" t="n">
+        <v>0.9262</v>
+      </c>
+      <c r="F243" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G243" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H243" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I243" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B244" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C244" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D244" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E244" s="15" t="n">
+        <v>0.9577</v>
+      </c>
+      <c r="F244" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G244" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H244" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I244" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B245" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C245" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D245" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E245" s="15" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="F245" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G245" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H245" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I245" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B246" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C246" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D246" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E246" s="15" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="F246" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G246" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H246" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I246" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B247" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C247" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D247" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E247" s="15" t="n">
+        <v>0.5737</v>
+      </c>
+      <c r="F247" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G247" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H247" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I247" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B248" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C248" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D248" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E248" s="15" t="n">
+        <v>0.6634</v>
+      </c>
+      <c r="F248" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G248" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H248" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I248" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B249" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C249" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D249" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E249" s="15" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="F249" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G249" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H249" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I249" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B250" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C250" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D250" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E250" s="15" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="F250" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G250" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H250" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I250" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B251" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C251" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D251" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E251" s="15" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="F251" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G251" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H251" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I251" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B252" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C252" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D252" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E252" s="15" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="F252" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G252" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H252" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I252" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B253" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C253" s="14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D253" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E253" s="15" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="F253" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio + Text CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G253" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H253" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_text/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I253" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B254" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C254" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D254" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E254" s="15" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="F254" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only, final stage 4 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G254" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H254" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I254" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B255" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C255" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D255" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E255" s="15" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="F255" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only, final stage 4 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G255" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H255" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I255" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B256" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C256" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D256" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E256" s="15" t="n">
+        <v>0.5554</v>
+      </c>
+      <c r="F256" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only, final stage 4 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G256" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H256" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I256" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B257" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C257" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D257" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E257" s="15" t="n">
+        <v>0.8441</v>
+      </c>
+      <c r="F257" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G257" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H257" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I257" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B258" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C258" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D258" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E258" s="15" t="n">
+        <v>0.8564000000000001</v>
+      </c>
+      <c r="F258" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G258" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H258" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I258" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B259" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C259" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D259" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E259" s="15" t="n">
+        <v>0.8531</v>
+      </c>
+      <c r="F259" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G259" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H259" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I259" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B260" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C260" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D260" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E260" s="15" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="F260" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G260" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H260" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I260" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B261" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C261" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D261" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E261" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F261" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G261" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H261" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I261" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B262" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C262" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D262" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E262" s="15" t="n">
+        <v>0.9366</v>
+      </c>
+      <c r="F262" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G262" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H262" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I262" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B263" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C263" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D263" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E263" s="15" t="n">
+        <v>0.5387</v>
+      </c>
+      <c r="F263" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G263" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H263" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I263" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B264" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C264" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D264" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E264" s="15" t="n">
+        <v>0.5925</v>
+      </c>
+      <c r="F264" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G264" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H264" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I264" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B265" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C265" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D265" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E265" s="15" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="F265" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G265" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H265" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I265" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B266" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C266" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D266" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E266" s="15" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="F266" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G266" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H266" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I266" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B267" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C267" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D267" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E267" s="15" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="F267" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G267" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H267" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I267" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B268" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C268" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D268" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E268" s="15" t="n">
+        <v>0.5631</v>
+      </c>
+      <c r="F268" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G268" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H268" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I268" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B269" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C269" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D269" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E269" s="15" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="F269" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G269" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H269" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I269" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B270" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C270" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D270" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E270" s="15" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="F270" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G270" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H270" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I270" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B271" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C271" s="14" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D271" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E271" s="15" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="F271" s="16" t="inlineStr">
+        <is>
+          <t>merged Audio only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G271" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H271" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/audio_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I271" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B272" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C272" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D272" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E272" s="15" t="n">
+        <v>0.7756</v>
+      </c>
+      <c r="F272" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only, final stage 5 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G272" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H272" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I272" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B273" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C273" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D273" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E273" s="15" t="n">
+        <v>0.7157</v>
+      </c>
+      <c r="F273" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only, final stage 5 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G273" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H273" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I273" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged final</t>
+        </is>
+      </c>
+      <c r="B274" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C274" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D274" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E274" s="15" t="n">
+        <v>0.7552</v>
+      </c>
+      <c r="F274" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only, final stage 5 epochs, run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G274" s="16" t="inlineStr">
+        <is>
+          <t>protected official holdout (47 subjects), teacher-forced</t>
+        </is>
+      </c>
+      <c r="H274" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/final/fold_0/postprocess_complete.json</t>
+        </is>
+      </c>
+      <c r="I274" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local postprocess summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B275" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C275" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D275" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E275" s="15" t="n">
+        <v>0.7714</v>
+      </c>
+      <c r="F275" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G275" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H275" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I275" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B276" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C276" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D276" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E276" s="15" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="F276" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G276" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H276" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I276" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B277" s="14" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="C277" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D277" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E277" s="15" t="n">
+        <v>0.8079</v>
+      </c>
+      <c r="F277" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G277" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H277" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I277" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B278" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C278" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D278" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E278" s="15" t="n">
+        <v>0.9698</v>
+      </c>
+      <c r="F278" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G278" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H278" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I278" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B279" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C279" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D279" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E279" s="15" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="F279" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G279" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H279" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I279" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B280" s="14" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="C280" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D280" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E280" s="15" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="F280" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G280" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H280" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I280" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B281" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C281" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D281" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E281" s="15" t="n">
+        <v>0.5733</v>
+      </c>
+      <c r="F281" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G281" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H281" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I281" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B282" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C282" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D282" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E282" s="15" t="n">
+        <v>0.6528</v>
+      </c>
+      <c r="F282" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G282" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H282" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I282" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B283" s="14" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="C283" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D283" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E283" s="15" t="n">
+        <v>0.5622</v>
+      </c>
+      <c r="F283" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G283" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H283" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I283" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B284" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C284" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D284" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E284" s="15" t="n">
+        <v>0.7168</v>
+      </c>
+      <c r="F284" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G284" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H284" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I284" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B285" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C285" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D285" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E285" s="15" t="n">
+        <v>0.7219</v>
+      </c>
+      <c r="F285" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G285" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H285" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I285" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B286" s="14" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C286" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D286" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E286" s="15" t="n">
+        <v>0.7093</v>
+      </c>
+      <c r="F286" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G286" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H286" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I286" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B287" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C287" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D287" s="14" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E287" s="15" t="n">
+        <v>0.6684</v>
+      </c>
+      <c r="F287" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G287" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H287" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I287" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B288" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C288" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D288" s="14" t="inlineStr">
+        <is>
+          <t>Fine-tuned Qwen</t>
+        </is>
+      </c>
+      <c r="E288" s="15" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="F288" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G288" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H288" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I288" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="14" t="inlineStr">
+        <is>
+          <t>Harmonized merged CV</t>
+        </is>
+      </c>
+      <c r="B289" s="14" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C289" s="14" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D289" s="14" t="inlineStr">
+        <is>
+          <t>XGBoost fixed</t>
+        </is>
+      </c>
+      <c r="E289" s="15" t="n">
+        <v>0.6288</v>
+      </c>
+      <c r="F289" s="16" t="inlineStr">
+        <is>
+          <t>merged Text only CV run harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b</t>
+        </is>
+      </c>
+      <c r="G289" s="16" t="inlineStr">
+        <is>
+          <t>mean of per-fold holdout macro-F1, 5 folds, teacher-forced</t>
+        </is>
+      </c>
+      <c r="H289" s="16" t="inlineStr">
+        <is>
+          <t>outputs/symmetric_merged/harmonized_v1/text_only/harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b/cv/fold_*/postprocess_complete.json + heads/*/metrics_by_dataset.json</t>
+        </is>
+      </c>
+      <c r="I289" s="16" t="inlineStr">
+        <is>
+          <t>recomputed 2026-08-10 from local fold summaries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -12793,7 +12793,7 @@
       </c>
       <c r="F192" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G192" s="16" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="F193" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G193" s="16" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="F195" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G195" s="16" t="inlineStr">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="F196" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G196" s="16" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="F198" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G198" s="16" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F199" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_daic_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G199" s="16" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="F201" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G201" s="16" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="F202" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G202" s="16" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="F204" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G204" s="16" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="F205" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G205" s="16" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F207" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G207" s="16" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="F208" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_cmdc_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G208" s="16" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G210" s="16" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G211" s="16" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="F213" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G213" s="16" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="F214" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G214" s="16" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="F216" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G216" s="16" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="F217" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_turkish_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G217" s="16" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="F219" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G219" s="16" t="inlineStr">
@@ -14053,7 +14053,7 @@
       </c>
       <c r="F220" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G220" s="16" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F222" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G222" s="16" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="F223" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G223" s="16" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="F225" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G225" s="16" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F226" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_d3tec_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G226" s="16" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F228" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G228" s="16" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="F229" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_text (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_audio_text (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G229" s="16" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="F231" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G231" s="16" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="F232" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_audio_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_audio_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G232" s="16" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="F234" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G234" s="16" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="F235" s="16" t="inlineStr">
         <is>
-          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_text_only (best-model hidden features)</t>
+          <t>harmonized_v1_harmonized_v1_prod_20260809T171705Z_d1e8130b_androids_interview_text_only (best-model hidden features, retry _r1 feature dirs)</t>
         </is>
       </c>
       <c r="G235" s="16" t="inlineStr">

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -13,7 +13,8 @@
     <sheet name="EN vs Native MacroF1" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Merged vs Standalone MacroF1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="DAIC Packed30 Family" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Provenance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gemma 4 DAIC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Provenance" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5903,7 +5904,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gemma 4 vs Qwen — DAIC official test (seed 1337, fold 0, strict teacher-forced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Gemma 4: google/gemma-4-12B-it revision 707f0a3b8a3c…, BF16 LoRA (288 decoder modules, rank 16/alpha 32), SDPA, gradient checkpointing, batch 1 x 32 accum x 4 GPUs. Campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae; source a6749b05 (clean main); PR #31; same manifest/split as the Qwen harmonized campaign (72e2dd204b91…/441333e0c888…). Evaluation: original_teacher_forced, harmonized_all_windows_full_coverage, subject mean-score, headline/binary_strict, INVALID counts as wrong (INVALID=0). Qwen column = canonical harmonized _r1 DAIC rows. One seed each — differences are observations, not variance estimates. All values recomputed locally from predictions_subject_level.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Positive-F1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Run / attempt / jobs</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Local evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7631048387096775</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.6875000000000001</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2; attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805; train 44518086 eval 44518087 (COMPLETED 0:0); selected epoch 3</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Qwen (harmonized _r1)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>harmonized_v1_…_daic_audio_text_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/audio_text/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only; attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2; train 44517565 eval 44517566 (COMPLETED 0:0); selected epoch n/a</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Qwen (harmonized _r1)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>harmonized_v1_…_daic_audio_only_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/audio_only/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only; attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3; train 44517484 eval 44517485 (COMPLETED 0:0); selected epoch 1</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Qwen (harmonized _r1)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>harmonized_v1_…_daic_text_only_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/text_only/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Positive-F1/accuracy/precision/recall are shown for Gemma only; the Qwen harmonized rows in the workbook carry macro-F1 (STANDALONE_QWEN) and the same binary-strict headline semantics (values: DAIC audio+text 0.7353, audio-only 0.5392, text-only 0.7353). audio_only Gemma predicted Non-depressed for all 47 subjects (degenerate but valid; run and evidence are sound). No winner is selected from test results.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14206,6 +14503,687 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B186" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C186" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D186" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 macro-F1</t>
+        </is>
+      </c>
+      <c r="E186" s="16" t="n">
+        <v>0.7631048387096775</v>
+      </c>
+      <c r="F186" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G186" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H186" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I186" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B187" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C187" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D187" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 positive-F1</t>
+        </is>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>0.6875000000000001</v>
+      </c>
+      <c r="F187" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G187" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H187" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I187" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B188" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C188" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D188" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 accuracy</t>
+        </is>
+      </c>
+      <c r="E188" s="16" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F188" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G188" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H188" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I188" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B189" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C189" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D189" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 confusion matrix</t>
+        </is>
+      </c>
+      <c r="E189" s="15" t="inlineStr">
+        <is>
+          <t>[[26, 7], [3, 11]]</t>
+        </is>
+      </c>
+      <c r="F189" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G189" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H189" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+        </is>
+      </c>
+      <c r="I189" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B190" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C190" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D190" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 invalid count</t>
+        </is>
+      </c>
+      <c r="E190" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G190" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H190" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+      <c r="I190" s="17" t="inlineStr">
+        <is>
+          <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B191" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C191" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D191" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 macro-F1</t>
+        </is>
+      </c>
+      <c r="E191" s="16" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="F191" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G191" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H191" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I191" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 positive-F1</t>
+        </is>
+      </c>
+      <c r="E192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G192" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H192" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I192" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B193" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C193" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D193" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 accuracy</t>
+        </is>
+      </c>
+      <c r="E193" s="16" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="F193" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G193" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H193" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I193" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 confusion matrix</t>
+        </is>
+      </c>
+      <c r="E194" s="15" t="inlineStr">
+        <is>
+          <t>[[33, 0], [14, 0]]</t>
+        </is>
+      </c>
+      <c r="F194" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G194" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H194" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+        </is>
+      </c>
+      <c r="I194" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B195" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C195" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D195" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 invalid count</t>
+        </is>
+      </c>
+      <c r="E195" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G195" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H195" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+      <c r="I195" s="17" t="inlineStr">
+        <is>
+          <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B196" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C196" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D196" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 macro-F1</t>
+        </is>
+      </c>
+      <c r="E196" s="16" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="F196" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G196" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H196" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I196" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B197" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C197" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D197" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 positive-F1</t>
+        </is>
+      </c>
+      <c r="E197" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F197" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G197" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H197" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I197" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B198" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C198" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 accuracy</t>
+        </is>
+      </c>
+      <c r="E198" s="16" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F198" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G198" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H198" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I198" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B199" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C199" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D199" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 confusion matrix</t>
+        </is>
+      </c>
+      <c r="E199" s="15" t="inlineStr">
+        <is>
+          <t>[[27, 6], [4, 10]]</t>
+        </is>
+      </c>
+      <c r="F199" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G199" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H199" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+        </is>
+      </c>
+      <c r="I199" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B200" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C200" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 invalid count</t>
+        </is>
+      </c>
+      <c r="E200" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G200" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H200" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+      <c r="I200" s="17" t="inlineStr">
+        <is>
+          <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -6007,7 +6007,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2; attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805; train 44518086 eval 44518087 (COMPLETED 0:0); selected epoch 3</t>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2; attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805; train 44518086 eval 44518087 (COMPLETED 0:0); selected epoch 3; first attempt 20260812T020449Z-gemma4_daic_audio_text_seed1337-cca3f4ae-5704f1f7 FAILED (train 44517567 CUDA OOM / eval 44517568 CANCELLED); superseded by this retry</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only; attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2; train 44517565 eval 44517566 (COMPLETED 0:0); selected epoch n/a</t>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only; attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2; train 44517565 eval 44517566 (COMPLETED 0:0); selected epoch 1</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="F186" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G186" s="17" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="F187" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G187" s="17" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="F188" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G188" s="17" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F189" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G189" s="17" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="F190" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G190" s="17" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="F191" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G191" s="17" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="F192" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G192" s="17" t="inlineStr">
@@ -14846,7 +14846,7 @@
       </c>
       <c r="F193" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G193" s="17" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="F194" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G194" s="17" t="inlineStr">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="F195" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G195" s="17" t="inlineStr">

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -5904,7 +5904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Gemma 4</t>
+          <t>Gemma 4 teacher-forced head</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -6024,169 +6024,391 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Qwen (harmonized _r1)</t>
+          <t>Gemma 4 LogReg raw hidden head</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.7353</v>
-      </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
+        <v>0.7898658718330849</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.8085106382978723</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>harmonized_v1_…_daic_audio_text_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+          <t>run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412; attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728; extract 44538980 heads 44538981 (COMPLETED 0:0); backend gemma4_hidden_logreg_raw; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0 / heads CANCELLED, wrapper race fixed in PR #45)</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1/audio_text/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.7834101382488479</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7096774193548386</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8085106382978723</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412; attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728; extract 44538980 heads 44538981 (COMPLETED 0:0); backend gemma4_hidden_xgb_raw; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0 / heads CANCELLED, wrapper race fixed in PR #45)</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Qwen harmonized _r1 reference</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>harmonized_v1_…_daic_audio_text_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/audio_text/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>Audio only</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Gemma 4</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4 teacher-forced head</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
         <v>0.4125</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E10" s="5" t="n">
         <v>0.7021276595744681</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only; attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2; train 44517565 eval 44517566 (COMPLETED 0:0); selected epoch 1</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Qwen (harmonized _r1)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0.5392</v>
-      </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>harmonized_v1_…_daic_audio_only_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1/audio_only/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Gemma 4</t>
+          <t>Gemma 4 LogReg raw hidden head</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.7552083333333333</v>
+        <v>0.6258420085731782</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only; attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3; train 44517484 eval 44517485 (COMPLETED 0:0); selected epoch 1</t>
+          <t>run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412; attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d; extract 44538982 heads 44538983 (COMPLETED 0:0); backend gemma4_hidden_logreg_raw; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0 / heads CANCELLED, wrapper race fixed in PR #45)</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412; attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d; extract 44538982 heads 44538983 (COMPLETED 0:0); backend gemma4_hidden_xgb_raw; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0 / heads CANCELLED, wrapper race fixed in PR #45)</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Qwen harmonized _r1 reference</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>harmonized_v1_…_daic_audio_only_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/audio_only/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Qwen (harmonized _r1)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4 teacher-forced head</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only; attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3; train 44517484 eval 44517485 (COMPLETED 0:0); selected epoch 1</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.7446808510638298</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412; attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58; extract 44538984 heads 44538985 (COMPLETED 0:0); backend gemma4_hidden_logreg_raw; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0 / heads CANCELLED, wrapper race fixed in PR #45)</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.6948051948051948</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.7446808510638298</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412; attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58; extract 44538984 heads 44538985 (COMPLETED 0:0); backend gemma4_hidden_xgb_raw; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0 / heads CANCELLED, wrapper race fixed in PR #45)</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Qwen harmonized _r1 reference</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>0.7353</v>
       </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>harmonized_v1_…_daic_text_only_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>output_model/harmonized_v1/text_only/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Positive-F1/accuracy/precision/recall are shown for Gemma only; the Qwen harmonized rows in the workbook carry macro-F1 (STANDALONE_QWEN) and the same binary-strict headline semantics (values: DAIC audio+text 0.7353, audio-only 0.5392, text-only 0.7353). audio_only Gemma predicted Non-depressed for all 47 subjects (degenerate but valid; run and evidence are sound). No winner is selected from test results.</t>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Fixed heads: final prompt-token hidden state (float32, 3840) from each Gemma 4 best_model; fit on the saved 107 official training subjects only (audio modes: all packed30 chunks, inverse-chunk weights; text: one vector per subject); test = official 47 subjects, mean depressed probability over chunks at &gt;= 0.5. LogReg: StandardScaler + balanced liblinear C=1.0 max_iter=5000; XGBoost: 300 trees lr 0.03 depth 2 min_child_weight 5 subsample 0.8 colsample 0.25 alpha 1.0 lambda 10.0 hist n_jobs=1; both seed 1337, sklearn 1.7.0 / xgboost 2.1.4. One seed each — differences are observations, not variance estimates. No winner is selected from test results.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -6200,7 +6422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:I236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14743,35 +14965,35 @@
       </c>
       <c r="C191" s="15" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D191" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 macro-F1</t>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E191" s="16" t="n">
-        <v>0.4125</v>
+        <v>0.7898658718330849</v>
       </c>
       <c r="F191" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
         </is>
       </c>
       <c r="G191" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H191" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I191" s="17" t="inlineStr">
         <is>
-          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+          <t>recomputed locally by verify-local (matches metrics JSON); REPORTABLE</t>
         </is>
       </c>
     </row>
@@ -14788,35 +15010,35 @@
       </c>
       <c r="C192" s="15" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 positive-F1</t>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E192" s="16" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F192" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
         </is>
       </c>
       <c r="G192" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H192" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I192" s="17" t="inlineStr">
         <is>
-          <t>recomputed locally from predictions (matches metrics JSON)</t>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
         </is>
       </c>
     </row>
@@ -14833,35 +15055,35 @@
       </c>
       <c r="C193" s="15" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D193" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 accuracy</t>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E193" s="16" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="F193" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
         </is>
       </c>
       <c r="G193" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H193" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I193" s="17" t="inlineStr">
         <is>
-          <t>recomputed locally from predictions (matches metrics JSON)</t>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
         </is>
       </c>
     </row>
@@ -14878,37 +15100,35 @@
       </c>
       <c r="C194" s="15" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D194" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 confusion matrix</t>
-        </is>
-      </c>
-      <c r="E194" s="15" t="inlineStr">
-        <is>
-          <t>[[33, 0], [14, 0]]</t>
-        </is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E194" s="16" t="n">
+        <v>0.631578947368421</v>
       </c>
       <c r="F194" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
         </is>
       </c>
       <c r="G194" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H194" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I194" s="17" t="inlineStr">
         <is>
-          <t>recomputed locally from predictions (matches metrics JSON)</t>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
         </is>
       </c>
     </row>
@@ -14925,35 +15145,35 @@
       </c>
       <c r="C195" s="15" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D195" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 invalid count</t>
-        </is>
-      </c>
-      <c r="E195" s="15" t="n">
-        <v>0</v>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E195" s="16" t="n">
+        <v>0.8571428571428571</v>
       </c>
       <c r="F195" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
         </is>
       </c>
       <c r="G195" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H195" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I195" s="17" t="inlineStr">
         <is>
-          <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
         </is>
       </c>
     </row>
@@ -14970,35 +15190,37 @@
       </c>
       <c r="C196" s="15" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D196" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 macro-F1</t>
-        </is>
-      </c>
-      <c r="E196" s="16" t="n">
-        <v>0.7552083333333333</v>
+          <t>Gemma 4 LogReg raw hidden head confusion matrix</t>
+        </is>
+      </c>
+      <c r="E196" s="15" t="inlineStr">
+        <is>
+          <t>[[26, 7], [2, 12]]</t>
+        </is>
       </c>
       <c r="F196" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
         </is>
       </c>
       <c r="G196" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H196" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json</t>
         </is>
       </c>
       <c r="I196" s="17" t="inlineStr">
         <is>
-          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
         </is>
       </c>
     </row>
@@ -15015,35 +15237,35 @@
       </c>
       <c r="C197" s="15" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D197" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 positive-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E197" s="16" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7834101382488479</v>
       </c>
       <c r="F197" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
         </is>
       </c>
       <c r="G197" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H197" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I197" s="17" t="inlineStr">
         <is>
-          <t>recomputed locally from predictions (matches metrics JSON)</t>
+          <t>recomputed locally by verify-local (matches metrics JSON); REPORTABLE</t>
         </is>
       </c>
     </row>
@@ -15060,35 +15282,35 @@
       </c>
       <c r="C198" s="15" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D198" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 accuracy</t>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E198" s="16" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.7096774193548386</v>
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
         </is>
       </c>
       <c r="G198" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H198" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I198" s="17" t="inlineStr">
         <is>
-          <t>recomputed locally from predictions (matches metrics JSON)</t>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
         </is>
       </c>
     </row>
@@ -15105,37 +15327,35 @@
       </c>
       <c r="C199" s="15" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D199" s="15" t="inlineStr">
         <is>
-          <t>Gemma 4 confusion matrix</t>
-        </is>
-      </c>
-      <c r="E199" s="15" t="inlineStr">
-        <is>
-          <t>[[27, 6], [4, 10]]</t>
-        </is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="n">
+        <v>0.8085106382978723</v>
       </c>
       <c r="F199" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
         </is>
       </c>
       <c r="G199" s="17" t="inlineStr">
         <is>
-          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
         </is>
       </c>
       <c r="H199" s="17" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I199" s="17" t="inlineStr">
         <is>
-          <t>recomputed locally from predictions (matches metrics JSON)</t>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
         </is>
       </c>
     </row>
@@ -15152,35 +15372,1669 @@
       </c>
       <c r="C200" s="15" t="inlineStr">
         <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E200" s="16" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="F200" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G200" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H200" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I200" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B201" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C201" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D201" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="F201" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G201" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H201" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I201" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B202" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C202" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head confusion matrix</t>
+        </is>
+      </c>
+      <c r="E202" s="15" t="inlineStr">
+        <is>
+          <t>[[27, 6], [3, 11]]</t>
+        </is>
+      </c>
+      <c r="F202" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155659Z-gemma4_daic_audio_text_fixed_heads_20260812t155635z_799cc412-799cc412-5ad76728, source 799cc412 (clean main), PR #46, jobs 44538980/44538981 (COMPLETED 0:0), parent attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153613Z-gemma4_daic_audio_text_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-a739f168 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G202" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H202" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_text/daic/gemma4_daic_audio_text_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json</t>
+        </is>
+      </c>
+      <c r="I202" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B203" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C203" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D203" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 macro-F1</t>
+        </is>
+      </c>
+      <c r="E203" s="16" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="F203" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G203" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H203" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I203" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B204" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C204" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D204" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 positive-F1</t>
+        </is>
+      </c>
+      <c r="E204" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G204" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H204" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I204" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B205" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C205" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D205" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 accuracy</t>
+        </is>
+      </c>
+      <c r="E205" s="16" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="F205" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G205" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H205" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I205" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B206" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C206" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 confusion matrix</t>
+        </is>
+      </c>
+      <c r="E206" s="15" t="inlineStr">
+        <is>
+          <t>[[33, 0], [14, 0]]</t>
+        </is>
+      </c>
+      <c r="F206" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G206" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H206" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+        </is>
+      </c>
+      <c r="I206" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B207" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C207" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D207" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 invalid count</t>
+        </is>
+      </c>
+      <c r="E207" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G207" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H207" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+      <c r="I207" s="17" t="inlineStr">
+        <is>
+          <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B208" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C208" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D208" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E208" s="16" t="n">
+        <v>0.6258420085731782</v>
+      </c>
+      <c r="F208" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G208" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H208" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I208" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON); REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B209" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C209" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D209" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E209" s="16" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="F209" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G209" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H209" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I209" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B210" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C210" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E210" s="16" t="n">
+        <v>0.723404255319149</v>
+      </c>
+      <c r="F210" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G210" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H210" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I210" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B211" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C211" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D211" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E211" s="16" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="F211" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G211" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H211" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I211" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B212" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C212" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D212" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E212" s="16" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="F212" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G212" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H212" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I212" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B213" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C213" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D213" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head confusion matrix</t>
+        </is>
+      </c>
+      <c r="E213" s="15" t="inlineStr">
+        <is>
+          <t>[[29, 4], [9, 5]]</t>
+        </is>
+      </c>
+      <c r="F213" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G213" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H213" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json</t>
+        </is>
+      </c>
+      <c r="I213" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B214" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C214" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D214" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E214" s="16" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="F214" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G214" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H214" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I214" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON); REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B215" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C215" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D215" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E215" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G215" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H215" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I215" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B216" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C216" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D216" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E216" s="16" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="F216" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G216" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H216" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I216" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B217" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C217" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D217" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E217" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G217" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H217" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I217" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B218" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C218" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D218" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E218" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G218" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H218" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I218" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B219" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C219" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D219" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head confusion matrix</t>
+        </is>
+      </c>
+      <c r="E219" s="15" t="inlineStr">
+        <is>
+          <t>[[33, 0], [14, 0]]</t>
+        </is>
+      </c>
+      <c r="F219" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155701Z-gemma4_daic_audio_only_fixed_heads_20260812t155635z_799cc412-799cc412-4fafe36d, source 799cc412 (clean main), PR #46, jobs 44538982/44538983 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153615Z-gemma4_daic_audio_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-f9cac152 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G219" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H219" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/audio_only/daic/gemma4_daic_audio_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json</t>
+        </is>
+      </c>
+      <c r="I219" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B220" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C220" s="15" t="inlineStr">
+        <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="D200" s="15" t="inlineStr">
+      <c r="D220" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 macro-F1</t>
+        </is>
+      </c>
+      <c r="E220" s="16" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="F220" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G220" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H220" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I220" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B221" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C221" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D221" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 positive-F1</t>
+        </is>
+      </c>
+      <c r="E221" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F221" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G221" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H221" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I221" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B222" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C222" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D222" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 accuracy</t>
+        </is>
+      </c>
+      <c r="E222" s="16" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F222" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G222" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H222" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I222" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B223" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C223" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D223" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 confusion matrix</t>
+        </is>
+      </c>
+      <c r="E223" s="15" t="inlineStr">
+        <is>
+          <t>[[27, 6], [4, 10]]</t>
+        </is>
+      </c>
+      <c r="F223" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G223" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H223" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+        </is>
+      </c>
+      <c r="I223" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B224" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C224" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D224" s="15" t="inlineStr">
         <is>
           <t>Gemma 4 invalid count</t>
         </is>
       </c>
-      <c r="E200" s="15" t="n">
+      <c r="E224" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F200" s="17" t="inlineStr">
+      <c r="F224" s="17" t="inlineStr">
         <is>
           <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
-      <c r="G200" s="17" t="inlineStr">
+      <c r="G224" s="17" t="inlineStr">
         <is>
           <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
-      <c r="H200" s="17" t="inlineStr">
+      <c r="H224" s="17" t="inlineStr">
         <is>
           <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
         </is>
       </c>
-      <c r="I200" s="17" t="inlineStr">
+      <c r="I224" s="17" t="inlineStr">
         <is>
           <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B225" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C225" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D225" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E225" s="16" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="F225" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G225" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H225" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I225" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON); REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B226" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C226" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D226" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E226" s="16" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="F226" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G226" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H226" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I226" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B227" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C227" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D227" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E227" s="16" t="n">
+        <v>0.7446808510638298</v>
+      </c>
+      <c r="F227" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G227" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H227" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I227" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B228" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C228" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D228" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E228" s="16" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="F228" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G228" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H228" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I228" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B229" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C229" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D229" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E229" s="16" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="F229" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G229" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H229" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I229" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B230" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C230" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D230" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head confusion matrix</t>
+        </is>
+      </c>
+      <c r="E230" s="15" t="inlineStr">
+        <is>
+          <t>[[26, 7], [5, 9]]</t>
+        </is>
+      </c>
+      <c r="F230" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_logreg_raw</t>
+        </is>
+      </c>
+      <c r="G230" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H230" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/logreg/metrics.json</t>
+        </is>
+      </c>
+      <c r="I230" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B231" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C231" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D231" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E231" s="16" t="n">
+        <v>0.6948051948051948</v>
+      </c>
+      <c r="F231" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G231" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H231" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I231" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON); REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B232" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C232" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D232" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E232" s="16" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F232" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G232" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H232" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I232" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B233" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C233" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D233" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E233" s="16" t="n">
+        <v>0.7446808510638298</v>
+      </c>
+      <c r="F233" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G233" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H233" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I233" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B234" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C234" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D234" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E234" s="16" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F234" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G234" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H234" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I234" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B235" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C235" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D235" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E235" s="16" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F235" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G235" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H235" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I235" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B236" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C236" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D236" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head confusion matrix</t>
+        </is>
+      </c>
+      <c r="E236" s="15" t="inlineStr">
+        <is>
+          <t>[[27, 6], [6, 8]]</t>
+        </is>
+      </c>
+      <c r="F236" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4-daic-fixed-heads-v1-799cc412, run gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412, attempt 20260812T155703Z-gemma4_daic_text_only_fixed_heads_20260812t155635z_799cc412-799cc412-735f2c58, source 799cc412 (clean main), PR #46, jobs 44538984/44538985 (COMPLETED 0:0), parent attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, parent adapter 72e2dd204b91…/… split 441333e0c888…, model google/gemma-4-12B-it rev 707f0a3b8a3c…; supersedes 20260812T153617Z-gemma4_daic_text_only_fixed_heads_20260812t153611z_dcfaa142-dcfaa142-066f6db6 (extract FAILED 1:0, heads CANCELLED, wrapper race fixed in PR #45), backend gemma4_hidden_xgb_raw</t>
+        </is>
+      </c>
+      <c r="G236" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_fit_locked_test_evaluation</t>
+        </is>
+      </c>
+      <c r="H236" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_heads/text_only/daic/gemma4_daic_text_only_fixed_heads_20260812T155635Z_799cc412/fold_0/hidden_classifiers/xgb/metrics.json</t>
+        </is>
+      </c>
+      <c r="I236" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local (matches metrics JSON)</t>
         </is>
       </c>
     </row>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Merged vs Standalone MacroF1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="DAIC Packed30 Family" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Gemma 4 DAIC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Provenance" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gemma vs Qwen" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Provenance" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6422,6 +6423,269 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gemma 4 vs Qwen — DAIC official test, macro-F1 (seed 1337, fold 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Macro-F1, binary-strict, best_model, official 47-subject DAIC test. Qwen: harmonized campaign harmonized_v1_prod_20260809T171705Z_d1e8130b (teacher-forced row = Fine-tuned Qwen STANDALONE_QWEN; head rows = harmonized hidden-state heads STANDALONE_HEADS, pooled subject-level). Gemma: campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae (teacher-forced GEMMA4_QWEN, subject mean-score) and fixed-head campaign gemma4-daic-fixed-heads-v1-799cc412 (GEMMA4_HEADS, subject mean probability &gt;= 0.5). One seed each — differences are observations, not variance estimates. Delta = Gemma minus Qwen. Provenance: Provenance sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Qwen macro-F1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Gemma macro-F1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Δ (Gemma − Qwen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.7631048387096775</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0.0278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7432</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7898658718330849</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.0467</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost raw hidden head</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7834101382488479</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.0481</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>-0.1267</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6258420085731782</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.0675</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost raw hidden head</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>-0.1065</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.0199</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>-0.0172</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost raw hidden head</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6948051948051948</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>-0.0509</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Teacher-forced = backbone classification without hidden-state heads. Hidden heads classify the final prompt-token hidden state with the locked LogReg/XGBoost implementations. See the 'Gemma 4 DAIC' and 'Summary' sheets for the full metric sets and per-cell provenance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A14:E14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -15,9 +15,10 @@
     <sheet name="DAIC Packed30 Family" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Gemma 4 DAIC" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Gemma vs Qwen" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="DAIC LLM Comparison" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="DAIC Head Ablation" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Provenance" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Optuna-100 XGB" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="DAIC LLM Comparison" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="DAIC Head Ablation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Provenance" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -836,6 +837,557 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DAIC-WOZ LLM literature comparison — official development partition (35 subjects)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Cited literature (DAIC official development partition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Study</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Backbone</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Partition</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Comparability</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DepresInstruct (Li et al., 2025)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Qwen2-Audio-7B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7714</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DAIC development</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C — reported as F1; shown as Macro-F1 per researcher decision</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.inffus.2025.104077</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DepresInstruct (Li et al., 2025)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Qwen2-7B</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DAIC development</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C — reported as F1; shown as Macro-F1 per researcher decision</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.inffus.2025.104077</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DepresInstruct (Li et al., 2025)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Qwen2-Audio-7B</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7619</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DAIC development</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>C — reported as F1; shown as Macro-F1 per researcher decision</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.inffus.2025.104077</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IT HEARS — Qwen2-7B baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Qwen2-7B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DAIC development</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>C — paper reports F1; baseline; no validation/accuracy reported</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2511.19877</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IT HEARS — Qwen2-Audio-7B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Qwen2-Audio-7B</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DAIC development</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>C — paper reports F1; no validation/accuracy reported</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2511.19877</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Ours — official development (35 subjects, seed 1337, fold 0, best_model)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Backbone</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Positive-F1</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Selected epoch</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B IT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>0.396551724137931</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions; attempt 20260813T142848Z-dai…</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0.3859649122807018</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.6285714285714286</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions; attempt 20260813T142847Z-dai…</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B IT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>0.7552447552447553</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0.6923076923076924</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>35</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions; attempt 20260813T142848Z-dai…</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>0.6258503401360545</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions; attempt 20260813T142848Z-dai…</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B IT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0.7822222222222222</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0.7199999999999999</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>35</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions; attempt 20260813T142849Z-dai…</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0.7086031452358927</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions; attempt 20260813T142848Z-dai…</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1734,7 +2286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21733,546 +22285,1961 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DAIC-WOZ LLM literature comparison — official development partition (35 subjects)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Cited literature (DAIC official development partition)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Study</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Backbone</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          <t>Standardized Optuna-100 XGBoost — macro-F1 (not run yet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Protocol harmonized_optuna100_v1: exactly 100 TPE trials, seeds 1337/1337/1337, 3 subject-grouped inner folds, threshold 0.5, sampling none, pooled inner subject-level macro-F1 objective (merged: unweighted mean of five per-dataset inner macro-F1). Prediction backends qwen_hidden_xgb_optuna100 / gemma4_hidden_xgb_optuna100 (+ _symmetric_merged for merged). Qwen and Gemma paired cells share manifests, splits, weights, view (original_teacher_forced, harmonized_all_windows_full_coverage), namespace headline/binary_strict, and seeds. Fixed historical XGB rows remain in their original sheets, labelled, and are not replaced. All cells blank until evidence exists; not-run fields stay blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Family / Dataset</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Modality</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Aggregation</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Macro-F1</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Partition</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Comparability</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DepresInstruct (Li et al., 2025)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Qwen2-Audio-7B</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Positive-F1</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Native — D3TEC</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Native — D3TEC</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Native — D3TEC</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Audio only</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7714</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DAIC development</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>C — reported as F1; shown as Macro-F1 per researcher decision</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.inffus.2025.104077</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DepresInstruct (Li et al., 2025)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Qwen2-7B</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Native — D3TEC</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Native — D3TEC</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0.7272999999999999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.7429</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DAIC development</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>C — reported as F1; shown as Macro-F1 per researcher decision</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.inffus.2025.104077</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DepresInstruct (Li et al., 2025)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Qwen2-Audio-7B</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Native — D3TEC</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Native — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Audio + Text</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0.7619</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>DAIC development</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>C — reported as F1; shown as Macro-F1 per researcher decision</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.inffus.2025.104077</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>IT HEARS — Qwen2-7B baseline</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Qwen2-7B</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Native — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Native — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Native — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Native — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DAIC development</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>C — paper reports F1; baseline; no validation/accuracy reported</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2511.19877</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IT HEARS — Qwen2-Audio-7B</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Qwen2-Audio-7B</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Native — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Native — CMDC</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Audio + Text</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>DAIC development</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>C — paper reports F1; no validation/accuracy reported</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2511.19877</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Ours — official development (35 subjects, seed 1337, fold 0, best_model)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Backbone</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Modality</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Macro-F1</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Positive-F1</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Selected epoch</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Gemma 4 12B IT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Native — CMDC</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Native — CMDC</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Audio only</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
-        <v>0.396551724137931</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.6571428571428571</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>35</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>recomputed locally from predictions; attempt 20260813T142848Z-dai…</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Qwen</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Native — CMDC</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Audio only</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
-        <v>0.3859649122807018</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>35</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>recomputed locally from predictions; attempt 20260813T142847Z-dai…</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Gemma 4 12B IT</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Native — CMDC</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Native — CMDC</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Native — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Audio + Text</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
-        <v>0.7552447552447553</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>0.6923076923076924</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.7714285714285715</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>35</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>recomputed locally from predictions; attempt 20260813T142848Z-dai…</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Qwen</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Native — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Audio + Text</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
-        <v>0.6258503401360545</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>0.4761904761904762</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>35</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>recomputed locally from predictions; attempt 20260813T142848Z-dai…</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Gemma 4 12B IT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Native — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Native — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Native — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
-        <v>0.7822222222222222</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>0.7199999999999999</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>35</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>recomputed locally from predictions; attempt 20260813T142849Z-dai…</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Qwen</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Native — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="C16" s="15" t="n">
-        <v>0.7086031452358927</v>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>0.6086956521739131</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>35</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>recomputed locally from predictions; attempt 20260813T142848Z-dai…</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Native — DAIC-WOZ</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Native — DAIC-WOZ</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Native — DAIC-WOZ</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Native — DAIC-WOZ</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Native — DAIC-WOZ</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Native — DAIC-WOZ</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>English — D3TEC</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>English — D3TEC</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>English — D3TEC</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>English — D3TEC</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>English — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>English — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>English — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>English — Androids Interview</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>English — CMDC</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>English — CMDC</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>English — CMDC</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>English — CMDC</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>English — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>English — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>English — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>English — Turkish t17</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Symmetric merged</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — CV (5-fold)</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — CV (5-fold)</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — CV (5-fold)</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — CV (5-fold)</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — CV (5-fold)</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — CV (5-fold)</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — Final (DAIC official test)</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — Final (DAIC official test)</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — Final (DAIC official test)</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — Final (DAIC official test)</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — Final (DAIC official test)</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Symmetric merged — Final (DAIC official test)</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="7" t="n"/>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>DAIC official development — Official dev</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>DAIC official development — Official dev</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>DAIC official development — Official dev</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>DAIC official development — Official dev</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>DAIC official development — Official dev</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>DAIC official development — Official dev</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>pooled / fold-mean</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>not run yet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="6">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -22300,14 +22300,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Standardized Optuna-100 XGBoost — macro-F1 (not run yet)</t>
+          <t>Standardized Optuna-100 XGBoost — macro-F1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Protocol harmonized_optuna100_v1: exactly 100 TPE trials, seeds 1337/1337/1337, 3 subject-grouped inner folds, threshold 0.5, sampling none, pooled inner subject-level macro-F1 objective (merged: unweighted mean of five per-dataset inner macro-F1). Prediction backends qwen_hidden_xgb_optuna100 / gemma4_hidden_xgb_optuna100 (+ _symmetric_merged for merged). Qwen and Gemma paired cells share manifests, splits, weights, view (original_teacher_forced, harmonized_all_windows_full_coverage), namespace headline/binary_strict, and seeds. Fixed historical XGB rows remain in their original sheets, labelled, and are not replaced. All cells blank until evidence exists; not-run fields stay blank.</t>
+          <t>Protocol harmonized_optuna100_v1: exactly 100 TPE trials, seeds 1337/1337/1337, 3 subject-grouped inner folds, threshold 0.5, sampling none, pooled inner subject-level macro-F1 objective (merged: unweighted mean of five per-dataset inner macro-F1). Prediction backends qwen_hidden_xgb_optuna100 / gemma4_hidden_xgb_optuna100 (+ _symmetric_merged for merged). Qwen and Gemma paired cells share manifests, splits, weights, view (original_teacher_forced, harmonized_all_windows_full_coverage), namespace headline/binary_strict, and seeds. Values are fold-mean macro-F1 from the qualified group reports; the merged 'Final (DAIC official test)' rows are the single DAIC test fold. Fixed historical XGB rows remain in their original sheets, labelled, and are not replaced.</t>
         </is>
       </c>
     </row>
@@ -22373,14 +22373,16 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5234</v>
+      </c>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/d3tec_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22402,14 +22404,16 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5832000000000001</v>
+      </c>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/d3tec_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22431,14 +22435,16 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5195</v>
+      </c>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/d3tec_audio_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22460,14 +22466,16 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5461</v>
+      </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/d3tec_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22489,14 +22497,16 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6345</v>
+      </c>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/d3tec_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22518,14 +22528,16 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5719</v>
+      </c>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/d3tec_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22547,14 +22559,16 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8542999999999999</v>
+      </c>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/androids_interview_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22576,14 +22590,16 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8565</v>
+      </c>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/androids_interview_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22605,14 +22621,16 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8109</v>
+      </c>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/androids_interview_audio_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22634,14 +22652,16 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.802</v>
+      </c>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/androids_interview_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22663,14 +22683,16 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8466</v>
+      </c>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/androids_interview_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22692,14 +22714,16 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.7482</v>
+      </c>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/androids_interview_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22721,14 +22745,16 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9251</v>
+      </c>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/cmdc_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22750,14 +22776,16 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.9841</v>
+      </c>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/cmdc_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22779,14 +22807,16 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.9516</v>
+      </c>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/cmdc_audio_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22808,14 +22838,16 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.9584</v>
+      </c>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/cmdc_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22837,14 +22869,16 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.9539</v>
+      </c>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/cmdc_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22866,14 +22900,16 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/cmdc_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22895,14 +22931,16 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.6311</v>
+      </c>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/turkish_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22924,14 +22962,16 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.6819</v>
+      </c>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/turkish_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22953,14 +22993,16 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.5145</v>
+      </c>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/turkish_audio_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -22982,14 +23024,16 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.5671</v>
+      </c>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/turkish_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23011,14 +23055,16 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.5891999999999999</v>
+      </c>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/turkish_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23040,14 +23086,16 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.5208</v>
+      </c>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/turkish_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23069,14 +23117,16 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.7157</v>
+      </c>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/daic_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23098,14 +23148,16 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.8157</v>
+      </c>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/daic_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23127,14 +23179,16 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.5760999999999999</v>
+      </c>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/daic_audio_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23156,14 +23210,16 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.7257</v>
+      </c>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/daic_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23185,14 +23241,16 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.7257</v>
+      </c>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/daic_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23214,14 +23272,16 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.7696</v>
+      </c>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_native/daic_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23250,14 +23310,16 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.5982</v>
+      </c>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/d3tec_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23279,14 +23341,16 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.5467</v>
+      </c>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/d3tec_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23308,14 +23372,16 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.5289</v>
+      </c>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/d3tec_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23337,14 +23403,16 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.5599</v>
+      </c>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/d3tec_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23366,14 +23434,16 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.8727</v>
+      </c>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/androids_interview_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23395,14 +23465,16 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.9028</v>
+      </c>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/androids_interview_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23424,14 +23496,16 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.8111</v>
+      </c>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/androids_interview_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23453,14 +23527,16 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.8084</v>
+      </c>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/androids_interview_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23482,14 +23558,16 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.9134</v>
+      </c>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/cmdc_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23511,14 +23589,16 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.9683</v>
+      </c>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/cmdc_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23540,14 +23620,16 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.9698</v>
+      </c>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/cmdc_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23569,14 +23651,16 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.9398</v>
+      </c>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/cmdc_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23598,14 +23682,16 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.6287</v>
+      </c>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/turkish_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23627,14 +23713,16 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.5928</v>
+      </c>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/turkish_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23656,14 +23744,16 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.6584</v>
+      </c>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/turkish_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23685,14 +23775,16 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.6296</v>
+      </c>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_english/turkish_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23721,14 +23813,16 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.7412</v>
+      </c>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/audio_text_cv_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23750,14 +23844,16 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.7644</v>
+      </c>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/audio_text_cv_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23779,14 +23875,16 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.7474</v>
+      </c>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/audio_only_cv_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23808,14 +23906,16 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.7008</v>
+      </c>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/audio_only_cv_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23837,14 +23937,16 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.7603</v>
+      </c>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/text_only_cv_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23866,14 +23968,16 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.7658</v>
+      </c>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/text_only_cv_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23895,14 +23999,16 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0.7432</v>
+      </c>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/audio_text_final_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23924,14 +24030,16 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.7457</v>
+      </c>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/audio_text_final_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23953,14 +24061,16 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0.4728</v>
+      </c>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/audio_only_final_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -23982,14 +24092,16 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0.5554</v>
+      </c>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/audio_only_final_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -24011,14 +24123,16 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.7552</v>
+      </c>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/text_only_final_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -24040,14 +24154,16 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.7631</v>
+      </c>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_merged/text_only_final_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -24076,14 +24192,16 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.5304</v>
+      </c>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_officialdev/daic_audio_text_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -24105,14 +24223,16 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0.6830000000000001</v>
+      </c>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_officialdev/daic_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -24134,14 +24254,16 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.5727</v>
+      </c>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_officialdev/daic_audio_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -24163,14 +24285,16 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0.6686</v>
+      </c>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_officialdev/daic_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>
@@ -24192,14 +24316,16 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.6749000000000001</v>
+      </c>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_officialdev/daic_text_only_qwen/group_report.json</t>
         </is>
       </c>
     </row>
@@ -24221,14 +24347,16 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>pooled / fold-mean</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="n"/>
+          <t>fold-mean</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0.7086</v>
+      </c>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>not run yet</t>
+          <t>report:outputs/experiment_reports/optuna100_officialdev/daic_text_only_gemma4/group_report.json</t>
         </is>
       </c>
     </row>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -544,6 +544,9 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -556,7 +559,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Macro-F1 only; higher is better. Harmonized campaign harmonized_v1_prod_20260809T171705Z_d1e8130b (recipe harmonized_full_transcript_single30_allwindows_selmacrof1_tf_v1; Issue #12 / PR #10): teacher-forced, binary-strict, best_model, macro-F1 selection, audio encoder frozen, no Optuna; first-wave failures replaced by _r1 retries (retry_r1_jobs.tsv). DAIC = fixed official test (47 subjects). CMDC/Turkish = 5-fold mean (train_val protocol). D3TEC = pooled 5-fold subject-level (62 subjects). Androids = pooled 5-fold subject-level (116 subjects). Optuna/Subject-OS not run -&gt; blank. Every value recomputed 2026-08-10 from local artifacts; per-cell provenance (run, aggregation, eval view, artifact): Provenance sheet.</t>
+          <t>Macro-F1 only; higher is better. Harmonized campaign harmonized_v1_prod_20260809T171705Z_d1e8130b (recipe harmonized_full_transcript_single30_allwindows_selmacrof1_tf_v1; Issue #12 / PR #10): teacher-forced, binary-strict, best_model, macro-F1 selection, audio encoder frozen, no Optuna; first-wave failures replaced by _r1 retries (retry_r1_jobs.tsv). DAIC = fixed official test (47 subjects). CMDC/Turkish = 5-fold mean (train_val protocol). D3TEC = pooled 5-fold subject-level (62 subjects). Androids = pooled 5-fold subject-level (116 subjects). Gemma columns: native Gemma harmonized campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2 (teacher-forced + LogReg fold-means from the verified native group reports; DAIC reuses the DAIC official-test campaign). 'XGBoost Optuna-100 (Gemma)' = the standardized Optuna-100 fold-mean; the runbook fits no fixed XGB head for Gemma by design. Optuna/Subject-OS not run -&gt; blank. Every value recomputed from local artifacts; per-cell provenance (run, aggregation, eval view, artifact): Provenance sheet.</t>
         </is>
       </c>
     </row>
@@ -581,6 +584,21 @@
           <t>XGBoost fixed</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Fine-tuned Gemma</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>LogReg head (Gemma)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 (Gemma)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -597,6 +615,15 @@
       <c r="D5" s="5" t="n">
         <v>0.7353</v>
       </c>
+      <c r="E5" s="5" t="n">
+        <v>0.7631048387096775</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.7898658718330849</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.815686</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -613,6 +640,15 @@
       <c r="D6" s="5" t="n">
         <v>0.519</v>
       </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.6258420085731782</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.725729</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -629,6 +665,15 @@
       <c r="D7" s="5" t="n">
         <v>0.7457</v>
       </c>
+      <c r="E7" s="5" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.769608</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -645,6 +690,15 @@
       <c r="D8" s="5" t="n">
         <v>0.97</v>
       </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.984127</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -661,6 +715,15 @@
       <c r="D9" s="5" t="n">
         <v>0.9225</v>
       </c>
+      <c r="E9" s="5" t="n">
+        <v>0.784022</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.984127</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.958369</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -677,6 +740,15 @@
       <c r="D10" s="5" t="n">
         <v>0.9683</v>
       </c>
+      <c r="E10" s="5" t="n">
+        <v>0.957439</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.956334</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.924588</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -693,6 +765,15 @@
       <c r="D11" s="5" t="n">
         <v>0.6325</v>
       </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5657759999999999</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.618816</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.681937</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -709,6 +790,15 @@
       <c r="D12" s="5" t="n">
         <v>0.4271</v>
       </c>
+      <c r="E12" s="5" t="n">
+        <v>0.468559</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.529039</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.567052</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -725,6 +815,15 @@
       <c r="D13" s="5" t="n">
         <v>0.5234</v>
       </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6781779999999999</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.558253</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.520832</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -741,6 +840,15 @@
       <c r="D14" s="5" t="n">
         <v>0.5585</v>
       </c>
+      <c r="E14" s="5" t="n">
+        <v>0.571399</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.498159</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.5832270000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -757,6 +865,15 @@
       <c r="D15" s="5" t="n">
         <v>0.5404</v>
       </c>
+      <c r="E15" s="5" t="n">
+        <v>0.405413</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.5226769999999999</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.546075</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -773,6 +890,15 @@
       <c r="D16" s="5" t="n">
         <v>0.5911</v>
       </c>
+      <c r="E16" s="5" t="n">
+        <v>0.550505</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.522456</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.571942</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -789,6 +915,15 @@
       <c r="D17" s="5" t="n">
         <v>0.8656</v>
       </c>
+      <c r="E17" s="5" t="n">
+        <v>0.860541</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.8572689999999999</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.8565469999999999</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -805,6 +940,15 @@
       <c r="D18" s="5" t="n">
         <v>0.8235</v>
       </c>
+      <c r="E18" s="5" t="n">
+        <v>0.806987</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.796701</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.802024</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -821,11 +965,20 @@
       <c r="D19" s="5" t="n">
         <v>0.8241000000000001</v>
       </c>
+      <c r="E19" s="5" t="n">
+        <v>0.776201</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.802669</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.748177</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2292,7 +2445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I314"/>
+  <dimension ref="A1:I350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12911,147 +13064,147 @@
     <row r="237">
       <c r="A237" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B237" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C237" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D237" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E237" s="17" t="n">
-        <v>0.3859649122807018</v>
+        <v>0.571399</v>
       </c>
       <c r="F237" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G237" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H237" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_d3tec_audio_text/group_report.json</t>
         </is>
       </c>
       <c r="I237" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B238" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C238" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D238" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E238" s="17" t="n">
-        <v>0</v>
+        <v>0.498159</v>
       </c>
       <c r="F238" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G238" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H238" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/d3tec_audio_text.json</t>
         </is>
       </c>
       <c r="I238" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B239" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C239" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D239" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E239" s="17" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5832270000000001</v>
       </c>
       <c r="F239" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G239" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H239" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I239" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B240" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C240" s="16" t="inlineStr">
@@ -13061,42 +13214,42 @@
       </c>
       <c r="D240" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E240" s="17" t="n">
-        <v>0.396551724137931</v>
+        <v>0.405413</v>
       </c>
       <c r="F240" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G240" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H240" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_d3tec_audio_only/group_report.json</t>
         </is>
       </c>
       <c r="I240" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B241" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C241" s="16" t="inlineStr">
@@ -13106,42 +13259,42 @@
       </c>
       <c r="D241" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E241" s="17" t="n">
-        <v>0</v>
+        <v>0.5226769999999999</v>
       </c>
       <c r="F241" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G241" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H241" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/d3tec_audio_only.json</t>
         </is>
       </c>
       <c r="I241" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B242" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C242" s="16" t="inlineStr">
@@ -13151,177 +13304,177 @@
       </c>
       <c r="D242" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E242" s="17" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.546075</v>
       </c>
       <c r="F242" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G242" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H242" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I242" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B243" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C243" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D243" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E243" s="17" t="n">
-        <v>0.6258503401360545</v>
+        <v>0.550505</v>
       </c>
       <c r="F243" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G243" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H243" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_d3tec_text_only/group_report.json</t>
         </is>
       </c>
       <c r="I243" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B244" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C244" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D244" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E244" s="17" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.522456</v>
       </c>
       <c r="F244" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G244" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H244" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/d3tec_text_only.json</t>
         </is>
       </c>
       <c r="I244" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B245" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C245" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D245" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E245" s="17" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.571942</v>
       </c>
       <c r="F245" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G245" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H245" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I245" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B246" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C246" s="16" t="inlineStr">
@@ -13331,42 +13484,42 @@
       </c>
       <c r="D246" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E246" s="17" t="n">
-        <v>0.7552447552447553</v>
+        <v>0.860541</v>
       </c>
       <c r="F246" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G246" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H246" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_androids_interview_audio_text/group_report.json</t>
         </is>
       </c>
       <c r="I246" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B247" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C247" s="16" t="inlineStr">
@@ -13376,42 +13529,42 @@
       </c>
       <c r="D247" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E247" s="17" t="n">
-        <v>0.6923076923076924</v>
+        <v>0.8572689999999999</v>
       </c>
       <c r="F247" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G247" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H247" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/androids_interview_audio_text.json</t>
         </is>
       </c>
       <c r="I247" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B248" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C248" s="16" t="inlineStr">
@@ -13421,177 +13574,177 @@
       </c>
       <c r="D248" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E248" s="17" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.8565469999999999</v>
       </c>
       <c r="F248" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G248" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H248" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I248" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B249" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C249" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D249" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E249" s="17" t="n">
-        <v>0.7086031452358927</v>
+        <v>0.806987</v>
       </c>
       <c r="F249" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G249" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H249" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_androids_interview_audio_only/group_report.json</t>
         </is>
       </c>
       <c r="I249" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B250" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C250" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D250" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E250" s="17" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.796701</v>
       </c>
       <c r="F250" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G250" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H250" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/androids_interview_audio_only.json</t>
         </is>
       </c>
       <c r="I250" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B251" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C251" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D251" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E251" s="17" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.802024</v>
       </c>
       <c r="F251" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G251" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H251" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I251" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B252" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C252" s="16" t="inlineStr">
@@ -13601,42 +13754,42 @@
       </c>
       <c r="D252" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E252" s="17" t="n">
-        <v>0.7822222222222222</v>
+        <v>0.776201</v>
       </c>
       <c r="F252" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G252" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H252" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_androids_interview_text_only/group_report.json</t>
         </is>
       </c>
       <c r="I252" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B253" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C253" s="16" t="inlineStr">
@@ -13646,42 +13799,42 @@
       </c>
       <c r="D253" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E253" s="17" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.802669</v>
       </c>
       <c r="F253" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G253" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>pooled 5-fold subject-level, LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H253" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/androids_interview_text_only.json</t>
         </is>
       </c>
       <c r="I253" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B254" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C254" s="16" t="inlineStr">
@@ -13691,177 +13844,177 @@
       </c>
       <c r="D254" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E254" s="17" t="n">
-        <v>0.8</v>
+        <v>0.748177</v>
       </c>
       <c r="F254" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G254" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H254" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I254" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B255" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C255" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D255" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E255" s="17" t="n">
-        <v>0.5716783216783217</v>
+        <v>1</v>
       </c>
       <c r="F255" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G255" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H255" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_cmdc_audio_text/group_report.json</t>
         </is>
       </c>
       <c r="I255" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B256" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C256" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D256" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E256" s="17" t="n">
-        <v>0.4615384615384615</v>
+        <v>1</v>
       </c>
       <c r="F256" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G256" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H256" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/cmdc_audio_text.json</t>
         </is>
       </c>
       <c r="I256" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B257" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C257" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D257" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E257" s="17" t="n">
-        <v>0.6</v>
+        <v>0.984127</v>
       </c>
       <c r="F257" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G257" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H257" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I257" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B258" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C258" s="16" t="inlineStr">
@@ -13871,42 +14024,42 @@
       </c>
       <c r="D258" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E258" s="17" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.784022</v>
       </c>
       <c r="F258" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G258" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H258" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_cmdc_audio_only/group_report.json</t>
         </is>
       </c>
       <c r="I258" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B259" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C259" s="16" t="inlineStr">
@@ -13916,42 +14069,42 @@
       </c>
       <c r="D259" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E259" s="17" t="n">
-        <v>0.5</v>
+        <v>0.984127</v>
       </c>
       <c r="F259" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G259" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H259" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/cmdc_audio_only.json</t>
         </is>
       </c>
       <c r="I259" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B260" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C260" s="16" t="inlineStr">
@@ -13961,312 +14114,312 @@
       </c>
       <c r="D260" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E260" s="17" t="n">
-        <v>0.4484848484848484</v>
+        <v>0.958369</v>
       </c>
       <c r="F260" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G260" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H260" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I260" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B261" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C261" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D261" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E261" s="17" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.957439</v>
       </c>
       <c r="F261" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G261" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H261" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_cmdc_text_only/group_report.json</t>
         </is>
       </c>
       <c r="I261" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B262" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C262" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D262" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E262" s="17" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.956334</v>
       </c>
       <c r="F262" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G262" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H262" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/cmdc_text_only.json</t>
         </is>
       </c>
       <c r="I262" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B263" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C263" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D263" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E263" s="17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.924588</v>
       </c>
       <c r="F263" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G263" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H263" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I263" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B264" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C264" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D264" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E264" s="17" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5657759999999999</v>
       </c>
       <c r="F264" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G264" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H264" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_turkish_audio_text/group_report.json</t>
         </is>
       </c>
       <c r="I264" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B265" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C265" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D265" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E265" s="17" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.618816</v>
       </c>
       <c r="F265" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G265" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H265" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/turkish_audio_text.json</t>
         </is>
       </c>
       <c r="I265" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B266" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C266" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D266" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E266" s="17" t="n">
-        <v>0.5</v>
+        <v>0.681937</v>
       </c>
       <c r="F266" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G266" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H266" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I266" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B267" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C267" s="16" t="inlineStr">
@@ -14276,42 +14429,42 @@
       </c>
       <c r="D267" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E267" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.468559</v>
       </c>
       <c r="F267" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G267" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H267" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_turkish_audio_only/group_report.json</t>
         </is>
       </c>
       <c r="I267" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B268" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C268" s="16" t="inlineStr">
@@ -14321,42 +14474,42 @@
       </c>
       <c r="D268" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E268" s="17" t="n">
-        <v>0.625</v>
+        <v>0.529039</v>
       </c>
       <c r="F268" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G268" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H268" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/turkish_audio_only.json</t>
         </is>
       </c>
       <c r="I268" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B269" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C269" s="16" t="inlineStr">
@@ -14366,172 +14519,172 @@
       </c>
       <c r="D269" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E269" s="17" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.567052</v>
       </c>
       <c r="F269" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G269" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H269" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I269" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B270" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C270" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D270" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E270" s="17" t="n">
-        <v>0.396551724137931</v>
+        <v>0.6781779999999999</v>
       </c>
       <c r="F270" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G270" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H270" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_tf_turkish_text_only/group_report.json</t>
         </is>
       </c>
       <c r="I270" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (matches metrics JSON); group report OK</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B271" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C271" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D271" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E271" s="17" t="n">
-        <v>0</v>
+        <v>0.558253</v>
       </c>
       <c r="F271" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G271" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>5-fold mean (train_val protocol), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H271" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/native_lr/turkish_text_only.json</t>
         </is>
       </c>
       <c r="I271" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma native</t>
         </is>
       </c>
       <c r="B272" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C272" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D272" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>Gemma XGBoost Optuna-100 raw hidden head</t>
         </is>
       </c>
       <c r="E272" s="17" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.520832</v>
       </c>
       <c r="F272" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, group gemma4-harmonized-v1-gemma4_v1_prod_20260814T2030Z_1ab337d2_r2, seed 1337, 5 folds REPORTABLE (registry); model google/gemma-4-12B-it rev 707f0a3b8a3c7ad586ed01e27eafbad8a27dd0f7</t>
         </is>
       </c>
       <c r="G272" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 trials seed 1337, 3 inner folds, subject-level macro-F1 objective</t>
         </is>
       </c>
       <c r="H272" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I272" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempt REPORTABLE in registry</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B273" s="16" t="inlineStr">
@@ -14546,37 +14699,37 @@
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E273" s="17" t="n">
-        <v>0</v>
+        <v>0.3859649122807018</v>
       </c>
       <c r="F273" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G273" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H273" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I273" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B274" s="16" t="inlineStr">
@@ -14591,7 +14744,7 @@
       </c>
       <c r="D274" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E274" s="17" t="n">
@@ -14599,29 +14752,29 @@
       </c>
       <c r="F274" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G274" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H274" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I274" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B275" s="16" t="inlineStr">
@@ -14631,42 +14784,42 @@
       </c>
       <c r="C275" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D275" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E275" s="17" t="n">
-        <v>0.6577777777777778</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F275" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G275" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H275" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I275" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B276" s="16" t="inlineStr">
@@ -14676,42 +14829,42 @@
       </c>
       <c r="C276" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D276" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E276" s="17" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F276" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G276" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H276" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I276" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B277" s="16" t="inlineStr">
@@ -14721,42 +14874,42 @@
       </c>
       <c r="C277" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D277" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E277" s="17" t="n">
-        <v>0.6857142857142857</v>
+        <v>0</v>
       </c>
       <c r="F277" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G277" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H277" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I277" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B278" s="16" t="inlineStr">
@@ -14766,42 +14919,42 @@
       </c>
       <c r="C278" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D278" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E278" s="17" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="F278" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G278" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H278" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I278" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B279" s="16" t="inlineStr">
@@ -14816,37 +14969,37 @@
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E279" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6258503401360545</v>
       </c>
       <c r="F279" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G279" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H279" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I279" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B280" s="16" t="inlineStr">
@@ -14861,37 +15014,37 @@
       </c>
       <c r="D280" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E280" s="17" t="n">
-        <v>0.5304437564499485</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="F280" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G280" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H280" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I280" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B281" s="16" t="inlineStr">
@@ -14906,37 +15059,37 @@
       </c>
       <c r="D281" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E281" s="17" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F281" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G281" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H281" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I281" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B282" s="16" t="inlineStr">
@@ -14951,37 +15104,37 @@
       </c>
       <c r="D282" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E282" s="17" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7552447552447553</v>
       </c>
       <c r="F282" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G282" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H282" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I282" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B283" s="16" t="inlineStr">
@@ -14996,37 +15149,37 @@
       </c>
       <c r="D283" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E283" s="17" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="F283" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G283" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H283" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I283" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B284" s="16" t="inlineStr">
@@ -15041,37 +15194,37 @@
       </c>
       <c r="D284" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E284" s="17" t="n">
-        <v>0.25</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="F284" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G284" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H284" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I284" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B285" s="16" t="inlineStr">
@@ -15081,42 +15234,42 @@
       </c>
       <c r="C285" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D285" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E285" s="17" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.7086031452358927</v>
       </c>
       <c r="F285" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G285" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H285" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I285" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B286" s="16" t="inlineStr">
@@ -15126,42 +15279,42 @@
       </c>
       <c r="C286" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D286" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E286" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="F286" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G286" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H286" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I286" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B287" s="16" t="inlineStr">
@@ -15171,42 +15324,42 @@
       </c>
       <c r="C287" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D287" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E287" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="F287" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G287" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H287" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I287" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B288" s="16" t="inlineStr">
@@ -15216,42 +15369,42 @@
       </c>
       <c r="C288" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D288" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E288" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7822222222222222</v>
       </c>
       <c r="F288" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G288" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H288" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I288" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B289" s="16" t="inlineStr">
@@ -15261,42 +15414,42 @@
       </c>
       <c r="C289" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D289" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E289" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="F289" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G289" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H289" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I289" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B290" s="16" t="inlineStr">
@@ -15306,35 +15459,35 @@
       </c>
       <c r="C290" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D290" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E290" s="17" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.8</v>
       </c>
       <c r="F290" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G290" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H290" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I290" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
@@ -15351,20 +15504,20 @@
       </c>
       <c r="C291" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D291" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E291" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5716783216783217</v>
       </c>
       <c r="F291" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G291" s="18" t="inlineStr">
@@ -15374,7 +15527,7 @@
       </c>
       <c r="H291" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I291" s="18" t="inlineStr">
@@ -15396,20 +15549,20 @@
       </c>
       <c r="C292" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D292" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E292" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="F292" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G292" s="18" t="inlineStr">
@@ -15419,7 +15572,7 @@
       </c>
       <c r="H292" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I292" s="18" t="inlineStr">
@@ -15441,20 +15594,20 @@
       </c>
       <c r="C293" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D293" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Qwen LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E293" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6</v>
       </c>
       <c r="F293" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G293" s="18" t="inlineStr">
@@ -15464,7 +15617,7 @@
       </c>
       <c r="H293" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I293" s="18" t="inlineStr">
@@ -15486,20 +15639,20 @@
       </c>
       <c r="C294" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D294" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
+          <t>Qwen LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E294" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F294" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G294" s="18" t="inlineStr">
@@ -15509,7 +15662,7 @@
       </c>
       <c r="H294" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I294" s="18" t="inlineStr">
@@ -15531,20 +15684,20 @@
       </c>
       <c r="C295" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D295" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>Qwen LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E295" s="17" t="n">
-        <v>0.6938775510204083</v>
+        <v>0.5</v>
       </c>
       <c r="F295" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G295" s="18" t="inlineStr">
@@ -15554,7 +15707,7 @@
       </c>
       <c r="H295" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I295" s="18" t="inlineStr">
@@ -15576,20 +15729,20 @@
       </c>
       <c r="C296" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D296" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E296" s="17" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.4484848484848484</v>
       </c>
       <c r="F296" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G296" s="18" t="inlineStr">
@@ -15599,7 +15752,7 @@
       </c>
       <c r="H296" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I296" s="18" t="inlineStr">
@@ -15621,20 +15774,20 @@
       </c>
       <c r="C297" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D297" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E297" s="17" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="F297" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G297" s="18" t="inlineStr">
@@ -15644,7 +15797,7 @@
       </c>
       <c r="H297" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I297" s="18" t="inlineStr">
@@ -15666,20 +15819,20 @@
       </c>
       <c r="C298" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D298" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E298" s="17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F298" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G298" s="18" t="inlineStr">
@@ -15689,7 +15842,7 @@
       </c>
       <c r="H298" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I298" s="18" t="inlineStr">
@@ -15711,20 +15864,20 @@
       </c>
       <c r="C299" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D299" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>Qwen XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E299" s="17" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F299" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G299" s="18" t="inlineStr">
@@ -15734,7 +15887,7 @@
       </c>
       <c r="H299" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I299" s="18" t="inlineStr">
@@ -15756,20 +15909,20 @@
       </c>
       <c r="C300" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D300" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>Qwen XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E300" s="17" t="n">
-        <v>0.6026831785345718</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F300" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G300" s="18" t="inlineStr">
@@ -15779,7 +15932,7 @@
       </c>
       <c r="H300" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I300" s="18" t="inlineStr">
@@ -15801,20 +15954,20 @@
       </c>
       <c r="C301" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D301" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E301" s="17" t="n">
-        <v>0.4210526315789474</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="F301" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G301" s="18" t="inlineStr">
@@ -15824,7 +15977,7 @@
       </c>
       <c r="H301" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I301" s="18" t="inlineStr">
@@ -15846,20 +15999,20 @@
       </c>
       <c r="C302" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D302" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E302" s="17" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="F302" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G302" s="18" t="inlineStr">
@@ -15869,7 +16022,7 @@
       </c>
       <c r="H302" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I302" s="18" t="inlineStr">
@@ -15891,20 +16044,20 @@
       </c>
       <c r="C303" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D303" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E303" s="17" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F303" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G303" s="18" t="inlineStr">
@@ -15914,7 +16067,7 @@
       </c>
       <c r="H303" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I303" s="18" t="inlineStr">
@@ -15936,20 +16089,20 @@
       </c>
       <c r="C304" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D304" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E304" s="17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.625</v>
       </c>
       <c r="F304" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G304" s="18" t="inlineStr">
@@ -15959,7 +16112,7 @@
       </c>
       <c r="H304" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I304" s="18" t="inlineStr">
@@ -15981,20 +16134,20 @@
       </c>
       <c r="C305" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D305" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E305" s="17" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F305" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G305" s="18" t="inlineStr">
@@ -16004,7 +16157,7 @@
       </c>
       <c r="H305" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I305" s="18" t="inlineStr">
@@ -16026,20 +16179,20 @@
       </c>
       <c r="C306" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D306" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E306" s="17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F306" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G306" s="18" t="inlineStr">
@@ -16049,7 +16202,7 @@
       </c>
       <c r="H306" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I306" s="18" t="inlineStr">
@@ -16071,20 +16224,20 @@
       </c>
       <c r="C307" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D307" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E307" s="17" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F307" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G307" s="18" t="inlineStr">
@@ -16094,7 +16247,7 @@
       </c>
       <c r="H307" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I307" s="18" t="inlineStr">
@@ -16116,20 +16269,20 @@
       </c>
       <c r="C308" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D308" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E308" s="17" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="F308" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G308" s="18" t="inlineStr">
@@ -16139,7 +16292,7 @@
       </c>
       <c r="H308" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I308" s="18" t="inlineStr">
@@ -16161,20 +16314,20 @@
       </c>
       <c r="C309" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D309" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E309" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="F309" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G309" s="18" t="inlineStr">
@@ -16184,7 +16337,7 @@
       </c>
       <c r="H309" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I309" s="18" t="inlineStr">
@@ -16206,20 +16359,20 @@
       </c>
       <c r="C310" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D310" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E310" s="17" t="n">
-        <v>0.6685606060606061</v>
+        <v>0</v>
       </c>
       <c r="F310" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G310" s="18" t="inlineStr">
@@ -16229,7 +16382,7 @@
       </c>
       <c r="H310" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I310" s="18" t="inlineStr">
@@ -16251,20 +16404,20 @@
       </c>
       <c r="C311" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D311" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E311" s="17" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6577777777777778</v>
       </c>
       <c r="F311" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G311" s="18" t="inlineStr">
@@ -16274,7 +16427,7 @@
       </c>
       <c r="H311" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I311" s="18" t="inlineStr">
@@ -16296,20 +16449,20 @@
       </c>
       <c r="C312" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D312" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E312" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="F312" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G312" s="18" t="inlineStr">
@@ -16319,7 +16472,7 @@
       </c>
       <c r="H312" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I312" s="18" t="inlineStr">
@@ -16341,20 +16494,20 @@
       </c>
       <c r="C313" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D313" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Qwen LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E313" s="17" t="n">
-        <v>0.6</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F313" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G313" s="18" t="inlineStr">
@@ -16364,7 +16517,7 @@
       </c>
       <c r="H313" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I313" s="18" t="inlineStr">
@@ -16386,33 +16539,1653 @@
       </c>
       <c r="C314" s="16" t="inlineStr">
         <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D314" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E314" s="17" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="F314" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G314" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H314" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I314" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B315" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C315" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D315" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E315" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F315" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G315" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H315" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I315" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B316" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C316" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D316" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E316" s="17" t="n">
+        <v>0.5304437564499485</v>
+      </c>
+      <c r="F316" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G316" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H316" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I316" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B317" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C317" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D317" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E317" s="17" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="F317" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G317" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H317" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I317" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B318" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C318" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D318" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E318" s="17" t="n">
+        <v>0.6285714285714286</v>
+      </c>
+      <c r="F318" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G318" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H318" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I318" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B319" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C319" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D319" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E319" s="17" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="F319" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G319" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H319" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I319" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B320" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C320" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D320" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E320" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F320" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G320" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H320" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I320" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B321" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C321" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D321" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E321" s="17" t="n">
+        <v>0.6829710144927537</v>
+      </c>
+      <c r="F321" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G321" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H321" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I321" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B322" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C322" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D322" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E322" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F322" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G322" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H322" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I322" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B323" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C323" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E323" s="17" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F323" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G323" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H323" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I323" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B324" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C324" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D324" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E324" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F324" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G324" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H324" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I324" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B325" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C325" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E325" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F325" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G325" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H325" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I325" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B326" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C326" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D326" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E326" s="17" t="n">
+        <v>0.6829710144927537</v>
+      </c>
+      <c r="F326" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G326" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H326" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I326" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B327" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C327" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D327" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E327" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F327" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G327" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H327" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I327" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B328" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C328" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D328" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E328" s="17" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F328" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G328" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H328" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I328" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B329" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C329" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D329" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E329" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F329" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G329" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H329" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I329" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B330" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C330" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D330" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E330" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F330" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G330" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H330" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I330" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B331" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C331" s="16" t="inlineStr">
+        <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="D314" s="16" t="inlineStr">
+      <c r="D331" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E331" s="17" t="n">
+        <v>0.6938775510204083</v>
+      </c>
+      <c r="F331" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G331" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H331" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I331" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B332" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C332" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D332" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E332" s="17" t="n">
+        <v>0.5714285714285715</v>
+      </c>
+      <c r="F332" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G332" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H332" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I332" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B333" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C333" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D333" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E333" s="17" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="F333" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G333" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H333" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I333" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B334" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C334" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D334" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E334" s="17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F334" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G334" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H334" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I334" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B335" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C335" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D335" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E335" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F335" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G335" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H335" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I335" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B336" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C336" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D336" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E336" s="17" t="n">
+        <v>0.6026831785345718</v>
+      </c>
+      <c r="F336" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G336" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H336" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I336" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B337" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C337" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D337" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E337" s="17" t="n">
+        <v>0.4210526315789474</v>
+      </c>
+      <c r="F337" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G337" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H337" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I337" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B338" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C338" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D338" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E338" s="17" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="F338" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G338" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H338" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I338" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B339" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C339" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D339" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E339" s="17" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F339" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G339" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H339" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I339" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B340" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C340" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D340" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E340" s="17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F340" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G340" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H340" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I340" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B341" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C341" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D341" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E341" s="17" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="F341" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G341" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H341" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I341" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B342" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C342" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D342" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E342" s="17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F342" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G342" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H342" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I342" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B343" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C343" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D343" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E343" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F343" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G343" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H343" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I343" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B344" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C344" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D344" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E344" s="17" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="F344" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G344" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H344" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I344" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B345" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C345" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D345" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E345" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F345" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G345" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H345" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I345" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B346" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C346" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D346" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E346" s="17" t="n">
+        <v>0.6685606060606061</v>
+      </c>
+      <c r="F346" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G346" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H346" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I346" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B347" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C347" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D347" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E347" s="17" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="F347" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G347" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H347" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I347" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B348" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C348" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D348" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E348" s="17" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F348" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G348" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H348" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I348" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B349" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C349" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D349" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E349" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F349" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G349" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H349" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I349" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B350" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C350" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D350" s="16" t="inlineStr">
         <is>
           <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
-      <c r="E314" s="17" t="n">
+      <c r="E350" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="F314" s="18" t="inlineStr">
+      <c r="F350" s="18" t="inlineStr">
         <is>
           <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
-      <c r="G314" s="18" t="inlineStr">
+      <c r="G350" s="18" t="inlineStr">
         <is>
           <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
-      <c r="H314" s="18" t="inlineStr">
+      <c r="H350" s="18" t="inlineStr">
         <is>
           <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
-      <c r="I314" s="18" t="inlineStr">
+      <c r="I350" s="18" t="inlineStr">
         <is>
           <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
@@ -22022,7 +23795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22035,245 +23808,1271 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gemma 4 vs Qwen — DAIC official test, macro-F1 (seed 1337, fold 0)</t>
+          <t>Gemma 4 vs Qwen — macro-F1 (seed 1337, harmonized view)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="110" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Macro-F1, binary-strict, best_model, official 47-subject DAIC test. Qwen: harmonized campaign harmonized_v1_prod_20260809T171705Z_d1e8130b (teacher-forced row = Fine-tuned Qwen STANDALONE_QWEN; head rows = harmonized hidden-state heads STANDALONE_HEADS, pooled subject-level). Gemma: campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae (teacher-forced GEMMA4_QWEN, subject mean-score) and fixed-head campaign gemma4-daic-fixed-heads-v1-799cc412 (GEMMA4_HEADS, subject mean probability &gt;= 0.5). One seed each — differences are observations, not variance estimates. Delta = Gemma minus Qwen. Provenance: Provenance sheet.</t>
+          <t>Macro-F1, binary-strict, best_model. Qwen: harmonized campaign harmonized_v1_prod_20260809T171705Z_d1e8130b (teacher-forced = Fine-tuned Qwen; head rows = harmonized hidden-state heads, pooled/fold subject-level). Gemma: native harmonized campaign gemma4_v1_prod_20260814T2030Z_1ab337d2_r2 (teacher-forced and LogReg fold-means from the verified native group reports); DAIC rows reuse the DAIC official-test campaign (GEMMA4_QWEN / GEMMA4_HEADS). XGBoost rows compare the standardized Optuna-100 fold-means (100 trials, seed 1337) for both backends; the runbook fits no fixed XGB head for Gemma by design, and the Qwen historical fixed-XGB rows remain in the Summary sheet. Delta = Gemma minus Qwen. Provenance: Provenance sheet.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Modality</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Qwen macro-F1</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Gemma macro-F1</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Δ (Gemma − Qwen)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Teacher-forced</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0.7353</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0.7631048387096775</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0278</v>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
           <t>Audio + Text</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>LogReg raw hidden head</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0.7432</v>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.7898658718330849</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0.0467</v>
+        <v>0.7353</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7631048387096775</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.0278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
           <t>Audio + Text</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>XGBoost raw hidden head</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0.7353</v>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.7834101382488479</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.0481</v>
+        <v>0.7432</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.7898658718330849</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0.0467</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>0.5392</v>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.4125</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>-0.1267</v>
+        <v>0.715726</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.815686</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
           <t>Audio only</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>LogReg raw hidden head</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0.5583</v>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.6258420085731782</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.0675</v>
+        <v>0.5392</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
           <t>Audio only</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>XGBoost raw hidden head</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0.519</v>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.4125</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>-0.1065</v>
+        <v>0.5583</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6258420085731782</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.0675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0.7353</v>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.7552083333333333</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.0199</v>
+        <v>0.5761269999999999</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.725729</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0.1496</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>LogReg raw hidden head</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0.7235</v>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.70625</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>-0.0172</v>
+        <v>0.7353</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.0199</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>XGBoost raw hidden head</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0.7457</v>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.6948051948051948</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>-0.0509</v>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Teacher-forced = backbone classification without hidden-state heads. Hidden heads classify the final prompt-token hidden state with the locked LogReg/XGBoost implementations. See the 'Gemma 4 DAIC' and 'Summary' sheets for the full metric sets and per-cell provenance.</t>
+        <v>0.7235</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>-0.0172</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.725729</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.769608</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.0439</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9614</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0.0386</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9250890000000001</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.984127</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.059</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.9516</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.784022</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>-0.1676</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.984127</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.951555</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.958369</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.0068</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.957439</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>-0.0139</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.956334</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0.0143</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.924588</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>-0.0293</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.5657759999999999</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>-0.1008</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0.6289</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.618816</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>-0.0101</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.631141</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.681937</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.0508</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.468559</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>-0.0451</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.5209</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.529039</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.0081</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0.514507</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.567052</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0.0525</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.6781779999999999</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.558253</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>-0.0292</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0.589237</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.520832</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>-0.0684</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.571399</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.498159</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>0.523398</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.5832270000000001</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>0.0598</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0.6649</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.405413</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>-0.2595</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.5226769999999999</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>-0.0804</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0.519475</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.546075</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0.0266</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.550505</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>-0.0608</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.522456</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0.0574</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0.634535</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.571942</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>-0.0626</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.860541</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>-0.0001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.8572689999999999</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>-0.0172</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.854305</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.8565469999999999</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0.0022</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.806987</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>-0.062</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.796701</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>-0.0545</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.810943</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.802024</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>-0.0089</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.7317</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.776201</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>0.0445</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>LogReg raw hidden head</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.802669</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>-0.0299</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>XGBoost Optuna-100 raw hidden head</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.846597</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.748177</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>-0.0984</v>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Teacher-forced = backbone classification without hidden-state heads. Hidden heads classify the final prompt-token hidden state with the locked LogReg or the standardized Optuna-100 XGBoost implementation. DAIC = official 47-subject test; CMDC/Turkish = 5-fold mean (train_val); D3TEC/Androids = pooled 5-fold subject-level. See the 'Gemma 4 DAIC', 'Summary', and 'Optuna-100 XGB' sheets for full metric sets and per-cell provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="8">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -586,15 +586,20 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>XGBoost Optuna-100 (Qwen)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>Fine-tuned Gemma</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>LogReg head (Gemma)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>XGBoost Optuna-100 (Gemma)</t>
         </is>
@@ -616,12 +621,15 @@
         <v>0.7353</v>
       </c>
       <c r="E5" s="5" t="n">
+        <v>0.715726</v>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>0.7631048387096775</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>0.7898658718330849</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <v>0.815686</v>
       </c>
     </row>
@@ -641,12 +649,15 @@
         <v>0.519</v>
       </c>
       <c r="E6" s="5" t="n">
+        <v>0.5761269999999999</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>0.4125</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>0.6258420085731782</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <v>0.725729</v>
       </c>
     </row>
@@ -666,12 +677,15 @@
         <v>0.7457</v>
       </c>
       <c r="E7" s="5" t="n">
+        <v>0.725729</v>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>0.7552083333333333</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>0.70625</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>0.769608</v>
       </c>
     </row>
@@ -691,12 +705,15 @@
         <v>0.97</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>0.9250890000000001</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>0.984127</v>
       </c>
     </row>
@@ -716,12 +733,15 @@
         <v>0.9225</v>
       </c>
       <c r="E9" s="5" t="n">
+        <v>0.951555</v>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>0.784022</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <v>0.984127</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <v>0.958369</v>
       </c>
     </row>
@@ -741,12 +761,15 @@
         <v>0.9683</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>0.957439</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>0.956334</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>0.924588</v>
       </c>
     </row>
@@ -766,12 +789,15 @@
         <v>0.6325</v>
       </c>
       <c r="E11" s="5" t="n">
+        <v>0.631141</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>0.5657759999999999</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>0.618816</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <v>0.681937</v>
       </c>
     </row>
@@ -791,12 +817,15 @@
         <v>0.4271</v>
       </c>
       <c r="E12" s="5" t="n">
+        <v>0.514507</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>0.468559</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>0.529039</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>0.567052</v>
       </c>
     </row>
@@ -816,12 +845,15 @@
         <v>0.5234</v>
       </c>
       <c r="E13" s="5" t="n">
+        <v>0.589237</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>0.6781779999999999</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>0.558253</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13" s="5" t="n">
         <v>0.520832</v>
       </c>
     </row>
@@ -841,12 +873,15 @@
         <v>0.5585</v>
       </c>
       <c r="E14" s="5" t="n">
+        <v>0.523398</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>0.571399</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>0.498159</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>0.5832270000000001</v>
       </c>
     </row>
@@ -866,12 +901,15 @@
         <v>0.5404</v>
       </c>
       <c r="E15" s="5" t="n">
+        <v>0.519475</v>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>0.405413</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>0.5226769999999999</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>0.546075</v>
       </c>
     </row>
@@ -891,12 +929,15 @@
         <v>0.5911</v>
       </c>
       <c r="E16" s="5" t="n">
+        <v>0.634535</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>0.550505</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>0.522456</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>0.571942</v>
       </c>
     </row>
@@ -916,12 +957,15 @@
         <v>0.8656</v>
       </c>
       <c r="E17" s="5" t="n">
+        <v>0.854305</v>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>0.860541</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>0.8572689999999999</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>0.8565469999999999</v>
       </c>
     </row>
@@ -941,12 +985,15 @@
         <v>0.8235</v>
       </c>
       <c r="E18" s="5" t="n">
+        <v>0.810943</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>0.806987</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>0.796701</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>0.802024</v>
       </c>
     </row>
@@ -966,12 +1013,15 @@
         <v>0.8241000000000001</v>
       </c>
       <c r="E19" s="5" t="n">
+        <v>0.846597</v>
+      </c>
+      <c r="F19" s="5" t="n">
         <v>0.776201</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <v>0.802669</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <v>0.748177</v>
       </c>
     </row>
@@ -2445,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I350"/>
+  <dimension ref="A1:I414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14684,102 +14734,102 @@
     <row r="273">
       <c r="A273" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B273" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C273" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E273" s="17" t="n">
-        <v>0.3859649122807018</v>
+        <v>0.5233976549766023</v>
       </c>
       <c r="F273" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G273" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H273" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I273" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B274" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C274" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D274" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E274" s="17" t="n">
-        <v>0</v>
+        <v>0.5832267732267733</v>
       </c>
       <c r="F274" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G274" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H274" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I274" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B275" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C275" s="16" t="inlineStr">
@@ -14789,42 +14839,42 @@
       </c>
       <c r="D275" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E275" s="17" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5194749694749694</v>
       </c>
       <c r="F275" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G275" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H275" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I275" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B276" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C276" s="16" t="inlineStr">
@@ -14834,132 +14884,132 @@
       </c>
       <c r="D276" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E276" s="17" t="n">
-        <v>0.396551724137931</v>
+        <v>0.546075036075036</v>
       </c>
       <c r="F276" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G276" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H276" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I276" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B277" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C277" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D277" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E277" s="17" t="n">
-        <v>0</v>
+        <v>0.634534632034632</v>
       </c>
       <c r="F277" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G277" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H277" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I277" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B278" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C278" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D278" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E278" s="17" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.5719417862838915</v>
       </c>
       <c r="F278" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G278" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H278" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I278" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B279" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C279" s="16" t="inlineStr">
@@ -14969,42 +15019,42 @@
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E279" s="17" t="n">
-        <v>0.6258503401360545</v>
+        <v>0.8543052605446494</v>
       </c>
       <c r="F279" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G279" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H279" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I279" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B280" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C280" s="16" t="inlineStr">
@@ -15014,402 +15064,402 @@
       </c>
       <c r="D280" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E280" s="17" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.8565473598042608</v>
       </c>
       <c r="F280" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G280" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H280" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I280" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B281" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C281" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D281" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E281" s="17" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.8109429700734049</v>
       </c>
       <c r="F281" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G281" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H281" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I281" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B282" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C282" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D282" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E282" s="17" t="n">
-        <v>0.7552447552447553</v>
+        <v>0.8020237849525775</v>
       </c>
       <c r="F282" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G282" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H282" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I282" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B283" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C283" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D283" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E283" s="17" t="n">
-        <v>0.6923076923076924</v>
+        <v>0.8465966593792681</v>
       </c>
       <c r="F283" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G283" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H283" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I283" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B284" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C284" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D284" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E284" s="17" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7481770520323419</v>
       </c>
       <c r="F284" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G284" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H284" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I284" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B285" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C285" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D285" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E285" s="17" t="n">
-        <v>0.7086031452358927</v>
+        <v>0.9250894033502728</v>
       </c>
       <c r="F285" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G285" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H285" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I285" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B286" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C286" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D286" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E286" s="17" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.9841269841269842</v>
       </c>
       <c r="F286" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G286" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H286" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I286" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B287" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C287" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D287" s="16" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E287" s="17" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.951555023923445</v>
       </c>
       <c r="F287" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G287" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H287" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I287" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B288" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C288" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D288" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E288" s="17" t="n">
-        <v>0.7822222222222222</v>
+        <v>0.9583694083694084</v>
       </c>
       <c r="F288" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G288" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H288" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I288" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B289" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C289" s="16" t="inlineStr">
@@ -15419,42 +15469,42 @@
       </c>
       <c r="D289" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E289" s="17" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.9538999012683224</v>
       </c>
       <c r="F289" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G289" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H289" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I289" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="16" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B290" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C290" s="16" t="inlineStr">
@@ -15464,132 +15514,132 @@
       </c>
       <c r="D290" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E290" s="17" t="n">
-        <v>0.8</v>
+        <v>0.9245881502174408</v>
       </c>
       <c r="F290" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G290" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H290" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I290" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B291" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C291" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D291" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E291" s="17" t="n">
-        <v>0.5716783216783217</v>
+        <v>0.6311408199643493</v>
       </c>
       <c r="F291" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G291" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H291" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I291" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B292" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C292" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D292" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E292" s="17" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.6819372214116374</v>
       </c>
       <c r="F292" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G292" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H292" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I292" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B293" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C293" s="16" t="inlineStr">
@@ -15599,42 +15649,42 @@
       </c>
       <c r="D293" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E293" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5145072673913382</v>
       </c>
       <c r="F293" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G293" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H293" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I293" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B294" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C294" s="16" t="inlineStr">
@@ -15644,127 +15694,127 @@
       </c>
       <c r="D294" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E294" s="17" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5670524643859309</v>
       </c>
       <c r="F294" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G294" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H294" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I294" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B295" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C295" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D295" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E295" s="17" t="n">
-        <v>0.5</v>
+        <v>0.5892365572441474</v>
       </c>
       <c r="F295" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G295" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H295" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I295" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B296" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C296" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D296" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E296" s="17" t="n">
-        <v>0.4484848484848484</v>
+        <v>0.5208317121475016</v>
       </c>
       <c r="F296" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G296" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H296" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I296" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B297" s="16" t="inlineStr">
@@ -15774,42 +15824,42 @@
       </c>
       <c r="C297" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D297" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E297" s="17" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.715725806451613</v>
       </c>
       <c r="F297" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G297" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H297" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I297" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B298" s="16" t="inlineStr">
@@ -15819,42 +15869,42 @@
       </c>
       <c r="C298" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D298" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E298" s="17" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.8156862745098039</v>
       </c>
       <c r="F298" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G298" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H298" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I298" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B299" s="16" t="inlineStr">
@@ -15869,37 +15919,37 @@
       </c>
       <c r="D299" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E299" s="17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5761273209549072</v>
       </c>
       <c r="F299" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G299" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H299" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I299" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B300" s="16" t="inlineStr">
@@ -15914,37 +15964,37 @@
       </c>
       <c r="D300" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E300" s="17" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.7257294429708223</v>
       </c>
       <c r="F300" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G300" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H300" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I300" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B301" s="16" t="inlineStr">
@@ -15954,42 +16004,42 @@
       </c>
       <c r="C301" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D301" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E301" s="17" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.7257294429708223</v>
       </c>
       <c r="F301" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G301" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H301" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I301" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B302" s="16" t="inlineStr">
@@ -15999,407 +16049,407 @@
       </c>
       <c r="C302" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D302" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E302" s="17" t="n">
-        <v>0.5</v>
+        <v>0.7696078431372548</v>
       </c>
       <c r="F302" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G302" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H302" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I302" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B303" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C303" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D303" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E303" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.598161968750204</v>
       </c>
       <c r="F303" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G303" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H303" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/d3tec_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I303" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B304" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C304" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D304" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E304" s="17" t="n">
-        <v>0.625</v>
+        <v>0.5467279942279942</v>
       </c>
       <c r="F304" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G304" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H304" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/d3tec_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I304" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B305" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C305" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D305" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E305" s="17" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5289319014319014</v>
       </c>
       <c r="F305" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G305" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H305" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/d3tec_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I305" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B306" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C306" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D306" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E306" s="17" t="n">
-        <v>0.396551724137931</v>
+        <v>0.5599448942869996</v>
       </c>
       <c r="F306" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G306" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H306" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/d3tec_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I306" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B307" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C307" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D307" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E307" s="17" t="n">
-        <v>0</v>
+        <v>0.8727292418997225</v>
       </c>
       <c r="F307" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G307" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H307" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/androids_interview_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I307" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B308" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C308" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D308" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E308" s="17" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.9027865444158352</v>
       </c>
       <c r="F308" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G308" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H308" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/androids_interview_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I308" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B309" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C309" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D309" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E309" s="17" t="n">
-        <v>0</v>
+        <v>0.8111428571428572</v>
       </c>
       <c r="F309" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G309" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H309" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/androids_interview_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I309" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B310" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C310" s="16" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D310" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E310" s="17" t="n">
-        <v>0</v>
+        <v>0.808360039884658</v>
       </c>
       <c r="F310" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G310" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H310" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/androids_interview_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I310" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B311" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C311" s="16" t="inlineStr">
@@ -16409,42 +16459,42 @@
       </c>
       <c r="D311" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E311" s="17" t="n">
-        <v>0.6577777777777778</v>
+        <v>0.9133968253968254</v>
       </c>
       <c r="F311" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G311" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H311" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/cmdc_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I311" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B312" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C312" s="16" t="inlineStr">
@@ -16454,132 +16504,132 @@
       </c>
       <c r="D312" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E312" s="17" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.9682539682539684</v>
       </c>
       <c r="F312" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G312" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H312" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/cmdc_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I312" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B313" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C313" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D313" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E313" s="17" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.9697729171413382</v>
       </c>
       <c r="F313" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G313" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H313" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/cmdc_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I313" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B314" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C314" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D314" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E314" s="17" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.9397729171413381</v>
       </c>
       <c r="F314" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G314" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H314" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/cmdc_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I314" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B315" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C315" s="16" t="inlineStr">
@@ -16589,42 +16639,42 @@
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E315" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6287301587301588</v>
       </c>
       <c r="F315" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G315" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H315" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/turkish_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I315" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B316" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C316" s="16" t="inlineStr">
@@ -16634,132 +16684,132 @@
       </c>
       <c r="D316" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E316" s="17" t="n">
-        <v>0.5304437564499485</v>
+        <v>0.5927987489058097</v>
       </c>
       <c r="F316" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G316" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H316" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/turkish_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I316" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B317" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C317" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D317" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E317" s="17" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.6584416576992479</v>
       </c>
       <c r="F317" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G317" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H317" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/turkish_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I317" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B318" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C318" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D318" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E318" s="17" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.6296220712136271</v>
       </c>
       <c r="F318" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G318" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H318" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/turkish_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I318" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B319" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C319" s="16" t="inlineStr">
@@ -16769,42 +16819,42 @@
       </c>
       <c r="D319" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E319" s="17" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.7411720992361243</v>
       </c>
       <c r="F319" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G319" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H319" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_text_cv_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I319" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B320" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C320" s="16" t="inlineStr">
@@ -16814,42 +16864,42 @@
       </c>
       <c r="D320" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E320" s="17" t="n">
-        <v>0.25</v>
+        <v>0.7644488625062797</v>
       </c>
       <c r="F320" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G320" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H320" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_text_cv_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I320" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B321" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C321" s="16" t="inlineStr">
@@ -16859,42 +16909,42 @@
       </c>
       <c r="D321" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E321" s="17" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.7431693989071039</v>
       </c>
       <c r="F321" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G321" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H321" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_text_final_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I321" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B322" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C322" s="16" t="inlineStr">
@@ -16904,397 +16954,397 @@
       </c>
       <c r="D322" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E322" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7456709956709957</v>
       </c>
       <c r="F322" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G322" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H322" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_text_final_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I322" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B323" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C323" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D323" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E323" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7473717357888511</v>
       </c>
       <c r="F323" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G323" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H323" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_only_cv_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I323" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B324" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C324" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D324" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E324" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.700813968808538</v>
       </c>
       <c r="F324" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G324" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H324" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_only_cv_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I324" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B325" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C325" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D325" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E325" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4727564102564102</v>
       </c>
       <c r="F325" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G325" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H325" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_only_final_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I325" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B326" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C326" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D326" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E326" s="17" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.5554054054054054</v>
       </c>
       <c r="F326" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G326" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H326" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_only_final_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I326" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B327" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C327" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D327" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E327" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7602906132436795</v>
       </c>
       <c r="F327" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G327" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H327" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/text_only_cv_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I327" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B328" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C328" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D328" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E328" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7657973784875042</v>
       </c>
       <c r="F328" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G328" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H328" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/text_only_cv_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I328" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B329" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C329" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D329" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E329" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7552083333333333</v>
       </c>
       <c r="F329" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G329" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H329" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/text_only_final_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I329" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B330" s="16" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C330" s="16" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D330" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E330" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7631048387096775</v>
       </c>
       <c r="F330" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G330" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H330" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/text_only_final_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I330" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B331" s="16" t="inlineStr">
@@ -17304,42 +17354,42 @@
       </c>
       <c r="C331" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D331" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E331" s="17" t="n">
-        <v>0.6938775510204083</v>
+        <v>0.5304437564499485</v>
       </c>
       <c r="F331" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G331" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H331" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I331" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B332" s="16" t="inlineStr">
@@ -17349,42 +17399,42 @@
       </c>
       <c r="C332" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D332" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E332" s="17" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.6829710144927537</v>
       </c>
       <c r="F332" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G332" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H332" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I332" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B333" s="16" t="inlineStr">
@@ -17394,42 +17444,42 @@
       </c>
       <c r="C333" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D333" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E333" s="17" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.5726970033296338</v>
       </c>
       <c r="F333" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G333" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H333" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I333" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B334" s="16" t="inlineStr">
@@ -17439,42 +17489,42 @@
       </c>
       <c r="C334" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D334" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E334" s="17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6685606060606061</v>
       </c>
       <c r="F334" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G334" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H334" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I334" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B335" s="16" t="inlineStr">
@@ -17489,37 +17539,37 @@
       </c>
       <c r="D335" s="16" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E335" s="17" t="n">
-        <v>0.5</v>
+        <v>0.674922600619195</v>
       </c>
       <c r="F335" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G335" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H335" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I335" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B336" s="16" t="inlineStr">
@@ -17534,37 +17584,37 @@
       </c>
       <c r="D336" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E336" s="17" t="n">
-        <v>0.6026831785345718</v>
+        <v>0.7086031452358927</v>
       </c>
       <c r="F336" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G336" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H336" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I336" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B337" s="16" t="inlineStr">
@@ -17574,42 +17624,42 @@
       </c>
       <c r="C337" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D337" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E337" s="17" t="n">
-        <v>0.4210526315789474</v>
+        <v>0.3859649122807018</v>
       </c>
       <c r="F337" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G337" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H337" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I337" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B338" s="16" t="inlineStr">
@@ -17619,42 +17669,42 @@
       </c>
       <c r="C338" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D338" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E338" s="17" t="n">
-        <v>0.6857142857142857</v>
+        <v>0</v>
       </c>
       <c r="F338" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G338" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H338" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I338" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B339" s="16" t="inlineStr">
@@ -17664,42 +17714,42 @@
       </c>
       <c r="C339" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D339" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E339" s="17" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F339" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G339" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H339" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I339" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B340" s="16" t="inlineStr">
@@ -17709,42 +17759,42 @@
       </c>
       <c r="C340" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D340" s="16" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E340" s="17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F340" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G340" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H340" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I340" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B341" s="16" t="inlineStr">
@@ -17754,42 +17804,42 @@
       </c>
       <c r="C341" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D341" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E341" s="17" t="n">
-        <v>0.7619047619047619</v>
+        <v>0</v>
       </c>
       <c r="F341" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G341" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H341" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I341" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B342" s="16" t="inlineStr">
@@ -17799,42 +17849,42 @@
       </c>
       <c r="C342" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D342" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E342" s="17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="F342" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G342" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H342" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I342" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B343" s="16" t="inlineStr">
@@ -17844,42 +17894,42 @@
       </c>
       <c r="C343" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D343" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E343" s="17" t="n">
-        <v>0.8</v>
+        <v>0.6258503401360545</v>
       </c>
       <c r="F343" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G343" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H343" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I343" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B344" s="16" t="inlineStr">
@@ -17889,42 +17939,42 @@
       </c>
       <c r="C344" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D344" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E344" s="17" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="F344" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G344" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H344" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I344" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B345" s="16" t="inlineStr">
@@ -17934,42 +17984,42 @@
       </c>
       <c r="C345" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D345" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E345" s="17" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F345" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G345" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H345" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I345" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B346" s="16" t="inlineStr">
@@ -17979,42 +18029,42 @@
       </c>
       <c r="C346" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D346" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E346" s="17" t="n">
-        <v>0.6685606060606061</v>
+        <v>0.7552447552447553</v>
       </c>
       <c r="F346" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G346" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H346" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I346" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B347" s="16" t="inlineStr">
@@ -18024,42 +18074,42 @@
       </c>
       <c r="C347" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D347" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E347" s="17" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="F347" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G347" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H347" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I347" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B348" s="16" t="inlineStr">
@@ -18069,42 +18119,42 @@
       </c>
       <c r="C348" s="16" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D348" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E348" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="F348" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G348" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H348" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I348" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="16" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B349" s="16" t="inlineStr">
@@ -18119,73 +18169,2953 @@
       </c>
       <c r="D349" s="16" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E349" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7086031452358927</v>
       </c>
       <c r="F349" s="18" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G349" s="18" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H349" s="18" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I349" s="18" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="16" t="inlineStr">
         <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B350" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C350" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D350" s="16" t="inlineStr">
+        <is>
+          <t>Qwen teacher-forced positive-F1</t>
+        </is>
+      </c>
+      <c r="E350" s="17" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="F350" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+        </is>
+      </c>
+      <c r="G350" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H350" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I350" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="16" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B351" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C351" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D351" s="16" t="inlineStr">
+        <is>
+          <t>Qwen teacher-forced accuracy</t>
+        </is>
+      </c>
+      <c r="E351" s="17" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="F351" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+        </is>
+      </c>
+      <c r="G351" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H351" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I351" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="16" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B352" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C352" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D352" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 teacher-forced macro-F1</t>
+        </is>
+      </c>
+      <c r="E352" s="17" t="n">
+        <v>0.7822222222222222</v>
+      </c>
+      <c r="F352" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+        </is>
+      </c>
+      <c r="G352" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H352" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I352" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="16" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B353" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C353" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D353" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 teacher-forced positive-F1</t>
+        </is>
+      </c>
+      <c r="E353" s="17" t="n">
+        <v>0.7199999999999999</v>
+      </c>
+      <c r="F353" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+        </is>
+      </c>
+      <c r="G353" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H353" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I353" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="16" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B354" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C354" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D354" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 teacher-forced accuracy</t>
+        </is>
+      </c>
+      <c r="E354" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F354" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+        </is>
+      </c>
+      <c r="G354" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H354" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I354" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="16" t="inlineStr">
+        <is>
           <t>DAIC Head Ablation</t>
         </is>
       </c>
-      <c r="B350" s="16" t="inlineStr">
+      <c r="B355" s="16" t="inlineStr">
         <is>
           <t>DAIC</t>
         </is>
       </c>
-      <c r="C350" s="16" t="inlineStr">
+      <c r="C355" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D355" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E355" s="17" t="n">
+        <v>0.5716783216783217</v>
+      </c>
+      <c r="F355" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G355" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H355" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I355" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B356" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C356" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D356" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E356" s="17" t="n">
+        <v>0.4615384615384615</v>
+      </c>
+      <c r="F356" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G356" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H356" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I356" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B357" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C357" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D357" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E357" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F357" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G357" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H357" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I357" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B358" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C358" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D358" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E358" s="17" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="F358" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G358" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H358" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I358" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B359" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C359" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D359" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E359" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F359" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G359" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H359" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I359" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B360" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C360" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D360" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E360" s="17" t="n">
+        <v>0.4484848484848484</v>
+      </c>
+      <c r="F360" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G360" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H360" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I360" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B361" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C361" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D361" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E361" s="17" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="F361" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G361" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H361" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I361" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B362" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C362" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D362" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E362" s="17" t="n">
+        <v>0.6285714285714286</v>
+      </c>
+      <c r="F362" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G362" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H362" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I362" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B363" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C363" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D363" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E363" s="17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F363" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G363" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H363" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I363" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B364" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C364" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D364" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E364" s="17" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="F364" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G364" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H364" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I364" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B365" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C365" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D365" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E365" s="17" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="F365" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G365" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H365" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I365" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B366" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C366" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D366" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E366" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F366" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G366" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H366" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I366" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B367" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C367" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D367" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E367" s="17" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F367" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G367" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H367" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I367" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B368" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C368" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D368" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E368" s="17" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F368" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G368" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H368" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I368" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B369" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C369" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D369" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E369" s="17" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="F369" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G369" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H369" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I369" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B370" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C370" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D370" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E370" s="17" t="n">
+        <v>0.396551724137931</v>
+      </c>
+      <c r="F370" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G370" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H370" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I370" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B371" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C371" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D371" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E371" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F371" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G371" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H371" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I371" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B372" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C372" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D372" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E372" s="17" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="F372" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G372" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H372" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I372" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B373" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C373" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D373" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E373" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F373" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G373" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H373" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I373" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B374" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C374" s="16" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D374" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E374" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F374" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G374" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H374" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I374" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B375" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C375" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D375" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E375" s="17" t="n">
+        <v>0.6577777777777778</v>
+      </c>
+      <c r="F375" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G375" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H375" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I375" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B376" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C376" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D376" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E376" s="17" t="n">
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="F376" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G376" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H376" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I376" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B377" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C377" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D377" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E377" s="17" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="F377" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G377" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H377" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I377" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B378" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C378" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D378" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E378" s="17" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="F378" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G378" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H378" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I378" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B379" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C379" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D379" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E379" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F379" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G379" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H379" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I379" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B380" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C380" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D380" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E380" s="17" t="n">
+        <v>0.5304437564499485</v>
+      </c>
+      <c r="F380" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G380" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H380" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I380" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B381" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C381" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D381" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E381" s="17" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="F381" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G381" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H381" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I381" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B382" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C382" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D382" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E382" s="17" t="n">
+        <v>0.6285714285714286</v>
+      </c>
+      <c r="F382" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G382" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H382" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I382" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B383" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C383" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D383" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E383" s="17" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="F383" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G383" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H383" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I383" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B384" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C384" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D384" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E384" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F384" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G384" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H384" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I384" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B385" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C385" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D385" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E385" s="17" t="n">
+        <v>0.6829710144927537</v>
+      </c>
+      <c r="F385" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G385" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H385" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I385" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B386" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C386" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D386" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E386" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F386" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G386" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H386" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I386" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B387" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C387" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D387" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E387" s="17" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F387" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G387" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H387" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I387" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B388" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C388" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D388" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E388" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F388" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G388" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H388" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I388" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B389" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C389" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D389" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E389" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F389" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G389" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H389" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I389" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B390" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C390" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D390" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E390" s="17" t="n">
+        <v>0.6829710144927537</v>
+      </c>
+      <c r="F390" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G390" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H390" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I390" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B391" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C391" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D391" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E391" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F391" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G391" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H391" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I391" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B392" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C392" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D392" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E392" s="17" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F392" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G392" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H392" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I392" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B393" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C393" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D393" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E393" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F393" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G393" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H393" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I393" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B394" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C394" s="16" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D394" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E394" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F394" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G394" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H394" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I394" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B395" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C395" s="16" t="inlineStr">
         <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="D350" s="16" t="inlineStr">
+      <c r="D395" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E395" s="17" t="n">
+        <v>0.6938775510204083</v>
+      </c>
+      <c r="F395" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G395" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H395" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I395" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B396" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C396" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D396" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E396" s="17" t="n">
+        <v>0.5714285714285715</v>
+      </c>
+      <c r="F396" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G396" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H396" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I396" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B397" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C397" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D397" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E397" s="17" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="F397" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G397" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H397" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I397" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B398" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C398" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D398" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E398" s="17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F398" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G398" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H398" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I398" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B399" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C399" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D399" s="16" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E399" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F399" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G399" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H399" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I399" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B400" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C400" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D400" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E400" s="17" t="n">
+        <v>0.6026831785345718</v>
+      </c>
+      <c r="F400" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G400" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H400" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I400" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B401" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C401" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D401" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E401" s="17" t="n">
+        <v>0.4210526315789474</v>
+      </c>
+      <c r="F401" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G401" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H401" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I401" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B402" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C402" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D402" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E402" s="17" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="F402" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G402" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H402" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I402" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B403" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C403" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D403" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E403" s="17" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F403" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G403" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H403" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I403" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B404" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C404" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D404" s="16" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E404" s="17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F404" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G404" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H404" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I404" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B405" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C405" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D405" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E405" s="17" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="F405" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G405" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H405" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I405" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B406" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C406" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D406" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E406" s="17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F406" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G406" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H406" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I406" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B407" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C407" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D407" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E407" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F407" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G407" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H407" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I407" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B408" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C408" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D408" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E408" s="17" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="F408" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G408" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H408" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I408" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B409" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C409" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D409" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E409" s="17" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F409" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G409" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H409" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I409" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B410" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C410" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D410" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E410" s="17" t="n">
+        <v>0.6685606060606061</v>
+      </c>
+      <c r="F410" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G410" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H410" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I410" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B411" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C411" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D411" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E411" s="17" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="F411" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G411" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H411" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I411" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B412" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C412" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D412" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E412" s="17" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F412" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G412" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H412" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I412" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B413" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C413" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D413" s="16" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E413" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F413" s="18" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G413" s="18" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H413" s="18" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I413" s="18" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="16" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B414" s="16" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C414" s="16" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D414" s="16" t="inlineStr">
         <is>
           <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
-      <c r="E350" s="17" t="n">
+      <c r="E414" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="F350" s="18" t="inlineStr">
+      <c r="F414" s="18" t="inlineStr">
         <is>
           <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
-      <c r="G350" s="18" t="inlineStr">
+      <c r="G414" s="18" t="inlineStr">
         <is>
           <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
-      <c r="H350" s="18" t="inlineStr">
+      <c r="H414" s="18" t="inlineStr">
         <is>
           <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
-      <c r="I350" s="18" t="inlineStr">
+      <c r="I414" s="18" t="inlineStr">
         <is>
           <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1211,7 +1211,7 @@
     <row r="2" ht="110" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Three main experiments, both models, macro-F1 (binary-strict, best_model, harmonized view). XGBoost uses the standardized search of 100 trials (the default), seed 1337, for both models; the runbook fits no fixed XGB head for Gemma. Delta = Gemma minus Qwen. DAIC = official 47-subject test; CMDC/Turkish = 5-fold mean (train_val); D3TEC/Androids = pooled 5-fold subject-level; merged CV = mean over the five datasets; merged Final = DAIC official test. The merged final teacher-forced test evaluation was not produced as a separate artifact for Gemma, so that row is omitted. Per-cell provenance: Provenance sheet.</t>
+          <t>Three main experiments, both models, macro-F1 (binary-strict, best_model, harmonized view). XGBoost uses the standardized search of 100 trials (the default), seed 1337, for both models; the runbook fits no fixed XGB head for Gemma. Delta = Gemma minus Qwen. DAIC = official 47-subject test; CMDC/Turkish = 5-fold mean (train_val); D3TEC/Androids = pooled 5-fold subject-level; merged CV = mean over the five datasets; merged Final = DAIC official test. Per-cell provenance: Provenance sheet.</t>
         </is>
       </c>
     </row>
@@ -2958,17 +2958,17 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>0.7432</v>
+        <v>0.7631</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.7834101382488479</v>
-      </c>
-      <c r="G61" s="7" t="n">
-        <v>0.0402</v>
+        <v>0.7257294429708223</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>-0.0374</v>
       </c>
     </row>
     <row r="62">
@@ -2989,17 +2989,17 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0.743235</v>
+        <v>0.7432</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.745671</v>
+        <v>0.7834101382488479</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>0.0024</v>
+        <v>0.0402</v>
       </c>
     </row>
     <row r="63">
@@ -3015,22 +3015,22 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0.6189</v>
+        <v>0.743235</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.4283783783783783</v>
-      </c>
-      <c r="G63" s="8" t="n">
-        <v>-0.1905</v>
+        <v>0.745671</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>0.0024</v>
       </c>
     </row>
     <row r="64">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>0.472823</v>
+        <v>0.5332</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.555405</v>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.5190058479532164</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>-0.0142</v>
       </c>
     </row>
     <row r="65">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>0.7157</v>
+        <v>0.6189</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>0.70625</v>
+        <v>0.4283783783783783</v>
       </c>
       <c r="G65" s="8" t="n">
-        <v>-0.0094</v>
+        <v>-0.1905</v>
       </c>
     </row>
     <row r="66">
@@ -3108,122 +3108,122 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>0.472823</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>0.555405</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Merged — Final (DAIC test)</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>0.755208</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>0.763105</v>
-      </c>
-      <c r="G66" s="7" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>English (translated)</t>
-        </is>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>0.7756</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>0.7755968169761273</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Merged — Final (DAIC test)</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>Merged</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>0.6125</v>
+        <v>0.7157</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.564983</v>
+        <v>0.70625</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>-0.0475</v>
+        <v>-0.0094</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Merged — Final (DAIC test)</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>Merged</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.5464</v>
+        <v>0.755208</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>0.532292</v>
-      </c>
-      <c r="G69" s="8" t="n">
-        <v>-0.0141</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>D3TEC</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="n">
-        <v>0.5982</v>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>0.546749</v>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>-0.0515</v>
+        <v>0.763105</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>English (translated)</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>0.5465</v>
+        <v>0.6125</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.4936</v>
+        <v>0.564983</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>-0.0529</v>
+        <v>-0.0475</v>
       </c>
     </row>
     <row r="72">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>0.5226</v>
+        <v>0.5464</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.596902</v>
-      </c>
-      <c r="G72" s="7" t="n">
-        <v>0.0743</v>
+        <v>0.532292</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>-0.0141</v>
       </c>
     </row>
     <row r="73">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3310,13 +3310,13 @@
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>0.5289</v>
+        <v>0.5982</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0.5599460000000001</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>0.031</v>
+        <v>0.546749</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>-0.0515</v>
       </c>
     </row>
     <row r="74">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3341,13 +3341,13 @@
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>0.8873</v>
+        <v>0.5465</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.876968</v>
+        <v>0.4936</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>-0.0103</v>
+        <v>-0.0529</v>
       </c>
     </row>
     <row r="75">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>0.8802</v>
+        <v>0.5226</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.902794</v>
+        <v>0.596902</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>0.0226</v>
+        <v>0.0743</v>
       </c>
     </row>
     <row r="76">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>0.8727</v>
+        <v>0.5289</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.902794</v>
+        <v>0.5599460000000001</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0.0301</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="77">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3434,13 +3434,13 @@
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>0.7921</v>
+        <v>0.8873</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.744654</v>
+        <v>0.876968</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>-0.0474</v>
+        <v>-0.0103</v>
       </c>
     </row>
     <row r="78">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3465,13 +3465,13 @@
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>0.8298</v>
+        <v>0.8802</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.83016</v>
-      </c>
-      <c r="G78" s="10" t="n">
-        <v>0.0004</v>
+        <v>0.902794</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>0.0226</v>
       </c>
     </row>
     <row r="79">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>0.8111</v>
+        <v>0.8727</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.808427</v>
-      </c>
-      <c r="G79" s="8" t="n">
-        <v>-0.0027</v>
+        <v>0.902794</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>0.0301</v>
       </c>
     </row>
     <row r="80">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>0.9856</v>
+        <v>0.7921</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.955419</v>
+        <v>0.744654</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>-0.0302</v>
+        <v>-0.0474</v>
       </c>
     </row>
     <row r="81">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>0.9856</v>
+        <v>0.8298</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0.9263479999999999</v>
-      </c>
-      <c r="G81" s="8" t="n">
-        <v>-0.0593</v>
+        <v>0.83016</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>0.0004</v>
       </c>
     </row>
     <row r="82">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>0.9134</v>
+        <v>0.8111</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>0.96828</v>
-      </c>
-      <c r="G82" s="7" t="n">
-        <v>0.0549</v>
+        <v>0.808427</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>-0.0027</v>
       </c>
     </row>
     <row r="83">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3620,13 +3620,13 @@
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9856</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.957439</v>
+        <v>0.955419</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>-0.0139</v>
+        <v>-0.0302</v>
       </c>
     </row>
     <row r="84">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>0.9698</v>
+        <v>0.9856</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.969835</v>
-      </c>
-      <c r="G84" s="10" t="n">
-        <v>0</v>
+        <v>0.9263479999999999</v>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>-0.0593</v>
       </c>
     </row>
     <row r="85">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3682,13 +3682,13 @@
         </is>
       </c>
       <c r="E85" s="6" t="n">
-        <v>0.9698</v>
+        <v>0.9134</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0.939796</v>
-      </c>
-      <c r="G85" s="8" t="n">
-        <v>-0.03</v>
+        <v>0.96828</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>0.0549</v>
       </c>
     </row>
     <row r="86">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>0.669119</v>
-      </c>
-      <c r="G86" s="7" t="n">
-        <v>0.0396</v>
+        <v>0.957439</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>-0.0139</v>
       </c>
     </row>
     <row r="87">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>0.6076</v>
+        <v>0.9698</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0.599564</v>
-      </c>
-      <c r="G87" s="8" t="n">
-        <v>-0.008</v>
+        <v>0.969835</v>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -3775,13 +3775,13 @@
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>0.6287</v>
+        <v>0.9698</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.592804</v>
+        <v>0.939796</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>-0.0359</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="89">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0.6641</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0.6774</v>
+        <v>0.669119</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>0.0133</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="90">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -3837,13 +3837,13 @@
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>0.5944</v>
+        <v>0.6076</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>0.6014350000000001</v>
-      </c>
-      <c r="G90" s="7" t="n">
-        <v>0.007</v>
+        <v>0.599564</v>
+      </c>
+      <c r="G90" s="8" t="n">
+        <v>-0.008</v>
       </c>
     </row>
     <row r="91">
@@ -3859,26 +3859,119 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>0.6287</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>0.592804</v>
+      </c>
+      <c r="G91" s="8" t="n">
+        <v>-0.0359</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
           <t>Text only</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>0.6774</v>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>0.0133</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>0.5944</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>0.6014350000000001</v>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="E94" s="6" t="n">
         <v>0.6584</v>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="F94" s="6" t="n">
         <v>0.629565</v>
       </c>
-      <c r="G91" s="8" t="n">
+      <c r="G94" s="8" t="n">
         <v>-0.0288</v>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Teacher-forced = backbone classification without hidden-state heads. Hidden heads classify the final prompt-token hidden state with the locked LogReg or the standardized XGBoost implementation. See the Provenance sheet for every value's run, aggregation, and local artifact.</t>
         </is>
@@ -3887,8 +3980,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A95:G95"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A5:G5"/>
@@ -4418,7 +4511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I436"/>
+  <dimension ref="A1:I442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20527,102 +20620,102 @@
     <row r="359">
       <c r="A359" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B359" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C359" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D359" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E359" s="12" t="n">
-        <v>0.3859649122807018</v>
+        <v>0.7257294429708223</v>
       </c>
       <c r="F359" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684476, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G359" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H359" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I359" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B360" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C360" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D360" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E360" s="12" t="n">
-        <v>0</v>
+        <v>0.7834101382488479</v>
       </c>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G360" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H360" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I360" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B361" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C361" s="11" t="inlineStr">
@@ -20632,42 +20725,42 @@
       </c>
       <c r="D361" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E361" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5190058479532164</v>
       </c>
       <c r="F361" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684479, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G361" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H361" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I361" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B362" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C362" s="11" t="inlineStr">
@@ -20677,120 +20770,120 @@
       </c>
       <c r="D362" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E362" s="12" t="n">
-        <v>0.396551724137931</v>
+        <v>0.4283783783783783</v>
       </c>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G362" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H362" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I362" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B363" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C363" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D363" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E363" s="12" t="n">
-        <v>0</v>
+        <v>0.7755968169761273</v>
       </c>
       <c r="F363" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684482, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G363" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H363" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I363" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B364" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C364" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D364" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E364" s="12" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.70625</v>
       </c>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G364" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H364" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I364" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
@@ -20807,7 +20900,7 @@
       </c>
       <c r="C365" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D365" s="11" t="inlineStr">
@@ -20816,11 +20909,11 @@
         </is>
       </c>
       <c r="E365" s="12" t="n">
-        <v>0.6258503401360545</v>
+        <v>0.3859649122807018</v>
       </c>
       <c r="F365" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G365" s="13" t="inlineStr">
@@ -20830,7 +20923,7 @@
       </c>
       <c r="H365" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I365" s="13" t="inlineStr">
@@ -20852,7 +20945,7 @@
       </c>
       <c r="C366" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D366" s="11" t="inlineStr">
@@ -20861,11 +20954,11 @@
         </is>
       </c>
       <c r="E366" s="12" t="n">
-        <v>0.4761904761904762</v>
+        <v>0</v>
       </c>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G366" s="13" t="inlineStr">
@@ -20875,7 +20968,7 @@
       </c>
       <c r="H366" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I366" s="13" t="inlineStr">
@@ -20897,7 +20990,7 @@
       </c>
       <c r="C367" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D367" s="11" t="inlineStr">
@@ -20906,11 +20999,11 @@
         </is>
       </c>
       <c r="E367" s="12" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F367" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G367" s="13" t="inlineStr">
@@ -20920,7 +21013,7 @@
       </c>
       <c r="H367" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I367" s="13" t="inlineStr">
@@ -20942,7 +21035,7 @@
       </c>
       <c r="C368" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D368" s="11" t="inlineStr">
@@ -20951,11 +21044,11 @@
         </is>
       </c>
       <c r="E368" s="12" t="n">
-        <v>0.7552447552447553</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G368" s="13" t="inlineStr">
@@ -20965,7 +21058,7 @@
       </c>
       <c r="H368" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I368" s="13" t="inlineStr">
@@ -20987,7 +21080,7 @@
       </c>
       <c r="C369" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D369" s="11" t="inlineStr">
@@ -20996,11 +21089,11 @@
         </is>
       </c>
       <c r="E369" s="12" t="n">
-        <v>0.6923076923076924</v>
+        <v>0</v>
       </c>
       <c r="F369" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G369" s="13" t="inlineStr">
@@ -21010,7 +21103,7 @@
       </c>
       <c r="H369" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I369" s="13" t="inlineStr">
@@ -21032,7 +21125,7 @@
       </c>
       <c r="C370" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D370" s="11" t="inlineStr">
@@ -21041,11 +21134,11 @@
         </is>
       </c>
       <c r="E370" s="12" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G370" s="13" t="inlineStr">
@@ -21055,7 +21148,7 @@
       </c>
       <c r="H370" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I370" s="13" t="inlineStr">
@@ -21077,7 +21170,7 @@
       </c>
       <c r="C371" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D371" s="11" t="inlineStr">
@@ -21086,11 +21179,11 @@
         </is>
       </c>
       <c r="E371" s="12" t="n">
-        <v>0.7086031452358927</v>
+        <v>0.6258503401360545</v>
       </c>
       <c r="F371" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G371" s="13" t="inlineStr">
@@ -21100,7 +21193,7 @@
       </c>
       <c r="H371" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I371" s="13" t="inlineStr">
@@ -21122,7 +21215,7 @@
       </c>
       <c r="C372" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D372" s="11" t="inlineStr">
@@ -21131,11 +21224,11 @@
         </is>
       </c>
       <c r="E372" s="12" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G372" s="13" t="inlineStr">
@@ -21145,7 +21238,7 @@
       </c>
       <c r="H372" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I372" s="13" t="inlineStr">
@@ -21167,7 +21260,7 @@
       </c>
       <c r="C373" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D373" s="11" t="inlineStr">
@@ -21176,11 +21269,11 @@
         </is>
       </c>
       <c r="E373" s="12" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F373" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G373" s="13" t="inlineStr">
@@ -21190,7 +21283,7 @@
       </c>
       <c r="H373" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I373" s="13" t="inlineStr">
@@ -21212,7 +21305,7 @@
       </c>
       <c r="C374" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D374" s="11" t="inlineStr">
@@ -21221,11 +21314,11 @@
         </is>
       </c>
       <c r="E374" s="12" t="n">
-        <v>0.7822222222222222</v>
+        <v>0.7552447552447553</v>
       </c>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G374" s="13" t="inlineStr">
@@ -21235,7 +21328,7 @@
       </c>
       <c r="H374" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I374" s="13" t="inlineStr">
@@ -21257,7 +21350,7 @@
       </c>
       <c r="C375" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D375" s="11" t="inlineStr">
@@ -21266,11 +21359,11 @@
         </is>
       </c>
       <c r="E375" s="12" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="F375" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G375" s="13" t="inlineStr">
@@ -21280,7 +21373,7 @@
       </c>
       <c r="H375" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I375" s="13" t="inlineStr">
@@ -21302,7 +21395,7 @@
       </c>
       <c r="C376" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D376" s="11" t="inlineStr">
@@ -21311,11 +21404,11 @@
         </is>
       </c>
       <c r="E376" s="12" t="n">
-        <v>0.8</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G376" s="13" t="inlineStr">
@@ -21325,7 +21418,7 @@
       </c>
       <c r="H376" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I376" s="13" t="inlineStr">
@@ -21337,7 +21430,7 @@
     <row r="377">
       <c r="A377" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B377" s="11" t="inlineStr">
@@ -21347,42 +21440,42 @@
       </c>
       <c r="C377" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D377" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E377" s="12" t="n">
-        <v>0.5716783216783217</v>
+        <v>0.7086031452358927</v>
       </c>
       <c r="F377" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G377" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H377" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I377" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B378" s="11" t="inlineStr">
@@ -21392,42 +21485,42 @@
       </c>
       <c r="C378" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D378" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E378" s="12" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="F378" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G378" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H378" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I378" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B379" s="11" t="inlineStr">
@@ -21437,42 +21530,42 @@
       </c>
       <c r="C379" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D379" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E379" s="12" t="n">
-        <v>0.6</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="F379" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G379" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H379" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I379" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B380" s="11" t="inlineStr">
@@ -21482,42 +21575,42 @@
       </c>
       <c r="C380" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D380" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E380" s="12" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.7822222222222222</v>
       </c>
       <c r="F380" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G380" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H380" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I380" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B381" s="11" t="inlineStr">
@@ -21527,42 +21620,42 @@
       </c>
       <c r="C381" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D381" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E381" s="12" t="n">
-        <v>0.5</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="F381" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G381" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H381" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I381" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B382" s="11" t="inlineStr">
@@ -21572,35 +21665,35 @@
       </c>
       <c r="C382" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D382" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E382" s="12" t="n">
-        <v>0.4484848484848484</v>
+        <v>0.8</v>
       </c>
       <c r="F382" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G382" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H382" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I382" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
@@ -21622,15 +21715,15 @@
       </c>
       <c r="D383" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E383" s="12" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.5716783216783217</v>
       </c>
       <c r="F383" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G383" s="13" t="inlineStr">
@@ -21640,7 +21733,7 @@
       </c>
       <c r="H383" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I383" s="13" t="inlineStr">
@@ -21667,15 +21760,15 @@
       </c>
       <c r="D384" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E384" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="F384" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G384" s="13" t="inlineStr">
@@ -21685,7 +21778,7 @@
       </c>
       <c r="H384" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I384" s="13" t="inlineStr">
@@ -21712,15 +21805,15 @@
       </c>
       <c r="D385" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Qwen LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E385" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F385" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G385" s="13" t="inlineStr">
@@ -21730,7 +21823,7 @@
       </c>
       <c r="H385" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I385" s="13" t="inlineStr">
@@ -21757,15 +21850,15 @@
       </c>
       <c r="D386" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Qwen LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E386" s="12" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F386" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G386" s="13" t="inlineStr">
@@ -21775,7 +21868,7 @@
       </c>
       <c r="H386" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I386" s="13" t="inlineStr">
@@ -21802,15 +21895,15 @@
       </c>
       <c r="D387" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Qwen LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E387" s="12" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="F387" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G387" s="13" t="inlineStr">
@@ -21820,7 +21913,7 @@
       </c>
       <c r="H387" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I387" s="13" t="inlineStr">
@@ -21847,15 +21940,15 @@
       </c>
       <c r="D388" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E388" s="12" t="n">
-        <v>0.5</v>
+        <v>0.4484848484848484</v>
       </c>
       <c r="F388" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G388" s="13" t="inlineStr">
@@ -21865,7 +21958,7 @@
       </c>
       <c r="H388" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I388" s="13" t="inlineStr">
@@ -21892,15 +21985,15 @@
       </c>
       <c r="D389" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E389" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="F389" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G389" s="13" t="inlineStr">
@@ -21910,7 +22003,7 @@
       </c>
       <c r="H389" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I389" s="13" t="inlineStr">
@@ -21937,15 +22030,15 @@
       </c>
       <c r="D390" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E390" s="12" t="n">
-        <v>0.625</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F390" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G390" s="13" t="inlineStr">
@@ -21955,7 +22048,7 @@
       </c>
       <c r="H390" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I390" s="13" t="inlineStr">
@@ -21982,15 +22075,15 @@
       </c>
       <c r="D391" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Qwen XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E391" s="12" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F391" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G391" s="13" t="inlineStr">
@@ -22000,7 +22093,7 @@
       </c>
       <c r="H391" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I391" s="13" t="inlineStr">
@@ -22027,15 +22120,15 @@
       </c>
       <c r="D392" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>Qwen XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E392" s="12" t="n">
-        <v>0.396551724137931</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F392" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G392" s="13" t="inlineStr">
@@ -22045,7 +22138,7 @@
       </c>
       <c r="H392" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I392" s="13" t="inlineStr">
@@ -22072,15 +22165,15 @@
       </c>
       <c r="D393" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E393" s="12" t="n">
-        <v>0</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="F393" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G393" s="13" t="inlineStr">
@@ -22090,7 +22183,7 @@
       </c>
       <c r="H393" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I393" s="13" t="inlineStr">
@@ -22117,15 +22210,15 @@
       </c>
       <c r="D394" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E394" s="12" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.5</v>
       </c>
       <c r="F394" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G394" s="13" t="inlineStr">
@@ -22135,7 +22228,7 @@
       </c>
       <c r="H394" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I394" s="13" t="inlineStr">
@@ -22162,15 +22255,15 @@
       </c>
       <c r="D395" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E395" s="12" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F395" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G395" s="13" t="inlineStr">
@@ -22180,7 +22273,7 @@
       </c>
       <c r="H395" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I395" s="13" t="inlineStr">
@@ -22207,15 +22300,15 @@
       </c>
       <c r="D396" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E396" s="12" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="F396" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G396" s="13" t="inlineStr">
@@ -22225,7 +22318,7 @@
       </c>
       <c r="H396" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I396" s="13" t="inlineStr">
@@ -22247,20 +22340,20 @@
       </c>
       <c r="C397" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D397" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E397" s="12" t="n">
-        <v>0.6577777777777778</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F397" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G397" s="13" t="inlineStr">
@@ -22270,7 +22363,7 @@
       </c>
       <c r="H397" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I397" s="13" t="inlineStr">
@@ -22292,20 +22385,20 @@
       </c>
       <c r="C398" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D398" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E398" s="12" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F398" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G398" s="13" t="inlineStr">
@@ -22315,7 +22408,7 @@
       </c>
       <c r="H398" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I398" s="13" t="inlineStr">
@@ -22337,20 +22430,20 @@
       </c>
       <c r="C399" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D399" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E399" s="12" t="n">
-        <v>0.6857142857142857</v>
+        <v>0</v>
       </c>
       <c r="F399" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G399" s="13" t="inlineStr">
@@ -22360,7 +22453,7 @@
       </c>
       <c r="H399" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I399" s="13" t="inlineStr">
@@ -22382,20 +22475,20 @@
       </c>
       <c r="C400" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D400" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E400" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="F400" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G400" s="13" t="inlineStr">
@@ -22405,7 +22498,7 @@
       </c>
       <c r="H400" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I400" s="13" t="inlineStr">
@@ -22427,20 +22520,20 @@
       </c>
       <c r="C401" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D401" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E401" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="F401" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G401" s="13" t="inlineStr">
@@ -22450,7 +22543,7 @@
       </c>
       <c r="H401" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I401" s="13" t="inlineStr">
@@ -22472,20 +22565,20 @@
       </c>
       <c r="C402" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D402" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E402" s="12" t="n">
-        <v>0.5304437564499485</v>
+        <v>0</v>
       </c>
       <c r="F402" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G402" s="13" t="inlineStr">
@@ -22495,7 +22588,7 @@
       </c>
       <c r="H402" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I402" s="13" t="inlineStr">
@@ -22522,15 +22615,15 @@
       </c>
       <c r="D403" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E403" s="12" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.6577777777777778</v>
       </c>
       <c r="F403" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G403" s="13" t="inlineStr">
@@ -22540,7 +22633,7 @@
       </c>
       <c r="H403" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I403" s="13" t="inlineStr">
@@ -22567,15 +22660,15 @@
       </c>
       <c r="D404" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E404" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="F404" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G404" s="13" t="inlineStr">
@@ -22585,7 +22678,7 @@
       </c>
       <c r="H404" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I404" s="13" t="inlineStr">
@@ -22612,15 +22705,15 @@
       </c>
       <c r="D405" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Qwen LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E405" s="12" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F405" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G405" s="13" t="inlineStr">
@@ -22630,7 +22723,7 @@
       </c>
       <c r="H405" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I405" s="13" t="inlineStr">
@@ -22657,15 +22750,15 @@
       </c>
       <c r="D406" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Qwen LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E406" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="F406" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G406" s="13" t="inlineStr">
@@ -22675,7 +22768,7 @@
       </c>
       <c r="H406" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I406" s="13" t="inlineStr">
@@ -22702,15 +22795,15 @@
       </c>
       <c r="D407" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Qwen LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E407" s="12" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F407" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G407" s="13" t="inlineStr">
@@ -22720,7 +22813,7 @@
       </c>
       <c r="H407" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I407" s="13" t="inlineStr">
@@ -22747,15 +22840,15 @@
       </c>
       <c r="D408" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E408" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5304437564499485</v>
       </c>
       <c r="F408" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G408" s="13" t="inlineStr">
@@ -22765,7 +22858,7 @@
       </c>
       <c r="H408" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I408" s="13" t="inlineStr">
@@ -22792,15 +22885,15 @@
       </c>
       <c r="D409" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E409" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="F409" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G409" s="13" t="inlineStr">
@@ -22810,7 +22903,7 @@
       </c>
       <c r="H409" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I409" s="13" t="inlineStr">
@@ -22837,15 +22930,15 @@
       </c>
       <c r="D410" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E410" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F410" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G410" s="13" t="inlineStr">
@@ -22855,7 +22948,7 @@
       </c>
       <c r="H410" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I410" s="13" t="inlineStr">
@@ -22882,15 +22975,15 @@
       </c>
       <c r="D411" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Qwen XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E411" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F411" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G411" s="13" t="inlineStr">
@@ -22900,7 +22993,7 @@
       </c>
       <c r="H411" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I411" s="13" t="inlineStr">
@@ -22927,15 +23020,15 @@
       </c>
       <c r="D412" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>Qwen XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E412" s="12" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.25</v>
       </c>
       <c r="F412" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G412" s="13" t="inlineStr">
@@ -22945,7 +23038,7 @@
       </c>
       <c r="H412" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I412" s="13" t="inlineStr">
@@ -22972,15 +23065,15 @@
       </c>
       <c r="D413" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E413" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6829710144927537</v>
       </c>
       <c r="F413" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G413" s="13" t="inlineStr">
@@ -22990,7 +23083,7 @@
       </c>
       <c r="H413" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I413" s="13" t="inlineStr">
@@ -23017,15 +23110,15 @@
       </c>
       <c r="D414" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E414" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F414" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G414" s="13" t="inlineStr">
@@ -23035,7 +23128,7 @@
       </c>
       <c r="H414" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I414" s="13" t="inlineStr">
@@ -23062,15 +23155,15 @@
       </c>
       <c r="D415" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E415" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F415" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G415" s="13" t="inlineStr">
@@ -23080,7 +23173,7 @@
       </c>
       <c r="H415" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I415" s="13" t="inlineStr">
@@ -23107,7 +23200,7 @@
       </c>
       <c r="D416" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E416" s="12" t="n">
@@ -23115,7 +23208,7 @@
       </c>
       <c r="F416" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G416" s="13" t="inlineStr">
@@ -23125,7 +23218,7 @@
       </c>
       <c r="H416" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I416" s="13" t="inlineStr">
@@ -23147,20 +23240,20 @@
       </c>
       <c r="C417" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D417" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E417" s="12" t="n">
-        <v>0.6938775510204083</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F417" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G417" s="13" t="inlineStr">
@@ -23170,7 +23263,7 @@
       </c>
       <c r="H417" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I417" s="13" t="inlineStr">
@@ -23192,20 +23285,20 @@
       </c>
       <c r="C418" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D418" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E418" s="12" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.6829710144927537</v>
       </c>
       <c r="F418" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G418" s="13" t="inlineStr">
@@ -23215,7 +23308,7 @@
       </c>
       <c r="H418" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I418" s="13" t="inlineStr">
@@ -23237,20 +23330,20 @@
       </c>
       <c r="C419" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D419" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E419" s="12" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F419" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G419" s="13" t="inlineStr">
@@ -23260,7 +23353,7 @@
       </c>
       <c r="H419" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I419" s="13" t="inlineStr">
@@ -23282,20 +23375,20 @@
       </c>
       <c r="C420" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D420" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E420" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F420" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G420" s="13" t="inlineStr">
@@ -23305,7 +23398,7 @@
       </c>
       <c r="H420" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I420" s="13" t="inlineStr">
@@ -23327,20 +23420,20 @@
       </c>
       <c r="C421" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D421" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E421" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F421" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G421" s="13" t="inlineStr">
@@ -23350,7 +23443,7 @@
       </c>
       <c r="H421" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I421" s="13" t="inlineStr">
@@ -23372,20 +23465,20 @@
       </c>
       <c r="C422" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D422" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E422" s="12" t="n">
-        <v>0.6026831785345718</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F422" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G422" s="13" t="inlineStr">
@@ -23395,7 +23488,7 @@
       </c>
       <c r="H422" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I422" s="13" t="inlineStr">
@@ -23422,15 +23515,15 @@
       </c>
       <c r="D423" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E423" s="12" t="n">
-        <v>0.4210526315789474</v>
+        <v>0.6938775510204083</v>
       </c>
       <c r="F423" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G423" s="13" t="inlineStr">
@@ -23440,7 +23533,7 @@
       </c>
       <c r="H423" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I423" s="13" t="inlineStr">
@@ -23467,15 +23560,15 @@
       </c>
       <c r="D424" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E424" s="12" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="F424" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G424" s="13" t="inlineStr">
@@ -23485,7 +23578,7 @@
       </c>
       <c r="H424" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I424" s="13" t="inlineStr">
@@ -23512,15 +23605,15 @@
       </c>
       <c r="D425" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Qwen LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E425" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="F425" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G425" s="13" t="inlineStr">
@@ -23530,7 +23623,7 @@
       </c>
       <c r="H425" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I425" s="13" t="inlineStr">
@@ -23557,15 +23650,15 @@
       </c>
       <c r="D426" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Qwen LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E426" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F426" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G426" s="13" t="inlineStr">
@@ -23575,7 +23668,7 @@
       </c>
       <c r="H426" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I426" s="13" t="inlineStr">
@@ -23602,15 +23695,15 @@
       </c>
       <c r="D427" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Qwen LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E427" s="12" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.5</v>
       </c>
       <c r="F427" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G427" s="13" t="inlineStr">
@@ -23620,7 +23713,7 @@
       </c>
       <c r="H427" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I427" s="13" t="inlineStr">
@@ -23647,15 +23740,15 @@
       </c>
       <c r="D428" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E428" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6026831785345718</v>
       </c>
       <c r="F428" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G428" s="13" t="inlineStr">
@@ -23665,7 +23758,7 @@
       </c>
       <c r="H428" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I428" s="13" t="inlineStr">
@@ -23692,15 +23785,15 @@
       </c>
       <c r="D429" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E429" s="12" t="n">
-        <v>0.8</v>
+        <v>0.4210526315789474</v>
       </c>
       <c r="F429" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G429" s="13" t="inlineStr">
@@ -23710,7 +23803,7 @@
       </c>
       <c r="H429" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I429" s="13" t="inlineStr">
@@ -23737,15 +23830,15 @@
       </c>
       <c r="D430" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E430" s="12" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F430" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G430" s="13" t="inlineStr">
@@ -23755,7 +23848,7 @@
       </c>
       <c r="H430" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I430" s="13" t="inlineStr">
@@ -23782,15 +23875,15 @@
       </c>
       <c r="D431" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Qwen XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E431" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F431" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G431" s="13" t="inlineStr">
@@ -23800,7 +23893,7 @@
       </c>
       <c r="H431" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I431" s="13" t="inlineStr">
@@ -23827,15 +23920,15 @@
       </c>
       <c r="D432" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>Qwen XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E432" s="12" t="n">
-        <v>0.6685606060606061</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F432" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G432" s="13" t="inlineStr">
@@ -23845,7 +23938,7 @@
       </c>
       <c r="H432" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I432" s="13" t="inlineStr">
@@ -23872,15 +23965,15 @@
       </c>
       <c r="D433" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E433" s="12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="F433" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G433" s="13" t="inlineStr">
@@ -23890,7 +23983,7 @@
       </c>
       <c r="H433" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I433" s="13" t="inlineStr">
@@ -23917,15 +24010,15 @@
       </c>
       <c r="D434" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E434" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F434" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G434" s="13" t="inlineStr">
@@ -23935,7 +24028,7 @@
       </c>
       <c r="H434" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I434" s="13" t="inlineStr">
@@ -23962,15 +24055,15 @@
       </c>
       <c r="D435" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E435" s="12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F435" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G435" s="13" t="inlineStr">
@@ -23980,7 +24073,7 @@
       </c>
       <c r="H435" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I435" s="13" t="inlineStr">
@@ -24007,28 +24100,298 @@
       </c>
       <c r="D436" s="11" t="inlineStr">
         <is>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E436" s="12" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="F436" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G436" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H436" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I436" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B437" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C437" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D437" s="11" t="inlineStr">
+        <is>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E437" s="12" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F437" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G437" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H437" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I437" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B438" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C438" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D438" s="11" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E438" s="12" t="n">
+        <v>0.6685606060606061</v>
+      </c>
+      <c r="F438" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G438" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H438" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I438" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B439" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C439" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D439" s="11" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E439" s="12" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="F439" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G439" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H439" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I439" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B440" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C440" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D440" s="11" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E440" s="12" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F440" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G440" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H440" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I440" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B441" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C441" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D441" s="11" t="inlineStr">
+        <is>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E441" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F441" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G441" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H441" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I441" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B442" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C442" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D442" s="11" t="inlineStr">
+        <is>
           <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
-      <c r="E436" s="12" t="n">
+      <c r="E442" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="F436" s="13" t="inlineStr">
+      <c r="F442" s="13" t="inlineStr">
         <is>
           <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
-      <c r="G436" s="13" t="inlineStr">
+      <c r="G442" s="13" t="inlineStr">
         <is>
           <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
-      <c r="H436" s="13" t="inlineStr">
+      <c r="H442" s="13" t="inlineStr">
         <is>
           <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
-      <c r="I436" s="13" t="inlineStr">
+      <c r="I442" s="13" t="inlineStr">
         <is>
           <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Qwen vs Gemma" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DAIC Packed30 Family" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Native vs EN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DAIC Packed30 Family" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3996,6 +3997,1070 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Native vs English-translated transcripts — macro-F1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="92" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Paired native and English-translated transcript conditions for Qwen and Gemma 4. Delta = EN minus native; positive means translation improved macro-F1. Teacher-forced and LogReg use the harmonized best_model evidence; XGBoost uses the standardized 100-trial Optuna search, seed 1337. D3TEC/Androids = pooled 5-fold subject-level; CMDC/Turkish = 5-fold mean (train_val). Audio-only is omitted because transcript translation does not create a distinct audio-only experiment. Per-cell evidence is in the Provenance sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Qwen native</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Qwen EN</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Qwen Δ (EN − native)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Gemma native</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Gemma EN</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Gemma Δ (EN − native)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.571399</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0.564983</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Qwen more</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0.5464</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.498159</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.532292</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>EN better for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.523398</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.5982</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.5832270000000001</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.546749</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>-0.0365</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Qwen more</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>-0.0648</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.550505</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>-0.0569</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Native better for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.522456</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.596902</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>EN better for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>D3TEC</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.634535</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.5289</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>-0.1056</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.571942</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.5599460000000001</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Gemma more</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0.8873</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0.860541</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0.876968</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>~tie for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.8802</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8572689999999999</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.902794</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Gemma more</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.854305</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.8565469999999999</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.902794</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Gemma more</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.7317</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.7921</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.776201</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.744654</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Qwen more</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.802669</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.83016</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>~tie for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Androids Interview</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.846597</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.8111</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>-0.0355</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.748177</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.808427</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Gemma more</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.955419</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Qwen more</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.9614</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.9263479999999999</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>-0.0737</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Qwen more</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.9250890000000001</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.9134</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.984127</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.96828</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>~tie for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.957439</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.957439</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>~tie for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.9698</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.956334</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.969835</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>~tie for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>CMDC</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0.9698</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.924588</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.939796</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>~tie for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>-0.0371</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0.5657759999999999</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.669119</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Gemma more</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.6289</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.618816</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.599564</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>-0.0193</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>~tie for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.631141</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.6287</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.681937</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.592804</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>-0.0891</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Qwen more</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Teacher-forced</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.6781779999999999</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.6774</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>~tie for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>LogReg head</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.5944</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.558253</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.6014350000000001</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>EN helps Gemma more</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.589237</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0.6584</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0.520832</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.629565</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>EN better for both</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Direction uses |Δ| &lt; 0.03 as a practical tie for the compact label only; the exact deltas remain visible. This is descriptive and is not a significance test.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4505,7 +5570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Qwen vs Gemma" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Native vs EN" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DAIC Packed30 Family" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qwen vs Gemma" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Native vs EN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAIC Packed30 Family" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5576,7 +5576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I442"/>
+  <dimension ref="A1:I378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17815,7 +17815,7 @@
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B273" s="11" t="inlineStr">
@@ -17830,37 +17830,37 @@
       </c>
       <c r="D273" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E273" s="12" t="n">
-        <v>0.5233976549766023</v>
+        <v>0.564983</v>
       </c>
       <c r="F273" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G273" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H273" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_text_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_en_gemma4/audio_text/d3tec/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_d3tec_audio_text/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I273" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B274" s="11" t="inlineStr">
@@ -17875,37 +17875,37 @@
       </c>
       <c r="D274" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E274" s="12" t="n">
-        <v>0.5832267732267733</v>
+        <v>0.532292</v>
       </c>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H274" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_text_gemma4/group_report.json</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/d3tec_audio_text.json</t>
         </is>
       </c>
       <c r="I274" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B275" s="11" t="inlineStr">
@@ -17915,42 +17915,42 @@
       </c>
       <c r="C275" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D275" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E275" s="12" t="n">
-        <v>0.5194749694749694</v>
+        <v>0.4936</v>
       </c>
       <c r="F275" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G275" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H275" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_en_gemma4/text_only/d3tec/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_d3tec_text_only/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I275" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B276" s="11" t="inlineStr">
@@ -17960,132 +17960,132 @@
       </c>
       <c r="C276" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D276" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E276" s="12" t="n">
-        <v>0.546075036075036</v>
+        <v>0.596902</v>
       </c>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H276" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_only_gemma4/group_report.json</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/d3tec_text_only.json</t>
         </is>
       </c>
       <c r="I276" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B277" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C277" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D277" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E277" s="12" t="n">
-        <v>0.634534632034632</v>
+        <v>0.876968</v>
       </c>
       <c r="F277" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G277" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H277" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/d3tec_text_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_en_gemma4/audio_text/androids_interview/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_androids_interview_audio_text/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I277" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B278" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C278" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D278" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E278" s="12" t="n">
-        <v>0.5719417862838915</v>
+        <v>0.902794</v>
       </c>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H278" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/d3tec_text_only_gemma4/group_report.json</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/androids_interview_audio_text.json</t>
         </is>
       </c>
       <c r="I278" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B279" s="11" t="inlineStr">
@@ -18095,42 +18095,42 @@
       </c>
       <c r="C279" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D279" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E279" s="12" t="n">
-        <v>0.8543052605446494</v>
+        <v>0.744654</v>
       </c>
       <c r="F279" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G279" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H279" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_text_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_en_gemma4/text_only/androids_interview/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_androids_interview_text_only/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I279" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr">
@@ -18140,137 +18140,137 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D280" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E280" s="12" t="n">
-        <v>0.8565473598042608</v>
+        <v>0.83016</v>
       </c>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H280" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_text_gemma4/group_report.json</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/androids_interview_text_only.json</t>
         </is>
       </c>
       <c r="I280" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B281" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D281" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E281" s="12" t="n">
-        <v>0.8109429700734049</v>
+        <v>0.955419</v>
       </c>
       <c r="F281" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G281" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H281" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_en_gemma4/audio_text/cmdc/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_cmdc_audio_text/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I281" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B282" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D282" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E282" s="12" t="n">
-        <v>0.8020237849525775</v>
+        <v>0.9263479999999999</v>
       </c>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H282" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_only_gemma4/group_report.json</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/cmdc_audio_text.json</t>
         </is>
       </c>
       <c r="I282" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B283" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C283" s="11" t="inlineStr">
@@ -18280,42 +18280,42 @@
       </c>
       <c r="D283" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E283" s="12" t="n">
-        <v>0.8465966593792681</v>
+        <v>0.957439</v>
       </c>
       <c r="F283" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G283" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H283" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/androids_interview_text_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_en_gemma4/text_only/cmdc/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_cmdc_text_only/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I283" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B284" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C284" s="11" t="inlineStr">
@@ -18325,42 +18325,42 @@
       </c>
       <c r="D284" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E284" s="12" t="n">
-        <v>0.7481770520323419</v>
+        <v>0.969835</v>
       </c>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H284" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/androids_interview_text_only_gemma4/group_report.json</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/cmdc_text_only.json</t>
         </is>
       </c>
       <c r="I284" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B285" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C285" s="11" t="inlineStr">
@@ -18370,42 +18370,42 @@
       </c>
       <c r="D285" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E285" s="12" t="n">
-        <v>0.9250894033502728</v>
+        <v>0.669119</v>
       </c>
       <c r="F285" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G285" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H285" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_text_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_en_gemma4/audio_text/turkish/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_turkish_audio_text/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I285" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B286" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C286" s="11" t="inlineStr">
@@ -18415,667 +18415,667 @@
       </c>
       <c r="D286" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E286" s="12" t="n">
-        <v>0.9841269841269842</v>
+        <v>0.599564</v>
       </c>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H286" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_text_gemma4/group_report.json</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/turkish_audio_text.json</t>
         </is>
       </c>
       <c r="I286" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B287" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D287" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E287" s="12" t="n">
-        <v>0.951555023923445</v>
+        <v>0.6774</v>
       </c>
       <c r="F287" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G287" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H287" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_en_gemma4/text_only/turkish/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_turkish_text_only/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I287" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B288" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D288" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E288" s="12" t="n">
-        <v>0.9583694083694084</v>
+        <v>0.6014350000000001</v>
       </c>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H288" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_only_gemma4/group_report.json</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/turkish_text_only.json</t>
         </is>
       </c>
       <c r="I288" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B289" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D289" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E289" s="12" t="n">
-        <v>0.9538999012683224</v>
+        <v>0.761239</v>
       </c>
       <c r="F289" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
         </is>
       </c>
       <c r="G289" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
         </is>
       </c>
       <c r="H289" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/cmdc_text_only_qwen/group_report.json</t>
+          <t>output_model/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
         </is>
       </c>
       <c r="I289" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>from local training_history selected epoch</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B290" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D290" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E290" s="12" t="n">
-        <v>0.9245881502174408</v>
+        <v>0.741441</v>
       </c>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H290" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/cmdc_text_only_gemma4/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I290" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B291" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D291" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E291" s="12" t="n">
-        <v>0.6311408199643493</v>
+        <v>0.386284</v>
       </c>
       <c r="F291" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
         </is>
       </c>
       <c r="G291" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
         </is>
       </c>
       <c r="H291" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/turkish_audio_text_qwen/group_report.json</t>
+          <t>output_model/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
         </is>
       </c>
       <c r="I291" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>from local training_history selected epoch</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B292" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D292" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E292" s="12" t="n">
-        <v>0.6819372214116374</v>
+        <v>0.637276</v>
       </c>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H292" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/turkish_audio_text_gemma4/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I292" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B293" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D293" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E293" s="12" t="n">
-        <v>0.5145072673913382</v>
+        <v>0.7763330000000001</v>
       </c>
       <c r="F293" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
         </is>
       </c>
       <c r="G293" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
         </is>
       </c>
       <c r="H293" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/turkish_audio_only_qwen/group_report.json</t>
+          <t>output_model/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
         </is>
       </c>
       <c r="I293" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>from local training_history selected epoch</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B294" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D294" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E294" s="12" t="n">
-        <v>0.5670524643859309</v>
+        <v>0.726577</v>
       </c>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H294" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/turkish_audio_only_gemma4/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I294" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B295" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D295" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E295" s="12" t="n">
-        <v>0.5892365572441474</v>
+        <v>0.7257294429708223</v>
       </c>
       <c r="F295" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684476, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G295" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H295" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/turkish_text_only_qwen/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I295" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D296" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E296" s="12" t="n">
-        <v>0.5208317121475016</v>
+        <v>0.7834101382488479</v>
       </c>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H296" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/turkish_text_only_gemma4/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I296" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C297" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D297" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E297" s="12" t="n">
-        <v>0.715725806451613</v>
+        <v>0.5190058479532164</v>
       </c>
       <c r="F297" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684479, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G297" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H297" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/daic_audio_text_qwen/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I297" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B298" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C298" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D298" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E298" s="12" t="n">
-        <v>0.8156862745098039</v>
+        <v>0.4283783783783783</v>
       </c>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H298" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/daic_audio_text_gemma4/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I298" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B299" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C299" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D299" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E299" s="12" t="n">
-        <v>0.5761273209549072</v>
+        <v>0.7755968169761273</v>
       </c>
       <c r="F299" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684482, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G299" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H299" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/daic_audio_only_qwen/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I299" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B300" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C300" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D300" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E300" s="12" t="n">
-        <v>0.7257294429708223</v>
+        <v>0.70625</v>
       </c>
       <c r="F300" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G300" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H300" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/daic_audio_only_gemma4/group_report.json</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I300" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B301" s="11" t="inlineStr">
@@ -19085,42 +19085,42 @@
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D301" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E301" s="12" t="n">
-        <v>0.7257294429708223</v>
+        <v>0.3859649122807018</v>
       </c>
       <c r="F301" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G301" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H301" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/daic_text_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I301" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 native</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B302" s="11" t="inlineStr">
@@ -19130,227 +19130,227 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D302" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E302" s="12" t="n">
-        <v>0.7696078431372548</v>
+        <v>0</v>
       </c>
       <c r="F302" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H302" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_native/daic_text_only_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I302" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B303" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D303" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E303" s="12" t="n">
-        <v>0.598161968750204</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F303" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G303" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H303" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/d3tec_audio_text_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I303" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B304" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D304" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E304" s="12" t="n">
-        <v>0.5467279942279942</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F304" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H304" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/d3tec_audio_text_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I304" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B305" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D305" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E305" s="12" t="n">
-        <v>0.5289319014319014</v>
+        <v>0</v>
       </c>
       <c r="F305" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G305" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H305" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/d3tec_text_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I305" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B306" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C306" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D306" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E306" s="12" t="n">
-        <v>0.5599448942869996</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="F306" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G306" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H306" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/d3tec_text_only_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I306" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B307" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C307" s="11" t="inlineStr">
@@ -19360,42 +19360,42 @@
       </c>
       <c r="D307" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E307" s="12" t="n">
-        <v>0.8727292418997225</v>
+        <v>0.6258503401360545</v>
       </c>
       <c r="F307" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G307" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H307" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/androids_interview_audio_text_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I307" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B308" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C308" s="11" t="inlineStr">
@@ -19405,132 +19405,132 @@
       </c>
       <c r="D308" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E308" s="12" t="n">
-        <v>0.9027865444158352</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="F308" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G308" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H308" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/androids_interview_audio_text_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I308" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B309" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C309" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D309" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E309" s="12" t="n">
-        <v>0.8111428571428572</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F309" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G309" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H309" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/androids_interview_text_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I309" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B310" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C310" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D310" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E310" s="12" t="n">
-        <v>0.808360039884658</v>
+        <v>0.7552447552447553</v>
       </c>
       <c r="F310" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G310" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H310" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/androids_interview_text_only_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I310" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B311" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C311" s="11" t="inlineStr">
@@ -19540,42 +19540,42 @@
       </c>
       <c r="D311" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E311" s="12" t="n">
-        <v>0.9133968253968254</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="F311" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G311" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H311" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/cmdc_audio_text_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I311" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B312" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C312" s="11" t="inlineStr">
@@ -19585,42 +19585,42 @@
       </c>
       <c r="D312" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E312" s="12" t="n">
-        <v>0.9682539682539684</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="F312" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G312" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H312" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/cmdc_audio_text_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I312" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B313" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C313" s="11" t="inlineStr">
@@ -19630,42 +19630,42 @@
       </c>
       <c r="D313" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E313" s="12" t="n">
-        <v>0.9697729171413382</v>
+        <v>0.7086031452358927</v>
       </c>
       <c r="F313" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G313" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H313" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/cmdc_text_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I313" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B314" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C314" s="11" t="inlineStr">
@@ -19675,132 +19675,132 @@
       </c>
       <c r="D314" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E314" s="12" t="n">
-        <v>0.9397729171413381</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H314" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/cmdc_text_only_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I314" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B315" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C315" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D315" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E315" s="12" t="n">
-        <v>0.6287301587301588</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="F315" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G315" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H315" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/turkish_audio_text_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I315" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B316" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C316" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D316" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E316" s="12" t="n">
-        <v>0.5927987489058097</v>
+        <v>0.7822222222222222</v>
       </c>
       <c r="F316" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G316" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H316" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/turkish_audio_text_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I316" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B317" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C317" s="11" t="inlineStr">
@@ -19810,42 +19810,42 @@
       </c>
       <c r="D317" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E317" s="12" t="n">
-        <v>0.6584416576992479</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="F317" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G317" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H317" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/turkish_text_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I317" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 english</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B318" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C318" s="11" t="inlineStr">
@@ -19855,222 +19855,222 @@
       </c>
       <c r="D318" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E318" s="12" t="n">
-        <v>0.6296220712136271</v>
+        <v>0.8</v>
       </c>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
         </is>
       </c>
       <c r="G318" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H318" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_english/turkish_text_only_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I318" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B319" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C319" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D319" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E319" s="12" t="n">
-        <v>0.7411720992361243</v>
+        <v>0.5716783216783217</v>
       </c>
       <c r="F319" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G319" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H319" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/audio_text_cv_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I319" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B320" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C320" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D320" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E320" s="12" t="n">
-        <v>0.7644488625062797</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="F320" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G320" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H320" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/audio_text_cv_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I320" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B321" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC official test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C321" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D321" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E321" s="12" t="n">
-        <v>0.7431693989071039</v>
+        <v>0.6</v>
       </c>
       <c r="F321" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G321" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H321" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/audio_text_final_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I321" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B322" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC official test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C322" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D322" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Qwen LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E322" s="12" t="n">
-        <v>0.7456709956709957</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F322" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G322" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H322" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/audio_text_final_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I322" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B323" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C323" s="11" t="inlineStr">
@@ -20080,42 +20080,42 @@
       </c>
       <c r="D323" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E323" s="12" t="n">
-        <v>0.7473717357888511</v>
+        <v>0.5</v>
       </c>
       <c r="F323" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G323" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H323" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/audio_only_cv_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I323" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B324" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C324" s="11" t="inlineStr">
@@ -20125,42 +20125,42 @@
       </c>
       <c r="D324" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E324" s="12" t="n">
-        <v>0.700813968808538</v>
+        <v>0.4484848484848484</v>
       </c>
       <c r="F324" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G324" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H324" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/audio_only_cv_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I324" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B325" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC official test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C325" s="11" t="inlineStr">
@@ -20170,42 +20170,42 @@
       </c>
       <c r="D325" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E325" s="12" t="n">
-        <v>0.4727564102564102</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="F325" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G325" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H325" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/audio_only_final_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I325" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B326" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC official test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C326" s="11" t="inlineStr">
@@ -20215,217 +20215,217 @@
       </c>
       <c r="D326" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E326" s="12" t="n">
-        <v>0.5554054054054054</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F326" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G326" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H326" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/audio_only_final_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I326" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B327" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C327" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D327" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Qwen XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E327" s="12" t="n">
-        <v>0.7602906132436795</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F327" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G327" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H327" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/text_only_cv_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I327" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B328" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C328" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D328" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Qwen XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E328" s="12" t="n">
-        <v>0.7657973784875042</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F328" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G328" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H328" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/text_only_cv_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I328" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B329" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC official test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C329" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D329" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E329" s="12" t="n">
-        <v>0.7552083333333333</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="F329" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G329" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H329" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/text_only_final_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I329" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B330" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC official test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C330" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D330" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E330" s="12" t="n">
-        <v>0.7631048387096775</v>
+        <v>0.5</v>
       </c>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G330" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H330" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_merged/text_only_final_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I330" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 officialdev</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B331" s="11" t="inlineStr">
@@ -20435,42 +20435,42 @@
       </c>
       <c r="C331" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D331" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E331" s="12" t="n">
-        <v>0.5304437564499485</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F331" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G331" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H331" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_text_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I331" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 officialdev</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B332" s="11" t="inlineStr">
@@ -20480,42 +20480,42 @@
       </c>
       <c r="C332" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D332" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E332" s="12" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.625</v>
       </c>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G332" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H332" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_text_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I332" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 officialdev</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B333" s="11" t="inlineStr">
@@ -20530,37 +20530,37 @@
       </c>
       <c r="D333" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E333" s="12" t="n">
-        <v>0.5726970033296338</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F333" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G333" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H333" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I333" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 officialdev</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B334" s="11" t="inlineStr">
@@ -20575,37 +20575,37 @@
       </c>
       <c r="D334" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E334" s="12" t="n">
-        <v>0.6685606060606061</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F334" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G334" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H334" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_only_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I334" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 officialdev</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B335" s="11" t="inlineStr">
@@ -20615,42 +20615,42 @@
       </c>
       <c r="C335" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D335" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Qwen)</t>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E335" s="12" t="n">
-        <v>0.674922600619195</v>
+        <v>0</v>
       </c>
       <c r="F335" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G335" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H335" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_officialdev/daic_text_only_qwen/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I335" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
         <is>
-          <t>Optuna100 officialdev</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B336" s="11" t="inlineStr">
@@ -20660,227 +20660,227 @@
       </c>
       <c r="C336" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D336" s="11" t="inlineStr">
         <is>
-          <t>XGBoost Optuna-100 (Gemma 4)</t>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E336" s="12" t="n">
-        <v>0.7086031452358927</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G336" s="13" t="inlineStr">
         <is>
-          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H336" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/optuna100_officialdev/daic_text_only_gemma4/group_report.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I336" s="13" t="inlineStr">
         <is>
-          <t>group report OK; attempts REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B337" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C337" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D337" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E337" s="12" t="n">
-        <v>0.564983</v>
+        <v>0</v>
       </c>
       <c r="F337" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G337" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H337" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/audio_text/d3tec/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_d3tec_audio_text/fold_*/best_model/standalone_eval</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I337" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B338" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C338" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D338" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E338" s="12" t="n">
-        <v>0.532292</v>
+        <v>0</v>
       </c>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G338" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H338" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/d3tec_audio_text.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I338" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B339" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C339" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D339" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E339" s="12" t="n">
-        <v>0.4936</v>
+        <v>0.6577777777777778</v>
       </c>
       <c r="F339" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G339" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H339" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/text_only/d3tec/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_d3tec_text_only/fold_*/best_model/standalone_eval</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I339" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B340" s="11" t="inlineStr">
         <is>
-          <t>D3TEC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C340" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D340" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E340" s="12" t="n">
-        <v>0.596902</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H340" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/d3tec_text_only.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I340" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B341" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C341" s="11" t="inlineStr">
@@ -20890,42 +20890,42 @@
       </c>
       <c r="D341" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>Qwen LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E341" s="12" t="n">
-        <v>0.876968</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F341" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G341" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H341" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/audio_text/androids_interview/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_androids_interview_audio_text/fold_*/best_model/standalone_eval</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I341" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B342" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C342" s="11" t="inlineStr">
@@ -20935,132 +20935,132 @@
       </c>
       <c r="D342" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>Qwen LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E342" s="12" t="n">
-        <v>0.902794</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G342" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H342" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/androids_interview_audio_text.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I342" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B343" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C343" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D343" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>Qwen LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E343" s="12" t="n">
-        <v>0.744654</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F343" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G343" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H343" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/text_only/androids_interview/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_androids_interview_text_only/fold_*/best_model/standalone_eval</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I343" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B344" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C344" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D344" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E344" s="12" t="n">
-        <v>0.83016</v>
+        <v>0.5304437564499485</v>
       </c>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G344" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H344" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/androids_interview_text_only.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I344" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B345" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C345" s="11" t="inlineStr">
@@ -21070,42 +21070,42 @@
       </c>
       <c r="D345" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E345" s="12" t="n">
-        <v>0.955419</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="F345" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G345" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H345" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/audio_text/cmdc/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_cmdc_audio_text/fold_*/best_model/standalone_eval</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I345" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B346" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C346" s="11" t="inlineStr">
@@ -21115,132 +21115,132 @@
       </c>
       <c r="D346" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E346" s="12" t="n">
-        <v>0.9263479999999999</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G346" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H346" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/cmdc_audio_text.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I346" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B347" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C347" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D347" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>Qwen XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E347" s="12" t="n">
-        <v>0.957439</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F347" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G347" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H347" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/text_only/cmdc/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_cmdc_text_only/fold_*/best_model/standalone_eval</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I347" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B348" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C348" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D348" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>Qwen XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E348" s="12" t="n">
-        <v>0.969835</v>
+        <v>0.25</v>
       </c>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G348" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H348" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/cmdc_text_only.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I348" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B349" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C349" s="11" t="inlineStr">
@@ -21250,42 +21250,42 @@
       </c>
       <c r="D349" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E349" s="12" t="n">
-        <v>0.669119</v>
+        <v>0.6829710144927537</v>
       </c>
       <c r="F349" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G349" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H349" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/audio_text/turkish/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_turkish_audio_text/fold_*/best_model/standalone_eval</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I349" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B350" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C350" s="11" t="inlineStr">
@@ -21295,132 +21295,132 @@
       </c>
       <c r="D350" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E350" s="12" t="n">
-        <v>0.599564</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G350" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H350" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/turkish_audio_text.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I350" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B351" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C351" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D351" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E351" s="12" t="n">
-        <v>0.6774</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F351" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G351" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H351" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/text_only/turkish/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_turkish_text_only/fold_*/best_model/standalone_eval</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I351" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B352" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C352" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D352" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E352" s="12" t="n">
-        <v>0.6014350000000001</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G352" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H352" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/turkish_text_only.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I352" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B353" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C353" s="11" t="inlineStr">
@@ -21430,42 +21430,42 @@
       </c>
       <c r="D353" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E353" s="12" t="n">
-        <v>0.761239</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F353" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G353" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H353" s="13" t="inlineStr">
         <is>
-          <t>output_model/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I353" s="13" t="inlineStr">
         <is>
-          <t>from local training_history selected epoch</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B354" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C354" s="11" t="inlineStr">
@@ -21475,402 +21475,402 @@
       </c>
       <c r="D354" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E354" s="12" t="n">
-        <v>0.741441</v>
+        <v>0.6829710144927537</v>
       </c>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G354" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H354" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I354" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B355" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C355" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D355" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E355" s="12" t="n">
-        <v>0.386284</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F355" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G355" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H355" s="13" t="inlineStr">
         <is>
-          <t>output_model/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I355" s="13" t="inlineStr">
         <is>
-          <t>from local training_history selected epoch</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B356" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C356" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D356" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E356" s="12" t="n">
-        <v>0.637276</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G356" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H356" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I356" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B357" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C357" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D357" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E357" s="12" t="n">
-        <v>0.7763330000000001</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F357" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G357" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H357" s="13" t="inlineStr">
         <is>
-          <t>output_model/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I357" s="13" t="inlineStr">
         <is>
-          <t>from local training_history selected epoch</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B358" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C358" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D358" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E358" s="12" t="n">
-        <v>0.726577</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G358" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H358" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I358" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B359" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C359" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D359" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E359" s="12" t="n">
-        <v>0.7257294429708223</v>
+        <v>0.6938775510204083</v>
       </c>
       <c r="F359" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684476, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G359" s="13" t="inlineStr">
         <is>
-          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H359" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I359" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B360" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C360" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D360" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E360" s="12" t="n">
-        <v>0.7834101382488479</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G360" s="13" t="inlineStr">
         <is>
-          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H360" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I360" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B361" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C361" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D361" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>Qwen LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E361" s="12" t="n">
-        <v>0.5190058479532164</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="F361" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684479, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G361" s="13" t="inlineStr">
         <is>
-          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H361" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I361" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B362" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C362" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D362" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>Qwen LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E362" s="12" t="n">
-        <v>0.4283783783783783</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G362" s="13" t="inlineStr">
         <is>
-          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H362" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I362" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B363" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C363" s="11" t="inlineStr">
@@ -21880,42 +21880,42 @@
       </c>
       <c r="D363" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>Qwen LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E363" s="12" t="n">
-        <v>0.7755968169761273</v>
+        <v>0.5</v>
       </c>
       <c r="F363" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684482, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G363" s="13" t="inlineStr">
         <is>
-          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H363" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I363" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B364" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C364" s="11" t="inlineStr">
@@ -21925,37 +21925,37 @@
       </c>
       <c r="D364" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E364" s="12" t="n">
-        <v>0.70625</v>
+        <v>0.6026831785345718</v>
       </c>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G364" s="13" t="inlineStr">
         <is>
-          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H364" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I364" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B365" s="11" t="inlineStr">
@@ -21965,42 +21965,42 @@
       </c>
       <c r="C365" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D365" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E365" s="12" t="n">
-        <v>0.3859649122807018</v>
+        <v>0.4210526315789474</v>
       </c>
       <c r="F365" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G365" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H365" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I365" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B366" s="11" t="inlineStr">
@@ -22010,42 +22010,42 @@
       </c>
       <c r="C366" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D366" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>Qwen XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E366" s="12" t="n">
-        <v>0</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G366" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H366" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I366" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B367" s="11" t="inlineStr">
@@ -22055,42 +22055,42 @@
       </c>
       <c r="C367" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D367" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>Qwen XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E367" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F367" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G367" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H367" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I367" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B368" s="11" t="inlineStr">
@@ -22100,42 +22100,42 @@
       </c>
       <c r="C368" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D368" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>Qwen XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E368" s="12" t="n">
-        <v>0.396551724137931</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G368" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H368" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I368" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B369" s="11" t="inlineStr">
@@ -22145,42 +22145,42 @@
       </c>
       <c r="C369" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D369" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E369" s="12" t="n">
-        <v>0</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="F369" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G369" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H369" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I369" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B370" s="11" t="inlineStr">
@@ -22190,42 +22190,42 @@
       </c>
       <c r="C370" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D370" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E370" s="12" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G370" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H370" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I370" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B371" s="11" t="inlineStr">
@@ -22235,42 +22235,42 @@
       </c>
       <c r="C371" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D371" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>Gemma 4 LogReg raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E371" s="12" t="n">
-        <v>0.6258503401360545</v>
+        <v>0.8</v>
       </c>
       <c r="F371" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G371" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H371" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I371" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B372" s="11" t="inlineStr">
@@ -22280,42 +22280,42 @@
       </c>
       <c r="C372" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D372" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>Gemma 4 LogReg raw hidden head precision</t>
         </is>
       </c>
       <c r="E372" s="12" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G372" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H372" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I372" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B373" s="11" t="inlineStr">
@@ -22325,42 +22325,42 @@
       </c>
       <c r="C373" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D373" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>Gemma 4 LogReg raw hidden head recall</t>
         </is>
       </c>
       <c r="E373" s="12" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F373" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
         </is>
       </c>
       <c r="G373" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H373" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I373" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B374" s="11" t="inlineStr">
@@ -22370,42 +22370,42 @@
       </c>
       <c r="C374" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D374" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
         </is>
       </c>
       <c r="E374" s="12" t="n">
-        <v>0.7552447552447553</v>
+        <v>0.6685606060606061</v>
       </c>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G374" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H374" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I374" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B375" s="11" t="inlineStr">
@@ -22415,42 +22415,42 @@
       </c>
       <c r="C375" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D375" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
         </is>
       </c>
       <c r="E375" s="12" t="n">
-        <v>0.6923076923076924</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="F375" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G375" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H375" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I375" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B376" s="11" t="inlineStr">
@@ -22460,42 +22460,42 @@
       </c>
       <c r="C376" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D376" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
         </is>
       </c>
       <c r="E376" s="12" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G376" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H376" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I376" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B377" s="11" t="inlineStr">
@@ -22510,37 +22510,37 @@
       </c>
       <c r="D377" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head precision</t>
         </is>
       </c>
       <c r="E377" s="12" t="n">
-        <v>0.7086031452358927</v>
+        <v>0.6</v>
       </c>
       <c r="F377" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G377" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H377" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I377" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>DAIC Head Ablation</t>
         </is>
       </c>
       <c r="B378" s="11" t="inlineStr">
@@ -22555,2908 +22555,28 @@
       </c>
       <c r="D378" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>Gemma 4 XGBoost raw hidden head recall</t>
         </is>
       </c>
       <c r="E378" s="12" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.5</v>
       </c>
       <c r="F378" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
         </is>
       </c>
       <c r="G378" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H378" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I378" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="11" t="inlineStr">
-        <is>
-          <t>DAIC official development</t>
-        </is>
-      </c>
-      <c r="B379" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C379" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D379" s="11" t="inlineStr">
-        <is>
-          <t>Qwen teacher-forced accuracy</t>
-        </is>
-      </c>
-      <c r="E379" s="12" t="n">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="F379" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
-        </is>
-      </c>
-      <c r="G379" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H379" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I379" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="11" t="inlineStr">
-        <is>
-          <t>DAIC official development</t>
-        </is>
-      </c>
-      <c r="B380" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C380" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D380" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
-        </is>
-      </c>
-      <c r="E380" s="12" t="n">
-        <v>0.7822222222222222</v>
-      </c>
-      <c r="F380" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
-        </is>
-      </c>
-      <c r="G380" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H380" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I380" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="11" t="inlineStr">
-        <is>
-          <t>DAIC official development</t>
-        </is>
-      </c>
-      <c r="B381" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C381" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D381" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
-        </is>
-      </c>
-      <c r="E381" s="12" t="n">
-        <v>0.7199999999999999</v>
-      </c>
-      <c r="F381" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
-        </is>
-      </c>
-      <c r="G381" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H381" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I381" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="11" t="inlineStr">
-        <is>
-          <t>DAIC official development</t>
-        </is>
-      </c>
-      <c r="B382" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C382" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D382" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
-        </is>
-      </c>
-      <c r="E382" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F382" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
-        </is>
-      </c>
-      <c r="G382" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H382" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I382" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B383" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C383" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D383" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E383" s="12" t="n">
-        <v>0.5716783216783217</v>
-      </c>
-      <c r="F383" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G383" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H383" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I383" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B384" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C384" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D384" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E384" s="12" t="n">
-        <v>0.4615384615384615</v>
-      </c>
-      <c r="F384" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G384" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H384" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I384" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B385" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C385" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D385" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E385" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F385" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G385" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H385" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I385" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B386" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C386" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D386" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E386" s="12" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="F386" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G386" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H386" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I386" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B387" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C387" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D387" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E387" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F387" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G387" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H387" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I387" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B388" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C388" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D388" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E388" s="12" t="n">
-        <v>0.4484848484848484</v>
-      </c>
-      <c r="F388" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G388" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H388" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I388" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B389" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C389" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D389" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E389" s="12" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="F389" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G389" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H389" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I389" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B390" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C390" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D390" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E390" s="12" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="F390" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G390" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H390" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I390" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B391" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C391" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D391" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E391" s="12" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="F391" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G391" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H391" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I391" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B392" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C392" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D392" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E392" s="12" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="F392" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G392" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H392" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I392" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B393" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C393" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D393" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E393" s="12" t="n">
-        <v>0.6499999999999999</v>
-      </c>
-      <c r="F393" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G393" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H393" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I393" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B394" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C394" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D394" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E394" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F394" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G394" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H394" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I394" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B395" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C395" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D395" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E395" s="12" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="F395" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G395" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H395" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I395" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B396" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C396" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D396" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E396" s="12" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="F396" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G396" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H396" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I396" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B397" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C397" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D397" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E397" s="12" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="F397" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G397" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H397" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I397" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B398" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C398" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D398" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E398" s="12" t="n">
-        <v>0.396551724137931</v>
-      </c>
-      <c r="F398" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G398" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H398" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I398" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B399" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C399" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D399" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E399" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F399" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G399" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H399" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I399" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B400" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C400" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D400" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E400" s="12" t="n">
-        <v>0.6571428571428571</v>
-      </c>
-      <c r="F400" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G400" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H400" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I400" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B401" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C401" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D401" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E401" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F401" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G401" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H401" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I401" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B402" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C402" s="11" t="inlineStr">
-        <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="D402" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E402" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F402" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G402" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H402" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I402" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B403" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C403" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D403" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E403" s="12" t="n">
-        <v>0.6577777777777778</v>
-      </c>
-      <c r="F403" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G403" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H403" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I403" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B404" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C404" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D404" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E404" s="12" t="n">
-        <v>0.5599999999999999</v>
-      </c>
-      <c r="F404" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G404" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H404" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I404" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B405" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C405" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D405" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E405" s="12" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="F405" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G405" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H405" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I405" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B406" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C406" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D406" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E406" s="12" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="F406" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G406" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H406" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I406" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B407" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C407" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D407" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E407" s="12" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F407" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G407" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H407" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I407" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B408" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C408" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D408" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E408" s="12" t="n">
-        <v>0.5304437564499485</v>
-      </c>
-      <c r="F408" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G408" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H408" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I408" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B409" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C409" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D409" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E409" s="12" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-      <c r="F409" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G409" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H409" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I409" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B410" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C410" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D410" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E410" s="12" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="F410" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G410" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H410" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I410" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B411" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C411" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D411" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E411" s="12" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="F411" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G411" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H411" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I411" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B412" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C412" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D412" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E412" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F412" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G412" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H412" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I412" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B413" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C413" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D413" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E413" s="12" t="n">
-        <v>0.6829710144927537</v>
-      </c>
-      <c r="F413" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G413" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H413" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I413" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B414" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C414" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D414" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E414" s="12" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F414" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G414" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H414" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I414" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B415" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C415" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D415" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E415" s="12" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="F415" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G415" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H415" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I415" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B416" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C416" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D416" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E416" s="12" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F416" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G416" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H416" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I416" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B417" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C417" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D417" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E417" s="12" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F417" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G417" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H417" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I417" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B418" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C418" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D418" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E418" s="12" t="n">
-        <v>0.6829710144927537</v>
-      </c>
-      <c r="F418" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G418" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H418" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I418" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B419" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C419" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D419" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E419" s="12" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F419" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G419" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H419" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I419" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B420" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C420" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D420" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E420" s="12" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="F420" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G420" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H420" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I420" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B421" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C421" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D421" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E421" s="12" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F421" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G421" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H421" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I421" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B422" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C422" s="11" t="inlineStr">
-        <is>
-          <t>Audio + Text</t>
-        </is>
-      </c>
-      <c r="D422" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E422" s="12" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F422" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G422" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H422" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I422" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B423" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C423" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D423" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E423" s="12" t="n">
-        <v>0.6938775510204083</v>
-      </c>
-      <c r="F423" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G423" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H423" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I423" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B424" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C424" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D424" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E424" s="12" t="n">
-        <v>0.5714285714285715</v>
-      </c>
-      <c r="F424" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G424" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H424" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I424" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B425" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C425" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D425" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E425" s="12" t="n">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="F425" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G425" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H425" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I425" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B426" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C426" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D426" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E426" s="12" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="F426" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G426" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H426" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I426" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B427" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C427" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D427" s="11" t="inlineStr">
-        <is>
-          <t>Qwen LogReg raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E427" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F427" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G427" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H427" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I427" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B428" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C428" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D428" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E428" s="12" t="n">
-        <v>0.6026831785345718</v>
-      </c>
-      <c r="F428" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G428" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H428" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I428" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B429" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C429" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D429" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E429" s="12" t="n">
-        <v>0.4210526315789474</v>
-      </c>
-      <c r="F429" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G429" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H429" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I429" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B430" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C430" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D430" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E430" s="12" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="F430" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G430" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H430" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I430" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B431" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C431" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D431" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E431" s="12" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="F431" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G431" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H431" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I431" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B432" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C432" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D432" s="11" t="inlineStr">
-        <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E432" s="12" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="F432" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G432" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H432" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I432" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B433" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C433" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D433" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E433" s="12" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="F433" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G433" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H433" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I433" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B434" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C434" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D434" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E434" s="12" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="F434" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G434" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H434" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I434" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B435" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C435" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D435" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E435" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F435" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G435" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H435" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I435" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B436" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C436" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D436" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E436" s="12" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="F436" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G436" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H436" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I436" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B437" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C437" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D437" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E437" s="12" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="F437" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G437" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H437" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I437" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B438" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C438" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D438" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
-        </is>
-      </c>
-      <c r="E438" s="12" t="n">
-        <v>0.6685606060606061</v>
-      </c>
-      <c r="F438" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G438" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H438" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I438" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B439" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C439" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D439" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
-        </is>
-      </c>
-      <c r="E439" s="12" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="F439" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G439" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H439" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I439" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B440" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C440" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D440" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
-        </is>
-      </c>
-      <c r="E440" s="12" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="F440" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G440" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H440" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I440" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B441" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C441" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D441" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
-        </is>
-      </c>
-      <c r="E441" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F441" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G441" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H441" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I441" s="13" t="inlineStr">
-        <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" s="11" t="inlineStr">
-        <is>
-          <t>DAIC Head Ablation</t>
-        </is>
-      </c>
-      <c r="B442" s="11" t="inlineStr">
-        <is>
-          <t>DAIC</t>
-        </is>
-      </c>
-      <c r="C442" s="11" t="inlineStr">
-        <is>
-          <t>Text only</t>
-        </is>
-      </c>
-      <c r="D442" s="11" t="inlineStr">
-        <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
-        </is>
-      </c>
-      <c r="E442" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F442" s="13" t="inlineStr">
-        <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
-        </is>
-      </c>
-      <c r="G442" s="13" t="inlineStr">
-        <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
-        </is>
-      </c>
-      <c r="H442" s="13" t="inlineStr">
-        <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
-        </is>
-      </c>
-      <c r="I442" s="13" t="inlineStr">
         <is>
           <t>recomputed locally by verify-local; REPORTABLE</t>
         </is>

--- a/depression_results_clean.xlsx
+++ b/depression_results_clean.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qwen vs Gemma" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Native vs EN" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAIC Packed30 Family" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Qwen vs Gemma" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Native vs EN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DAIC Packed30 Family" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5576,7 +5576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I378"/>
+  <dimension ref="A1:I442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17815,7 +17815,7 @@
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B273" s="11" t="inlineStr">
@@ -17830,37 +17830,37 @@
       </c>
       <c r="D273" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E273" s="12" t="n">
-        <v>0.564983</v>
+        <v>0.5233976549766023</v>
       </c>
       <c r="F273" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G273" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H273" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/audio_text/d3tec/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_d3tec_audio_text/fold_*/best_model/standalone_eval</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I273" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B274" s="11" t="inlineStr">
@@ -17875,37 +17875,37 @@
       </c>
       <c r="D274" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E274" s="12" t="n">
-        <v>0.532292</v>
+        <v>0.5832267732267733</v>
       </c>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H274" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/d3tec_audio_text.json</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I274" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B275" s="11" t="inlineStr">
@@ -17915,42 +17915,42 @@
       </c>
       <c r="C275" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D275" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E275" s="12" t="n">
-        <v>0.4936</v>
+        <v>0.5194749694749694</v>
       </c>
       <c r="F275" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G275" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H275" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/text_only/d3tec/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_d3tec_text_only/fold_*/best_model/standalone_eval</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I275" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B276" s="11" t="inlineStr">
@@ -17960,132 +17960,132 @@
       </c>
       <c r="C276" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D276" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E276" s="12" t="n">
-        <v>0.596902</v>
+        <v>0.546075036075036</v>
       </c>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H276" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/d3tec_text_only.json</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I276" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B277" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C277" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D277" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E277" s="12" t="n">
-        <v>0.876968</v>
+        <v>0.634534632034632</v>
       </c>
       <c r="F277" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G277" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H277" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/audio_text/androids_interview/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_androids_interview_audio_text/fold_*/best_model/standalone_eval</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I277" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B278" s="11" t="inlineStr">
         <is>
-          <t>Androids Interview</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C278" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D278" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E278" s="12" t="n">
-        <v>0.902794</v>
+        <v>0.5719417862838915</v>
       </c>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H278" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/androids_interview_audio_text.json</t>
+          <t>outputs/experiment_reports/optuna100_native/d3tec_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I278" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B279" s="11" t="inlineStr">
@@ -18095,42 +18095,42 @@
       </c>
       <c r="C279" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D279" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E279" s="12" t="n">
-        <v>0.744654</v>
+        <v>0.8543052605446494</v>
       </c>
       <c r="F279" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G279" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H279" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/text_only/androids_interview/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_androids_interview_text_only/fold_*/best_model/standalone_eval</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I279" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr">
@@ -18140,137 +18140,137 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D280" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E280" s="12" t="n">
-        <v>0.83016</v>
+        <v>0.8565473598042608</v>
       </c>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H280" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/androids_interview_text_only.json</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I280" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B281" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D281" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E281" s="12" t="n">
-        <v>0.955419</v>
+        <v>0.8109429700734049</v>
       </c>
       <c r="F281" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G281" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H281" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/audio_text/cmdc/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_cmdc_audio_text/fold_*/best_model/standalone_eval</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I281" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B282" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D282" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E282" s="12" t="n">
-        <v>0.9263479999999999</v>
+        <v>0.8020237849525775</v>
       </c>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H282" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/cmdc_audio_text.json</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I282" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B283" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C283" s="11" t="inlineStr">
@@ -18280,42 +18280,42 @@
       </c>
       <c r="D283" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E283" s="12" t="n">
-        <v>0.957439</v>
+        <v>0.8465966593792681</v>
       </c>
       <c r="F283" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G283" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H283" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/text_only/cmdc/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_cmdc_text_only/fold_*/best_model/standalone_eval</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I283" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B284" s="11" t="inlineStr">
         <is>
-          <t>CMDC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C284" s="11" t="inlineStr">
@@ -18325,42 +18325,42 @@
       </c>
       <c r="D284" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E284" s="12" t="n">
-        <v>0.969835</v>
+        <v>0.7481770520323419</v>
       </c>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H284" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/cmdc_text_only.json</t>
+          <t>outputs/experiment_reports/optuna100_native/androids_interview_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I284" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B285" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C285" s="11" t="inlineStr">
@@ -18370,42 +18370,42 @@
       </c>
       <c r="D285" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E285" s="12" t="n">
-        <v>0.669119</v>
+        <v>0.9250894033502728</v>
       </c>
       <c r="F285" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G285" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H285" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/audio_text/turkish/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_turkish_audio_text/fold_*/best_model/standalone_eval</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I285" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B286" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C286" s="11" t="inlineStr">
@@ -18415,667 +18415,667 @@
       </c>
       <c r="D286" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E286" s="12" t="n">
-        <v>0.599564</v>
+        <v>0.9841269841269842</v>
       </c>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H286" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/turkish_audio_text.json</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I286" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B287" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D287" s="11" t="inlineStr">
         <is>
-          <t>Fine-tuned Gemma (teacher-forced)</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E287" s="12" t="n">
-        <v>0.6774</v>
+        <v>0.951555023923445</v>
       </c>
       <c r="F287" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G287" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H287" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_en_gemma4/text_only/turkish/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_turkish_text_only/fold_*/best_model/standalone_eval</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I287" s="13" t="inlineStr">
         <is>
-          <t>recomputed from local predictions (registry REPORTABLE)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>Gemma EN</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B288" s="11" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D288" s="11" t="inlineStr">
         <is>
-          <t>Gemma LogReg raw hidden head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E288" s="12" t="n">
-        <v>0.6014350000000001</v>
+        <v>0.9583694083694084</v>
       </c>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr">
         <is>
-          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H288" s="13" t="inlineStr">
         <is>
-          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/turkish_text_only.json</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I288" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B289" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D289" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E289" s="12" t="n">
-        <v>0.761239</v>
+        <v>0.9538999012683224</v>
       </c>
       <c r="F289" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G289" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H289" s="13" t="inlineStr">
         <is>
-          <t>output_model/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I289" s="13" t="inlineStr">
         <is>
-          <t>from local training_history selected epoch</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B290" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D290" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E290" s="12" t="n">
-        <v>0.741441</v>
+        <v>0.9245881502174408</v>
       </c>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H290" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>outputs/experiment_reports/optuna100_native/cmdc_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I290" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B291" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D291" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E291" s="12" t="n">
-        <v>0.386284</v>
+        <v>0.6311408199643493</v>
       </c>
       <c r="F291" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G291" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H291" s="13" t="inlineStr">
         <is>
-          <t>output_model/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I291" s="13" t="inlineStr">
         <is>
-          <t>from local training_history selected epoch</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B292" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D292" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E292" s="12" t="n">
-        <v>0.637276</v>
+        <v>0.6819372214116374</v>
       </c>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H292" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I292" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B293" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D293" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E293" s="12" t="n">
-        <v>0.7763330000000001</v>
+        <v>0.5145072673913382</v>
       </c>
       <c r="F293" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G293" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H293" s="13" t="inlineStr">
         <is>
-          <t>output_model/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I293" s="13" t="inlineStr">
         <is>
-          <t>from local training_history selected epoch</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B294" s="11" t="inlineStr">
         <is>
-          <t>CV (5-fold)</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D294" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E294" s="12" t="n">
-        <v>0.726577</v>
+        <v>0.5670524643859309</v>
       </c>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr">
         <is>
-          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H294" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I294" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B295" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D295" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E295" s="12" t="n">
-        <v>0.7257294429708223</v>
+        <v>0.5892365572441474</v>
       </c>
       <c r="F295" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684476, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G295" s="13" t="inlineStr">
         <is>
-          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H295" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I295" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D296" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E296" s="12" t="n">
-        <v>0.7834101382488479</v>
+        <v>0.5208317121475016</v>
       </c>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr">
         <is>
-          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H296" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>outputs/experiment_reports/optuna100_native/turkish_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I296" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C297" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D297" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E297" s="12" t="n">
-        <v>0.5190058479532164</v>
+        <v>0.715725806451613</v>
       </c>
       <c r="F297" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684479, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G297" s="13" t="inlineStr">
         <is>
-          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H297" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I297" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B298" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C298" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D298" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E298" s="12" t="n">
-        <v>0.4283783783783783</v>
+        <v>0.8156862745098039</v>
       </c>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr">
         <is>
-          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H298" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I298" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B299" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C299" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D299" s="11" t="inlineStr">
         <is>
-          <t>Teacher-forced</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E299" s="12" t="n">
-        <v>0.7755968169761273</v>
+        <v>0.5761273209549072</v>
       </c>
       <c r="F299" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684482, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G299" s="13" t="inlineStr">
         <is>
-          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H299" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I299" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>Gemma merged</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B300" s="11" t="inlineStr">
         <is>
-          <t>Final (DAIC test)</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="C300" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D300" s="11" t="inlineStr">
         <is>
-          <t>LogReg head</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E300" s="12" t="n">
-        <v>0.70625</v>
+        <v>0.7257294429708223</v>
       </c>
       <c r="F300" s="13" t="inlineStr">
         <is>
-          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G300" s="13" t="inlineStr">
         <is>
-          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H300" s="13" t="inlineStr">
         <is>
-          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I300" s="13" t="inlineStr">
         <is>
-          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B301" s="11" t="inlineStr">
@@ -19085,42 +19085,42 @@
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D301" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E301" s="12" t="n">
-        <v>0.3859649122807018</v>
+        <v>0.7257294429708223</v>
       </c>
       <c r="F301" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G301" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H301" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I301" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 native</t>
         </is>
       </c>
       <c r="B302" s="11" t="inlineStr">
@@ -19130,227 +19130,227 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D302" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E302" s="12" t="n">
-        <v>0</v>
+        <v>0.7696078431372548</v>
       </c>
       <c r="F302" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign optuna100_native_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group native-optuna100-optuna100_native_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H302" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_native/daic_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I302" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B303" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D303" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E303" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.598161968750204</v>
       </c>
       <c r="F303" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G303" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H303" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/d3tec_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I303" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B304" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D304" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E304" s="12" t="n">
-        <v>0.396551724137931</v>
+        <v>0.5467279942279942</v>
       </c>
       <c r="F304" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H304" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/d3tec_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I304" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B305" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D305" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E305" s="12" t="n">
-        <v>0</v>
+        <v>0.5289319014319014</v>
       </c>
       <c r="F305" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G305" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H305" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/d3tec_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I305" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B306" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C306" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D306" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E306" s="12" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.5599448942869996</v>
       </c>
       <c r="F306" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G306" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H306" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/d3tec_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I306" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B307" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C307" s="11" t="inlineStr">
@@ -19360,42 +19360,42 @@
       </c>
       <c r="D307" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E307" s="12" t="n">
-        <v>0.6258503401360545</v>
+        <v>0.8727292418997225</v>
       </c>
       <c r="F307" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G307" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H307" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/androids_interview_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I307" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B308" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C308" s="11" t="inlineStr">
@@ -19405,132 +19405,132 @@
       </c>
       <c r="D308" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E308" s="12" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.9027865444158352</v>
       </c>
       <c r="F308" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G308" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H308" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/androids_interview_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I308" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B309" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C309" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D309" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E309" s="12" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.8111428571428572</v>
       </c>
       <c r="F309" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G309" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H309" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/androids_interview_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I309" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B310" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C310" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D310" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E310" s="12" t="n">
-        <v>0.7552447552447553</v>
+        <v>0.808360039884658</v>
       </c>
       <c r="F310" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G310" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H310" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/androids_interview_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I310" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B311" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C311" s="11" t="inlineStr">
@@ -19540,42 +19540,42 @@
       </c>
       <c r="D311" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E311" s="12" t="n">
-        <v>0.6923076923076924</v>
+        <v>0.9133968253968254</v>
       </c>
       <c r="F311" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G311" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H311" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/cmdc_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I311" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B312" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C312" s="11" t="inlineStr">
@@ -19585,42 +19585,42 @@
       </c>
       <c r="D312" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E312" s="12" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.9682539682539684</v>
       </c>
       <c r="F312" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G312" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H312" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/cmdc_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I312" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B313" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C313" s="11" t="inlineStr">
@@ -19630,42 +19630,42 @@
       </c>
       <c r="D313" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E313" s="12" t="n">
-        <v>0.7086031452358927</v>
+        <v>0.9697729171413382</v>
       </c>
       <c r="F313" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G313" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H313" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/cmdc_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I313" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B314" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C314" s="11" t="inlineStr">
@@ -19675,132 +19675,132 @@
       </c>
       <c r="D314" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E314" s="12" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.9397729171413381</v>
       </c>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H314" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/cmdc_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I314" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B315" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C315" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D315" s="11" t="inlineStr">
         <is>
-          <t>Qwen teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E315" s="12" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.6287301587301588</v>
       </c>
       <c r="F315" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G315" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H315" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/turkish_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I315" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B316" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C316" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D316" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E316" s="12" t="n">
-        <v>0.7822222222222222</v>
+        <v>0.5927987489058097</v>
       </c>
       <c r="F316" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G316" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H316" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/turkish_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I316" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B317" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C317" s="11" t="inlineStr">
@@ -19810,42 +19810,42 @@
       </c>
       <c r="D317" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E317" s="12" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.6584416576992479</v>
       </c>
       <c r="F317" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G317" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H317" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/turkish_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I317" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>DAIC official development</t>
+          <t>Optuna100 english</t>
         </is>
       </c>
       <c r="B318" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C318" s="11" t="inlineStr">
@@ -19855,222 +19855,222 @@
       </c>
       <c r="D318" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 teacher-forced accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E318" s="12" t="n">
-        <v>0.8</v>
+        <v>0.6296220712136271</v>
       </c>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+          <t>campaign optuna100_english_20260815T2300Z_a955cdd, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group english-optuna100-optuna100_english_20260815T2300Z_a955cdd)</t>
         </is>
       </c>
       <c r="G318" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H318" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_english/turkish_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I318" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally from synced predictions; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B319" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C319" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D319" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E319" s="12" t="n">
-        <v>0.5716783216783217</v>
+        <v>0.7411720992361243</v>
       </c>
       <c r="F319" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G319" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H319" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_text_cv_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I319" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B320" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C320" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D320" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E320" s="12" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.7644488625062797</v>
       </c>
       <c r="F320" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G320" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H320" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_text_cv_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I320" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B321" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C321" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D321" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E321" s="12" t="n">
-        <v>0.6</v>
+        <v>0.7431693989071039</v>
       </c>
       <c r="F321" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G321" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H321" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_text_final_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I321" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B322" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C322" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D322" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E322" s="12" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.7456709956709957</v>
       </c>
       <c r="F322" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G322" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H322" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_text_final_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I322" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B323" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C323" s="11" t="inlineStr">
@@ -20080,42 +20080,42 @@
       </c>
       <c r="D323" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E323" s="12" t="n">
-        <v>0.5</v>
+        <v>0.7473717357888511</v>
       </c>
       <c r="F323" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G323" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H323" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_only_cv_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I323" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B324" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C324" s="11" t="inlineStr">
@@ -20125,42 +20125,42 @@
       </c>
       <c r="D324" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E324" s="12" t="n">
-        <v>0.4484848484848484</v>
+        <v>0.700813968808538</v>
       </c>
       <c r="F324" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G324" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H324" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_only_cv_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I324" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B325" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C325" s="11" t="inlineStr">
@@ -20170,42 +20170,42 @@
       </c>
       <c r="D325" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E325" s="12" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4727564102564102</v>
       </c>
       <c r="F325" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G325" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H325" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_only_final_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I325" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B326" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C326" s="11" t="inlineStr">
@@ -20215,217 +20215,217 @@
       </c>
       <c r="D326" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E326" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5554054054054054</v>
       </c>
       <c r="F326" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G326" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H326" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/audio_only_final_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I326" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B327" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C327" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D327" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E327" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7602906132436795</v>
       </c>
       <c r="F327" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G327" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H327" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/text_only_cv_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I327" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B328" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C328" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D328" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E328" s="12" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.7657973784875042</v>
       </c>
       <c r="F328" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G328" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H328" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/text_only_cv_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I328" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B329" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C329" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D329" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E329" s="12" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.7552083333333333</v>
       </c>
       <c r="F329" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G329" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H329" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/text_only_final_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I329" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 merged</t>
         </is>
       </c>
       <c r="B330" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC official test)</t>
         </is>
       </c>
       <c r="C330" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D330" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E330" s="12" t="n">
-        <v>0.5</v>
+        <v>0.7631048387096775</v>
       </c>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_merged_20260816T2000Z_9efd6e5, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group merged-optuna100-optuna100_merged_20260816T2000Z_9efd6e5)</t>
         </is>
       </c>
       <c r="G330" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H330" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_merged/text_only_final_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I330" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B331" s="11" t="inlineStr">
@@ -20435,42 +20435,42 @@
       </c>
       <c r="C331" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D331" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E331" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5304437564499485</v>
       </c>
       <c r="F331" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G331" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H331" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_text_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I331" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B332" s="11" t="inlineStr">
@@ -20480,42 +20480,42 @@
       </c>
       <c r="C332" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D332" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E332" s="12" t="n">
-        <v>0.625</v>
+        <v>0.6829710144927537</v>
       </c>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G332" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H332" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_text_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I332" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B333" s="11" t="inlineStr">
@@ -20530,37 +20530,37 @@
       </c>
       <c r="D333" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E333" s="12" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5726970033296338</v>
       </c>
       <c r="F333" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-3e3a37d62c53729cf5db69b5, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G333" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H333" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I333" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B334" s="11" t="inlineStr">
@@ -20575,37 +20575,37 @@
       </c>
       <c r="D334" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E334" s="12" t="n">
-        <v>0.396551724137931</v>
+        <v>0.6685606060606061</v>
       </c>
       <c r="F334" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G334" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H334" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_audio_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I334" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B335" s="11" t="inlineStr">
@@ -20615,42 +20615,42 @@
       </c>
       <c r="C335" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D335" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>XGBoost Optuna-100 (Qwen)</t>
         </is>
       </c>
       <c r="E335" s="12" t="n">
-        <v>0</v>
+        <v>0.674922600619195</v>
       </c>
       <c r="F335" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Qwen backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G335" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H335" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_text_only_qwen/group_report.json</t>
         </is>
       </c>
       <c r="I335" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Optuna100 officialdev</t>
         </is>
       </c>
       <c r="B336" s="11" t="inlineStr">
@@ -20660,227 +20660,227 @@
       </c>
       <c r="C336" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D336" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>XGBoost Optuna-100 (Gemma 4)</t>
         </is>
       </c>
       <c r="E336" s="12" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.7086031452358927</v>
       </c>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign optuna100_officialdev_20260815T0330Z_99efc52, Gemma 4 backend, 100 trials/fold, all attempts REPORTABLE in registry (group officialdev-optuna100-optuna100_officialdev_20260815T0330Z_99efc52)</t>
         </is>
       </c>
       <c r="G336" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Optuna-100 fold-mean, 100 TPE trials seed 1337, 3 subject-grouped inner folds, macro-F1 objective, harmonized_all_windows_full_coverage, headline/binary-strict</t>
         </is>
       </c>
       <c r="H336" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/optuna100_officialdev/daic_text_only_gemma4/group_report.json</t>
         </is>
       </c>
       <c r="I336" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>group report OK; attempts REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B337" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C337" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D337" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E337" s="12" t="n">
-        <v>0</v>
+        <v>0.564983</v>
       </c>
       <c r="F337" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G337" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H337" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_en_gemma4/audio_text/d3tec/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_d3tec_audio_text/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I337" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B338" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C338" s="11" t="inlineStr">
         <is>
-          <t>Audio only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D338" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E338" s="12" t="n">
-        <v>0</v>
+        <v>0.532292</v>
       </c>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T151846Z-daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2-1327849b-640f4031, eval eval-ad6e2a2ce408aed6f96f39d3, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G338" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H338" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_only/daic/daic_officialdev_gemma4_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_1327849b_r2/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/d3tec_audio_text.json</t>
         </is>
       </c>
       <c r="I338" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B339" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C339" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D339" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E339" s="12" t="n">
-        <v>0.6577777777777778</v>
+        <v>0.4936</v>
       </c>
       <c r="F339" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G339" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H339" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_en_gemma4/text_only/d3tec/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_d3tec_text_only/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I339" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B340" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>D3TEC</t>
         </is>
       </c>
       <c r="C340" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D340" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E340" s="12" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.596902</v>
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H340" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/d3tec_text_only.json</t>
         </is>
       </c>
       <c r="I340" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B341" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C341" s="11" t="inlineStr">
@@ -20890,42 +20890,42 @@
       </c>
       <c r="D341" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E341" s="12" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.876968</v>
       </c>
       <c r="F341" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G341" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H341" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_en_gemma4/audio_text/androids_interview/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_androids_interview_audio_text/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I341" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B342" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C342" s="11" t="inlineStr">
@@ -20935,132 +20935,132 @@
       </c>
       <c r="D342" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E342" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.902794</v>
       </c>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G342" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H342" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/androids_interview_audio_text.json</t>
         </is>
       </c>
       <c r="I342" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B343" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C343" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D343" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E343" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.744654</v>
       </c>
       <c r="F343" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-536fc321c7611b917b42fdf6, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G343" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H343" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_en_gemma4/text_only/androids_interview/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_androids_interview_text_only/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I343" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B344" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Androids Interview</t>
         </is>
       </c>
       <c r="C344" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D344" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E344" s="12" t="n">
-        <v>0.5304437564499485</v>
+        <v>0.83016</v>
       </c>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G344" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H344" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/androids_interview_text_only.json</t>
         </is>
       </c>
       <c r="I344" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B345" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C345" s="11" t="inlineStr">
@@ -21070,42 +21070,42 @@
       </c>
       <c r="D345" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E345" s="12" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.955419</v>
       </c>
       <c r="F345" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G345" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H345" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_en_gemma4/audio_text/cmdc/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_cmdc_audio_text/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I345" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B346" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C346" s="11" t="inlineStr">
@@ -21115,132 +21115,132 @@
       </c>
       <c r="D346" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E346" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.9263479999999999</v>
       </c>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G346" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H346" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/cmdc_audio_text.json</t>
         </is>
       </c>
       <c r="I346" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B347" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C347" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D347" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E347" s="12" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.957439</v>
       </c>
       <c r="F347" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G347" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H347" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_en_gemma4/text_only/cmdc/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_cmdc_text_only/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I347" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B348" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CMDC</t>
         </is>
       </c>
       <c r="C348" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D348" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E348" s="12" t="n">
-        <v>0.25</v>
+        <v>0.969835</v>
       </c>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-b7d64c2f, eval eval-c9a4f95ffa07bebb8aa2c104, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G348" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H348" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/audio_text/daic/daic_officialdev_qwen_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/cmdc_text_only.json</t>
         </is>
       </c>
       <c r="I348" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B349" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C349" s="11" t="inlineStr">
@@ -21250,42 +21250,42 @@
       </c>
       <c r="D349" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E349" s="12" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.669119</v>
       </c>
       <c r="F349" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G349" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H349" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_en_gemma4/audio_text/turkish/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_turkish_audio_text/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I349" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B350" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C350" s="11" t="inlineStr">
@@ -21295,132 +21295,132 @@
       </c>
       <c r="D350" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E350" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.599564</v>
       </c>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G350" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H350" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/turkish_audio_text.json</t>
         </is>
       </c>
       <c r="I350" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B351" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C351" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D351" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Fine-tuned Gemma (teacher-forced)</t>
         </is>
       </c>
       <c r="E351" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6774</v>
       </c>
       <c r="F351" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G351" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H351" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_en_gemma4/text_only/turkish/gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd_turkish_text_only/fold_*/best_model/standalone_eval</t>
         </is>
       </c>
       <c r="I351" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from local predictions (registry REPORTABLE)</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma EN</t>
         </is>
       </c>
       <c r="B352" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="C352" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D352" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Gemma LogReg raw hidden head</t>
         </is>
       </c>
       <c r="E352" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6014350000000001</v>
       </c>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, group gemma4-harmonized-v1-en-gemma4_harmonized_v1_en_gemma4_en_prod_20260815T1300Z_a955cdd, 5 folds REPORTABLE</t>
         </is>
       </c>
       <c r="G352" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>English-translated, pooled 5-fold subject-level (D3TEC/Androids) or 5-fold mean (CMDC/Turkish), LogReg raw hidden head, binary-strict, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H352" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/experiment_reports/gemma4_harmonized/english_lr/turkish_text_only.json</t>
         </is>
       </c>
       <c r="I352" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions_subject_level.csv (matches metrics.json)</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B353" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C353" s="11" t="inlineStr">
@@ -21430,42 +21430,42 @@
       </c>
       <c r="D353" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E353" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.761239</v>
       </c>
       <c r="F353" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-70d39c1caadc8712d02ae7fb, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
         </is>
       </c>
       <c r="G353" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
         </is>
       </c>
       <c r="H353" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
         </is>
       </c>
       <c r="I353" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>from local training_history selected epoch</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B354" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C354" s="11" t="inlineStr">
@@ -21475,402 +21475,402 @@
       </c>
       <c r="D354" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E354" s="12" t="n">
-        <v>0.6829710144927537</v>
+        <v>0.741441</v>
       </c>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G354" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H354" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I354" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B355" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C355" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D355" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E355" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.386284</v>
       </c>
       <c r="F355" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
         </is>
       </c>
       <c r="G355" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
         </is>
       </c>
       <c r="H355" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
         </is>
       </c>
       <c r="I355" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>from local training_history selected epoch</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B356" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C356" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D356" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E356" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.637276</v>
       </c>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G356" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H356" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I356" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B357" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C357" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D357" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E357" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7763330000000001</v>
       </c>
       <c r="F357" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged training selection (mean_dataset_macro_f1)</t>
         </is>
       </c>
       <c r="G357" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>CV (5-fold), teacher-forced, mean over five datasets</t>
         </is>
       </c>
       <c r="H357" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/logs/training_history.json</t>
         </is>
       </c>
       <c r="I357" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>from local training_history selected epoch</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B358" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CV (5-fold)</t>
         </is>
       </c>
       <c r="C358" s="11" t="inlineStr">
         <is>
-          <t>Audio + Text</t>
+          <t>Text only</t>
         </is>
       </c>
       <c r="D358" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head recall</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E358" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.726577</v>
       </c>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T175117Z-daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6-90c6cc39-438b3be6, eval eval-e480a1844b709554d1d22b7c, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G358" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>CV (5-fold), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H358" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/audio_text/daic/daic_officialdev_gemma4_audio_text_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r6/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/cv/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I358" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B359" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C359" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D359" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head macro-F1</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E359" s="12" t="n">
-        <v>0.6938775510204083</v>
+        <v>0.7257294429708223</v>
       </c>
       <c r="F359" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684476, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G359" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H359" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I359" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B360" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C360" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D360" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head positive-F1</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E360" s="12" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.7834101382488479</v>
       </c>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G360" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H360" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_text/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I360" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B361" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C361" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D361" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head accuracy</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E361" s="12" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.5190058479532164</v>
       </c>
       <c r="F361" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684479, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G361" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H361" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I361" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B362" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C362" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D362" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head precision</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E362" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4283783783783783</v>
       </c>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G362" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H362" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/audio_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I362" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B363" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C363" s="11" t="inlineStr">
@@ -21880,42 +21880,42 @@
       </c>
       <c r="D363" s="11" t="inlineStr">
         <is>
-          <t>Qwen LogReg raw hidden head recall</t>
+          <t>Teacher-forced</t>
         </is>
       </c>
       <c r="E363" s="12" t="n">
-        <v>0.5</v>
+        <v>0.7755968169761273</v>
       </c>
       <c r="F363" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-225153901c0e8896c9900e4a, backend qwen_hidden_logreg_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, postprocess job 44684482, source bfc13b4f8b177547a11a9abad526115b712d32ef</t>
         </is>
       </c>
       <c r="G363" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>DAIC official test, 47 subjects, teacher-forced, binary-strict, subject mean-score, harmonized_all_windows_full_coverage</t>
         </is>
       </c>
       <c r="H363" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/gemma4/daic/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I363" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from 47 subject predictions; zero invalid subjects</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>Gemma merged</t>
         </is>
       </c>
       <c r="B364" s="11" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>Final (DAIC test)</t>
         </is>
       </c>
       <c r="C364" s="11" t="inlineStr">
@@ -21925,37 +21925,37 @@
       </c>
       <c r="D364" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head macro-F1</t>
+          <t>LogReg head</t>
         </is>
       </c>
       <c r="E364" s="12" t="n">
-        <v>0.6026831785345718</v>
+        <v>0.70625</v>
       </c>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign gemma4_merged_v1_prod_20260816T0000Z_d4ff33e, merged heads</t>
         </is>
       </c>
       <c r="G364" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>Final (DAIC test), LogReg raw hidden head, mean over five datasets</t>
         </is>
       </c>
       <c r="H364" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>outputs/symmetric_merged/gemma4/harmonized_v1/text_only/gemma4_merged_v1_prod_20260816T0000Z_d4ff33e/final/fold_0/heads/logreg/metrics_by_dataset.json</t>
         </is>
       </c>
       <c r="I364" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed from predictions (matches metrics_by_dataset.json)</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B365" s="11" t="inlineStr">
@@ -21965,42 +21965,42 @@
       </c>
       <c r="C365" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D365" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head positive-F1</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E365" s="12" t="n">
-        <v>0.4210526315789474</v>
+        <v>0.3859649122807018</v>
       </c>
       <c r="F365" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G365" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H365" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I365" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B366" s="11" t="inlineStr">
@@ -22010,42 +22010,42 @@
       </c>
       <c r="C366" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D366" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head accuracy</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E366" s="12" t="n">
-        <v>0.6857142857142857</v>
+        <v>0</v>
       </c>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G366" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H366" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I366" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B367" s="11" t="inlineStr">
@@ -22055,42 +22055,42 @@
       </c>
       <c r="C367" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D367" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head precision</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E367" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="F367" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142847Z-daic_officialdev_qwen_audio_only_seed1337-22f85e6e-9c326e1d, eval eval-7c1ef60108d44e8081fa66cd, selected epoch 7, best_model</t>
         </is>
       </c>
       <c r="G367" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H367" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_only/daic/daic_officialdev_qwen_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I367" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B368" s="11" t="inlineStr">
@@ -22100,42 +22100,42 @@
       </c>
       <c r="C368" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D368" s="11" t="inlineStr">
         <is>
-          <t>Qwen XGBoost raw hidden head recall</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E368" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T153611Z-daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3-90c6cc39-df721ed6, eval eval-28be66b87b3641742e847e9d, backend qwen_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G368" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H368" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_officialdev_heads/text_only/daic/daic_officialdev_qwen_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r3/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I368" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B369" s="11" t="inlineStr">
@@ -22145,42 +22145,42 @@
       </c>
       <c r="C369" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D369" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head macro-F1</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E369" s="12" t="n">
-        <v>0.7619047619047619</v>
+        <v>0</v>
       </c>
       <c r="F369" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G369" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H369" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I369" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B370" s="11" t="inlineStr">
@@ -22190,42 +22190,42 @@
       </c>
       <c r="C370" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio only</t>
         </is>
       </c>
       <c r="D370" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head positive-F1</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E370" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_only_seed1337-22f85e6e-bb8bbbed, eval eval-6df29e41d91c3bd14a35b17a, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G370" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H370" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_only/daic/daic_officialdev_gemma4_audio_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I370" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B371" s="11" t="inlineStr">
@@ -22235,42 +22235,42 @@
       </c>
       <c r="C371" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D371" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head accuracy</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E371" s="12" t="n">
-        <v>0.8</v>
+        <v>0.6258503401360545</v>
       </c>
       <c r="F371" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G371" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H371" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I371" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B372" s="11" t="inlineStr">
@@ -22280,42 +22280,42 @@
       </c>
       <c r="C372" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D372" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head precision</t>
+          <t>Qwen teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E372" s="12" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G372" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H372" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I372" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B373" s="11" t="inlineStr">
@@ -22325,42 +22325,42 @@
       </c>
       <c r="C373" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D373" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 LogReg raw hidden head recall</t>
+          <t>Qwen teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E373" s="12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="F373" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-846a6445ccd968563f454777, backend gemma4_hidden_logreg_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_audio_text_seed1337-22f85e6e-16e99f52, eval eval-c4dd0ff1892bd0e3a39cc9bb, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G373" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H373" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/audio_text/daic/daic_officialdev_qwen_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I373" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B374" s="11" t="inlineStr">
@@ -22370,42 +22370,42 @@
       </c>
       <c r="C374" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D374" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head macro-F1</t>
+          <t>Gemma 4 teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E374" s="12" t="n">
-        <v>0.6685606060606061</v>
+        <v>0.7552447552447553</v>
       </c>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G374" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H374" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I374" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B375" s="11" t="inlineStr">
@@ -22415,42 +22415,42 @@
       </c>
       <c r="C375" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D375" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head positive-F1</t>
+          <t>Gemma 4 teacher-forced positive-F1</t>
         </is>
       </c>
       <c r="E375" s="12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="F375" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G375" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H375" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I375" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B376" s="11" t="inlineStr">
@@ -22460,42 +22460,42 @@
       </c>
       <c r="C376" s="11" t="inlineStr">
         <is>
-          <t>Text only</t>
+          <t>Audio + Text</t>
         </is>
       </c>
       <c r="D376" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head accuracy</t>
+          <t>Gemma 4 teacher-forced accuracy</t>
         </is>
       </c>
       <c r="E376" s="12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_gemma4_audio_text_seed1337-22f85e6e-df9dad6b, eval eval-0eb033332e85c3a84b70b52e, selected epoch 2, best_model</t>
         </is>
       </c>
       <c r="G376" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H376" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_gemma4_officialdev/audio_text/daic/daic_officialdev_gemma4_audio_text_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I376" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="11" t="inlineStr">
         <is>
-          <t>DAIC Head Ablation</t>
+          <t>DAIC official development</t>
         </is>
       </c>
       <c r="B377" s="11" t="inlineStr">
@@ -22510,73 +22510,2953 @@
       </c>
       <c r="D377" s="11" t="inlineStr">
         <is>
-          <t>Gemma 4 XGBoost raw hidden head precision</t>
+          <t>Qwen teacher-forced macro-F1</t>
         </is>
       </c>
       <c r="E377" s="12" t="n">
-        <v>0.6</v>
+        <v>0.7086031452358927</v>
       </c>
       <c r="F377" s="13" t="inlineStr">
         <is>
-          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T163105Z-daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5-90c6cc39-bee30555, eval eval-f5173eec4fb4b8a5fb612e04, backend gemma4_hidden_xgb_raw, parent best_model</t>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
         </is>
       </c>
       <c r="G377" s="13" t="inlineStr">
         <is>
-          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
         </is>
       </c>
       <c r="H377" s="13" t="inlineStr">
         <is>
-          <t>output_model/harmonized_v1_gemma4_officialdev_heads/text_only/daic/daic_officialdev_gemma4_text_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r5/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
         </is>
       </c>
       <c r="I377" s="13" t="inlineStr">
         <is>
-          <t>recomputed locally by verify-local; REPORTABLE</t>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="11" t="inlineStr">
         <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B378" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C378" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D378" s="11" t="inlineStr">
+        <is>
+          <t>Qwen teacher-forced positive-F1</t>
+        </is>
+      </c>
+      <c r="E378" s="12" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="F378" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+        </is>
+      </c>
+      <c r="G378" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H378" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I378" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="11" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B379" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C379" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D379" s="11" t="inlineStr">
+        <is>
+          <t>Qwen teacher-forced accuracy</t>
+        </is>
+      </c>
+      <c r="E379" s="12" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="F379" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142848Z-daic_officialdev_qwen_text_only_seed1337-22f85e6e-713b6d93, eval eval-6a466b499f152ea1b9c3c489, selected epoch 1, best_model</t>
+        </is>
+      </c>
+      <c r="G379" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H379" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev/text_only/daic/daic_officialdev_qwen_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I379" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="11" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B380" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C380" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D380" s="11" t="inlineStr">
+        <is>
+          <t>Gemma 4 teacher-forced macro-F1</t>
+        </is>
+      </c>
+      <c r="E380" s="12" t="n">
+        <v>0.7822222222222222</v>
+      </c>
+      <c r="F380" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+        </is>
+      </c>
+      <c r="G380" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H380" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I380" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="11" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B381" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C381" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D381" s="11" t="inlineStr">
+        <is>
+          <t>Gemma 4 teacher-forced positive-F1</t>
+        </is>
+      </c>
+      <c r="E381" s="12" t="n">
+        <v>0.7199999999999999</v>
+      </c>
+      <c r="F381" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+        </is>
+      </c>
+      <c r="G381" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H381" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I381" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="11" t="inlineStr">
+        <is>
+          <t>DAIC official development</t>
+        </is>
+      </c>
+      <c r="B382" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C382" s="11" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D382" s="11" t="inlineStr">
+        <is>
+          <t>Gemma 4 teacher-forced accuracy</t>
+        </is>
+      </c>
+      <c r="E382" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F382" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T142849Z-daic_officialdev_gemma4_text_only_seed1337-22f85e6e-75450bbe, eval eval-8a5d52df50d78e5dbeae4008, selected epoch 4, best_model</t>
+        </is>
+      </c>
+      <c r="G382" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H382" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4_officialdev/text_only/daic/daic_officialdev_gemma4_text_only_seed1337_prod_20260813T150000Z_22f85e6e_22f85e6e/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I382" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally from synced predictions; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="11" t="inlineStr">
+        <is>
           <t>DAIC Head Ablation</t>
         </is>
       </c>
-      <c r="B378" s="11" t="inlineStr">
+      <c r="B383" s="11" t="inlineStr">
         <is>
           <t>DAIC</t>
         </is>
       </c>
-      <c r="C378" s="11" t="inlineStr">
+      <c r="C383" s="11" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D383" s="11" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E383" s="12" t="n">
+        <v>0.5716783216783217</v>
+      </c>
+      <c r="F383" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G383" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H383" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I383" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B384" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C384" s="11" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D384" s="11" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E384" s="12" t="n">
+        <v>0.4615384615384615</v>
+      </c>
+      <c r="F384" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G384" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H384" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I384" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B385" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C385" s="11" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D385" s="11" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head accuracy</t>
+        </is>
+      </c>
+      <c r="E385" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F385" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G385" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H385" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I385" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B386" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C386" s="11" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D386" s="11" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head precision</t>
+        </is>
+      </c>
+      <c r="E386" s="12" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="F386" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G386" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H386" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I386" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B387" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C387" s="11" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D387" s="11" t="inlineStr">
+        <is>
+          <t>Qwen LogReg raw hidden head recall</t>
+        </is>
+      </c>
+      <c r="E387" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F387" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-e84ce4e0072e72d7eff086bb, backend qwen_hidden_logreg_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G387" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H387" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/logreg/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I387" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B388" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C388" s="11" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D388" s="11" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head macro-F1</t>
+        </is>
+      </c>
+      <c r="E388" s="12" t="n">
+        <v>0.4484848484848484</v>
+      </c>
+      <c r="F388" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G388" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H388" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I388" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      </c>
+      <c r="B389" s="11" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C389" s="11" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D389" s="11" t="inlineStr">
+        <is>
+          <t>Qwen XGBoost raw hidden head positive-F1</t>
+        </is>
+      </c>
+      <c r="E389" s="12" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="F389" s="13" t="inlineStr">
+        <is>
+          <t>campaign prod_20260813T150000Z_22f85e6e, group daic-officialdev-qwen-gemma-v1-22f85e6e473b, source 22f85e6e (clean main), Issue #60 / PR #52, manifest 72e2dd204b91… / split 441333e0c888…, attempt 20260813T154455Z-daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4-90c6cc39-269b5f37, eval eval-125e3b8f5bcc860eb4369ceb, backend qwen_hidden_xgb_raw, parent best_model</t>
+        </is>
+      </c>
+      <c r="G389" s="13" t="inlineStr">
+        <is>
+          <t>official development partition (35 subjects), subject mean probability &gt;= 0.5, binary-strict, harmonized_all_windows_full_coverage, daic_official_train_inner_split_dev_evaluation</t>
+        </is>
+      </c>
+      <c r="H389" s="13" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_officialdev_heads/audio_only/daic/daic_officialdev_qwen_audio_only_fixed_heads_seed1337_prod_20260813t150000z_22f85e6e_90c6cc39_r4/fold_0/hidden_classifiers/xgb/metrics.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I389" s="13" t="inlineStr">
+        <is>
+          <t>recomputed locally by verify-local; REPORTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="11" t="inlineStr">
+        <is>
+          <t>DAIC Head Ablation</t>
+        </is>
+      